--- a/prix/prix.xlsx
+++ b/prix/prix.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\platres-et-enduits\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\site-internet\platres-et-enduits\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A489E4-36FD-449E-9EDE-2F9001742A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36A36D4D-891B-49DF-9424-0B93C11DDE61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="409">
   <si>
     <t>path</t>
   </si>
@@ -1036,6 +1036,252 @@
   </si>
   <si>
     <t>galerie/vis-montage-rapide-pfs.png</t>
+  </si>
+  <si>
+    <t>61063472</t>
+  </si>
+  <si>
+    <t>61063474</t>
+  </si>
+  <si>
+    <t>61063475</t>
+  </si>
+  <si>
+    <t>61063476</t>
+  </si>
+  <si>
+    <t>61063477</t>
+  </si>
+  <si>
+    <t>61063480</t>
+  </si>
+  <si>
+    <t>61063484</t>
+  </si>
+  <si>
+    <t>61063486</t>
+  </si>
+  <si>
+    <t>61063488</t>
+  </si>
+  <si>
+    <t>61063492</t>
+  </si>
+  <si>
+    <t>61063494</t>
+  </si>
+  <si>
+    <t>Platresse INOX  280</t>
+  </si>
+  <si>
+    <t>Platresse INOX  260 mm cp217426</t>
+  </si>
+  <si>
+    <t>Platresse a chape cp400262</t>
+  </si>
+  <si>
+    <t>Platresse inox- 0.3mm 28x11</t>
+  </si>
+  <si>
+    <t>Platresse inox- 0.3mm 35X11</t>
+  </si>
+  <si>
+    <t>Platresse ACIER 280</t>
+  </si>
+  <si>
+    <t>Platresse  inox 280 mm dent 6 x 6 m</t>
+  </si>
+  <si>
+    <t>Platresse inox 280 mm dent 8 x 8 mm</t>
+  </si>
+  <si>
+    <t>Platresse inox 280 mm dent 10 x 10</t>
+  </si>
+  <si>
+    <t>Platresse inox 100x450 arrondie</t>
+  </si>
+  <si>
+    <t>Platresse inox 120x305 arrondie 0.65</t>
+  </si>
+  <si>
+    <t>61118599</t>
+  </si>
+  <si>
+    <t>61118606</t>
+  </si>
+  <si>
+    <t>61118607</t>
+  </si>
+  <si>
+    <t>61118610</t>
+  </si>
+  <si>
+    <t>61118611</t>
+  </si>
+  <si>
+    <t>61118612</t>
+  </si>
+  <si>
+    <t>61118614</t>
+  </si>
+  <si>
+    <t>61118651</t>
+  </si>
+  <si>
+    <t>61118652</t>
+  </si>
+  <si>
+    <t>61119013</t>
+  </si>
+  <si>
+    <t>61119014</t>
+  </si>
+  <si>
+    <t>61119015</t>
+  </si>
+  <si>
+    <t>61119022</t>
+  </si>
+  <si>
+    <t>61119180</t>
+  </si>
+  <si>
+    <t>61119182</t>
+  </si>
+  <si>
+    <t>61119184</t>
+  </si>
+  <si>
+    <t>61119190</t>
+  </si>
+  <si>
+    <t>61119191</t>
+  </si>
+  <si>
+    <t>61119192</t>
+  </si>
+  <si>
+    <t>61119196</t>
+  </si>
+  <si>
+    <t>61119198</t>
+  </si>
+  <si>
+    <t>61119200</t>
+  </si>
+  <si>
+    <t>611192000</t>
+  </si>
+  <si>
+    <t>61119201</t>
+  </si>
+  <si>
+    <t>61119202</t>
+  </si>
+  <si>
+    <t>61119204</t>
+  </si>
+  <si>
+    <t>61119206</t>
+  </si>
+  <si>
+    <t>61119210</t>
+  </si>
+  <si>
+    <t>platress+B2:B26e inox 280x130mm</t>
+  </si>
+  <si>
+    <t>Platresse  hollande dentée inox 33433440</t>
+  </si>
+  <si>
+    <t>Platresse  hollande dentée inoxx</t>
+  </si>
+  <si>
+    <t>Platresse hollande inox 28x13 33433437</t>
+  </si>
+  <si>
+    <t>Palette de platrier alu ds36950</t>
+  </si>
+  <si>
+    <t>Platresse inox dentee 12x12</t>
+  </si>
+  <si>
+    <t>Platresse acier pointue 110x400</t>
+  </si>
+  <si>
+    <t>Platresse Plasticflex 330x110x1mm</t>
+  </si>
+  <si>
+    <t>Platresse coins arrondis 406x100</t>
+  </si>
+  <si>
+    <t>Taloche plastique 14x8cm</t>
+  </si>
+  <si>
+    <t>Taloche gratton 14x24cm</t>
+  </si>
+  <si>
+    <t>Taloche frottoir blanc 120x250</t>
+  </si>
+  <si>
+    <t>Trepan multi mat.D35</t>
+  </si>
+  <si>
+    <t>Palette de joint droite - inox 230</t>
+  </si>
+  <si>
+    <t>Palette de joint gauche - inox 230</t>
+  </si>
+  <si>
+    <t>Palette de joint droite pl252132</t>
+  </si>
+  <si>
+    <t>Taloche point polyst noir 27x18</t>
+  </si>
+  <si>
+    <t>Taloche point polyst noir  27x18</t>
+  </si>
+  <si>
+    <t>Taloche rect polyst noir 350 x 260m</t>
+  </si>
+  <si>
+    <t>Taloche rect. épong oran. pl260028</t>
+  </si>
+  <si>
+    <t>Taloche angulaire éponge orange</t>
+  </si>
+  <si>
+    <t>Taloche éponge orange</t>
+  </si>
+  <si>
+    <t>Taloche mousse orange</t>
+  </si>
+  <si>
+    <t>Taloche éponge noire</t>
+  </si>
+  <si>
+    <t>Frottoir en polyurethane 280x140</t>
+  </si>
+  <si>
+    <t>Platoir ragni 318 28x12</t>
+  </si>
+  <si>
+    <t>Platoir plast semelle hydro eponge</t>
+  </si>
+  <si>
+    <t>Platoir plast rape métal 108127</t>
+  </si>
+  <si>
+    <t>61063286</t>
+  </si>
+  <si>
+    <t>61063287</t>
+  </si>
+  <si>
+    <t>Couteau à enduire 800mm x 0.3mm</t>
+  </si>
+  <si>
+    <t>Couteau à enduire 600mm x 0.3mm</t>
   </si>
 </sst>
 </file>
@@ -1171,7 +1417,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1204,17 +1450,11 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1228,24 +1468,21 @@
     <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1601,7 +1838,7 @@
       <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="18" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="7" t="s">
@@ -1656,7 +1893,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="25"/>
+      <c r="A4" s="20"/>
       <c r="B4" s="11" t="s">
         <v>71</v>
       </c>
@@ -1674,7 +1911,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="25"/>
+      <c r="A5" s="20"/>
       <c r="B5" s="11" t="s">
         <v>72</v>
       </c>
@@ -1792,7 +2029,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="25"/>
+      <c r="A11" s="20"/>
       <c r="B11" s="11" t="s">
         <v>78</v>
       </c>
@@ -1850,7 +2087,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="25"/>
+      <c r="A14" s="20"/>
       <c r="B14" s="2" t="s">
         <v>321</v>
       </c>
@@ -2008,7 +2245,7 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="25"/>
+      <c r="A22" s="20"/>
       <c r="B22" s="11" t="s">
         <v>88</v>
       </c>
@@ -2026,7 +2263,7 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="25"/>
+      <c r="A23" s="20"/>
       <c r="B23" s="11" t="s">
         <v>89</v>
       </c>
@@ -2044,7 +2281,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="25"/>
+      <c r="A24" s="20"/>
       <c r="B24" s="11" t="s">
         <v>90</v>
       </c>
@@ -2062,7 +2299,7 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="25"/>
+      <c r="A25" s="20"/>
       <c r="B25" s="11" t="s">
         <v>91</v>
       </c>
@@ -2160,7 +2397,7 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="25"/>
+      <c r="A30" s="20"/>
       <c r="B30" s="11" t="s">
         <v>96</v>
       </c>
@@ -2178,7 +2415,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="25"/>
+      <c r="A31" s="20"/>
       <c r="B31" s="11" t="s">
         <v>97</v>
       </c>
@@ -2216,7 +2453,7 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="25"/>
+      <c r="A33" s="20"/>
       <c r="B33" s="11" t="s">
         <v>99</v>
       </c>
@@ -2234,7 +2471,7 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="25"/>
+      <c r="A34" s="20"/>
       <c r="B34" s="11" t="s">
         <v>100</v>
       </c>
@@ -2252,7 +2489,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="25"/>
+      <c r="A35" s="20"/>
       <c r="B35" s="11" t="s">
         <v>101</v>
       </c>
@@ -2270,7 +2507,7 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="25"/>
+      <c r="A36" s="20"/>
       <c r="B36" s="11" t="s">
         <v>102</v>
       </c>
@@ -2351,7 +2588,7 @@
       <c r="A40" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="B40" s="16" t="s">
+      <c r="B40" s="14" t="s">
         <v>19</v>
       </c>
       <c r="C40" s="5" t="s">
@@ -2420,7 +2657,7 @@
       <c r="D43" s="3">
         <v>20.76</v>
       </c>
-      <c r="E43" s="17" t="s">
+      <c r="E43" s="15" t="s">
         <v>12</v>
       </c>
       <c r="F43" s="5">
@@ -2440,7 +2677,7 @@
       <c r="D44" s="3">
         <v>31.470000000000002</v>
       </c>
-      <c r="E44" s="17" t="s">
+      <c r="E44" s="15" t="s">
         <v>13</v>
       </c>
       <c r="F44" s="5">
@@ -2460,7 +2697,7 @@
       <c r="D45" s="3">
         <v>21.89</v>
       </c>
-      <c r="E45" s="18" t="s">
+      <c r="E45" s="16" t="s">
         <v>14</v>
       </c>
       <c r="F45" s="5">
@@ -2480,7 +2717,7 @@
       <c r="D46" s="3">
         <v>6.6400000000000006</v>
       </c>
-      <c r="E46" s="18" t="s">
+      <c r="E46" s="16" t="s">
         <v>15</v>
       </c>
       <c r="F46" s="5">
@@ -2500,7 +2737,7 @@
       <c r="D47" s="3">
         <v>5.47</v>
       </c>
-      <c r="E47" s="19" t="s">
+      <c r="E47" s="17" t="s">
         <v>103</v>
       </c>
       <c r="F47" s="5">
@@ -2520,7 +2757,7 @@
       <c r="D48" s="3">
         <v>4.33</v>
       </c>
-      <c r="E48" s="19" t="s">
+      <c r="E48" s="17" t="s">
         <v>104</v>
       </c>
       <c r="F48" s="5">
@@ -2540,7 +2777,7 @@
       <c r="D49" s="3">
         <v>4.84</v>
       </c>
-      <c r="E49" s="19" t="s">
+      <c r="E49" s="17" t="s">
         <v>105</v>
       </c>
       <c r="F49" s="5">
@@ -2560,7 +2797,7 @@
       <c r="D50" s="3">
         <v>5.09</v>
       </c>
-      <c r="E50" s="19" t="s">
+      <c r="E50" s="17" t="s">
         <v>106</v>
       </c>
       <c r="F50" s="5">
@@ -2580,7 +2817,7 @@
       <c r="D51" s="3">
         <v>5.26</v>
       </c>
-      <c r="E51" s="19" t="s">
+      <c r="E51" s="17" t="s">
         <v>107</v>
       </c>
       <c r="F51" s="5">
@@ -2600,7 +2837,7 @@
       <c r="D52" s="3">
         <v>5.09</v>
       </c>
-      <c r="E52" s="19" t="s">
+      <c r="E52" s="17" t="s">
         <v>108</v>
       </c>
       <c r="F52" s="5">
@@ -2620,7 +2857,7 @@
       <c r="D53" s="3">
         <v>5.26</v>
       </c>
-      <c r="E53" s="19" t="s">
+      <c r="E53" s="17" t="s">
         <v>109</v>
       </c>
       <c r="F53" s="5">
@@ -2640,7 +2877,7 @@
       <c r="D54" s="3">
         <v>5.13</v>
       </c>
-      <c r="E54" s="19" t="s">
+      <c r="E54" s="17" t="s">
         <v>110</v>
       </c>
       <c r="F54" s="5">
@@ -2660,7 +2897,7 @@
       <c r="D55" s="3">
         <v>5.09</v>
       </c>
-      <c r="E55" s="19" t="s">
+      <c r="E55" s="17" t="s">
         <v>111</v>
       </c>
       <c r="F55" s="5">
@@ -2680,7 +2917,7 @@
       <c r="D56" s="3">
         <v>9.0400000000000009</v>
       </c>
-      <c r="E56" s="19" t="s">
+      <c r="E56" s="17" t="s">
         <v>112</v>
       </c>
       <c r="F56" s="5">
@@ -2700,7 +2937,7 @@
       <c r="D57" s="3">
         <v>9.0400000000000009</v>
       </c>
-      <c r="E57" s="19" t="s">
+      <c r="E57" s="17" t="s">
         <v>113</v>
       </c>
       <c r="F57" s="5">
@@ -2720,7 +2957,7 @@
       <c r="D58" s="3">
         <v>7.25</v>
       </c>
-      <c r="E58" s="19" t="s">
+      <c r="E58" s="17" t="s">
         <v>114</v>
       </c>
       <c r="F58" s="5">
@@ -2740,7 +2977,7 @@
       <c r="D59" s="3">
         <v>8.16</v>
       </c>
-      <c r="E59" s="19" t="s">
+      <c r="E59" s="17" t="s">
         <v>115</v>
       </c>
       <c r="F59" s="5">
@@ -2760,7 +2997,7 @@
       <c r="D60" s="3">
         <v>7.71</v>
       </c>
-      <c r="E60" s="19" t="s">
+      <c r="E60" s="17" t="s">
         <v>116</v>
       </c>
       <c r="F60" s="5">
@@ -2780,7 +3017,7 @@
       <c r="D61" s="3">
         <v>8.4499999999999993</v>
       </c>
-      <c r="E61" s="19" t="s">
+      <c r="E61" s="17" t="s">
         <v>117</v>
       </c>
       <c r="F61" s="5">
@@ -2791,7 +3028,7 @@
       <c r="A62" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="B62" s="16" t="s">
+      <c r="B62" s="14" t="s">
         <v>134</v>
       </c>
       <c r="C62" s="2" t="s">
@@ -2800,7 +3037,7 @@
       <c r="D62" s="3">
         <v>9.33</v>
       </c>
-      <c r="E62" s="19" t="s">
+      <c r="E62" s="17" t="s">
         <v>118</v>
       </c>
       <c r="F62" s="5">
@@ -2820,7 +3057,7 @@
       <c r="D63" s="3">
         <v>23.900000000000002</v>
       </c>
-      <c r="E63" s="20" t="s">
+      <c r="E63" s="22" t="s">
         <v>135</v>
       </c>
       <c r="F63" s="5">
@@ -2831,7 +3068,7 @@
       <c r="A64" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="B64" s="16" t="s">
+      <c r="B64" s="14" t="s">
         <v>144</v>
       </c>
       <c r="C64" s="2" t="s">
@@ -2840,7 +3077,7 @@
       <c r="D64" s="3">
         <v>10.9</v>
       </c>
-      <c r="E64" s="20" t="s">
+      <c r="E64" s="22" t="s">
         <v>136</v>
       </c>
       <c r="F64" s="5">
@@ -2860,7 +3097,7 @@
       <c r="D65" s="3">
         <v>12.06</v>
       </c>
-      <c r="E65" s="20" t="s">
+      <c r="E65" s="22" t="s">
         <v>137</v>
       </c>
       <c r="F65" s="5">
@@ -2880,7 +3117,7 @@
       <c r="D66" s="3">
         <v>1.78</v>
       </c>
-      <c r="E66" s="20" t="s">
+      <c r="E66" s="22" t="s">
         <v>138</v>
       </c>
       <c r="F66" s="5">
@@ -2900,7 +3137,7 @@
       <c r="D67" s="3">
         <v>5.48</v>
       </c>
-      <c r="E67" s="20" t="s">
+      <c r="E67" s="22" t="s">
         <v>139</v>
       </c>
       <c r="F67" s="5">
@@ -2908,7 +3145,7 @@
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A68" s="25"/>
+      <c r="A68" s="20"/>
       <c r="B68" s="11" t="s">
         <v>148</v>
       </c>
@@ -2918,7 +3155,7 @@
       <c r="D68" s="3">
         <v>5</v>
       </c>
-      <c r="E68" s="20" t="s">
+      <c r="E68" s="22" t="s">
         <v>140</v>
       </c>
       <c r="F68" s="5">
@@ -2938,7 +3175,7 @@
       <c r="D69" s="3">
         <v>5.49</v>
       </c>
-      <c r="E69" s="20" t="s">
+      <c r="E69" s="22" t="s">
         <v>141</v>
       </c>
       <c r="F69" s="5">
@@ -2946,7 +3183,7 @@
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" s="25"/>
+      <c r="A70" s="20"/>
       <c r="B70" s="11" t="s">
         <v>150</v>
       </c>
@@ -2956,7 +3193,7 @@
       <c r="D70" s="3">
         <v>19.41</v>
       </c>
-      <c r="E70" s="20" t="s">
+      <c r="E70" s="22" t="s">
         <v>142</v>
       </c>
       <c r="F70" s="5">
@@ -2976,13 +3213,13 @@
       <c r="D71" s="3">
         <v>25.8</v>
       </c>
-      <c r="E71" s="22" t="s">
+      <c r="E71" s="23" t="s">
         <v>151</v>
       </c>
       <c r="F71" s="5">
         <v>4</v>
       </c>
-      <c r="G71" s="23"/>
+      <c r="G71" s="19"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
@@ -2997,7 +3234,7 @@
       <c r="D72" s="3">
         <v>27.3</v>
       </c>
-      <c r="E72" s="22" t="s">
+      <c r="E72" s="23" t="s">
         <v>152</v>
       </c>
       <c r="F72" s="5">
@@ -3017,7 +3254,7 @@
       <c r="D73" s="3">
         <v>40.119999999999997</v>
       </c>
-      <c r="E73" s="22" t="s">
+      <c r="E73" s="23" t="s">
         <v>153</v>
       </c>
       <c r="F73" s="5">
@@ -3037,7 +3274,7 @@
       <c r="D74" s="3">
         <v>16.170000000000002</v>
       </c>
-      <c r="E74" s="22" t="s">
+      <c r="E74" s="23" t="s">
         <v>154</v>
       </c>
       <c r="F74" s="5">
@@ -3057,7 +3294,7 @@
       <c r="D75" s="3">
         <v>22.05</v>
       </c>
-      <c r="E75" s="22" t="s">
+      <c r="E75" s="23" t="s">
         <v>155</v>
       </c>
       <c r="F75" s="5">
@@ -3077,7 +3314,7 @@
       <c r="D76" s="3">
         <v>25.810000000000002</v>
       </c>
-      <c r="E76" s="22" t="s">
+      <c r="E76" s="23" t="s">
         <v>156</v>
       </c>
       <c r="F76" s="5">
@@ -3097,7 +3334,7 @@
       <c r="D77" s="3">
         <v>13.07</v>
       </c>
-      <c r="E77" s="22" t="s">
+      <c r="E77" s="23" t="s">
         <v>157</v>
       </c>
       <c r="F77" s="5">
@@ -3117,7 +3354,7 @@
       <c r="D78" s="3">
         <v>3.15</v>
       </c>
-      <c r="E78" s="22" t="s">
+      <c r="E78" s="23" t="s">
         <v>158</v>
       </c>
       <c r="F78" s="5">
@@ -3137,7 +3374,7 @@
       <c r="D79" s="3">
         <v>16.63</v>
       </c>
-      <c r="E79" s="22" t="s">
+      <c r="E79" s="23" t="s">
         <v>159</v>
       </c>
       <c r="F79" s="5">
@@ -3157,7 +3394,7 @@
       <c r="D80" s="3">
         <v>6.17</v>
       </c>
-      <c r="E80" s="22" t="s">
+      <c r="E80" s="23" t="s">
         <v>160</v>
       </c>
       <c r="F80" s="5">
@@ -3177,7 +3414,7 @@
       <c r="D81" s="3">
         <v>15.73</v>
       </c>
-      <c r="E81" s="22" t="s">
+      <c r="E81" s="23" t="s">
         <v>161</v>
       </c>
       <c r="F81" s="5">
@@ -3197,7 +3434,7 @@
       <c r="D82" s="3">
         <v>3.92</v>
       </c>
-      <c r="E82" s="22" t="s">
+      <c r="E82" s="23" t="s">
         <v>162</v>
       </c>
       <c r="F82" s="5">
@@ -3217,7 +3454,7 @@
       <c r="D83" s="3">
         <v>21.95</v>
       </c>
-      <c r="E83" s="22" t="s">
+      <c r="E83" s="23" t="s">
         <v>163</v>
       </c>
       <c r="F83" s="5">
@@ -3237,7 +3474,7 @@
       <c r="D84" s="3">
         <v>4.99</v>
       </c>
-      <c r="E84" s="22" t="s">
+      <c r="E84" s="23" t="s">
         <v>164</v>
       </c>
       <c r="F84" s="5">
@@ -3257,7 +3494,7 @@
       <c r="D85" s="3">
         <v>7.36</v>
       </c>
-      <c r="E85" s="22" t="s">
+      <c r="E85" s="23" t="s">
         <v>165</v>
       </c>
       <c r="F85" s="5">
@@ -3277,7 +3514,7 @@
       <c r="D86" s="3">
         <v>30.52</v>
       </c>
-      <c r="E86" s="22" t="s">
+      <c r="E86" s="23" t="s">
         <v>166</v>
       </c>
       <c r="F86" s="5">
@@ -3297,7 +3534,7 @@
       <c r="D87" s="3">
         <v>6.05</v>
       </c>
-      <c r="E87" s="22" t="s">
+      <c r="E87" s="23" t="s">
         <v>167</v>
       </c>
       <c r="F87" s="5">
@@ -3317,7 +3554,7 @@
       <c r="D88" s="3">
         <v>4.67</v>
       </c>
-      <c r="E88" s="22" t="s">
+      <c r="E88" s="23" t="s">
         <v>168</v>
       </c>
       <c r="F88" s="5">
@@ -3337,7 +3574,7 @@
       <c r="D89" s="3">
         <v>15.58</v>
       </c>
-      <c r="E89" s="22" t="s">
+      <c r="E89" s="23" t="s">
         <v>169</v>
       </c>
       <c r="F89" s="5">
@@ -3357,7 +3594,7 @@
       <c r="D90" s="3">
         <v>18.63</v>
       </c>
-      <c r="E90" s="22" t="s">
+      <c r="E90" s="23" t="s">
         <v>170</v>
       </c>
       <c r="F90" s="5">
@@ -3377,7 +3614,7 @@
       <c r="D91" s="3">
         <v>10.99</v>
       </c>
-      <c r="E91" s="22" t="s">
+      <c r="E91" s="23" t="s">
         <v>171</v>
       </c>
       <c r="F91" s="5">
@@ -3397,7 +3634,7 @@
       <c r="D92" s="3">
         <v>22.97</v>
       </c>
-      <c r="E92" s="22" t="s">
+      <c r="E92" s="23" t="s">
         <v>172</v>
       </c>
       <c r="F92" s="5">
@@ -3417,7 +3654,7 @@
       <c r="D93" s="3">
         <v>18.150000000000002</v>
       </c>
-      <c r="E93" s="22" t="s">
+      <c r="E93" s="23" t="s">
         <v>173</v>
       </c>
       <c r="F93" s="5">
@@ -3437,7 +3674,7 @@
       <c r="D94" s="3">
         <v>12.83</v>
       </c>
-      <c r="E94" s="22" t="s">
+      <c r="E94" s="23" t="s">
         <v>174</v>
       </c>
       <c r="F94" s="5">
@@ -3457,7 +3694,7 @@
       <c r="D95" s="3">
         <v>42.25</v>
       </c>
-      <c r="E95" s="22" t="s">
+      <c r="E95" s="23" t="s">
         <v>175</v>
       </c>
       <c r="F95" s="5">
@@ -3477,7 +3714,7 @@
       <c r="D96" s="3">
         <v>17.38</v>
       </c>
-      <c r="E96" s="22" t="s">
+      <c r="E96" s="23" t="s">
         <v>176</v>
       </c>
       <c r="F96" s="5">
@@ -3497,7 +3734,7 @@
       <c r="D97" s="3">
         <v>27.18</v>
       </c>
-      <c r="E97" s="22" t="s">
+      <c r="E97" s="23" t="s">
         <v>177</v>
       </c>
       <c r="F97" s="5">
@@ -3517,7 +3754,7 @@
       <c r="D98" s="3">
         <v>34.51</v>
       </c>
-      <c r="E98" s="22" t="s">
+      <c r="E98" s="23" t="s">
         <v>178</v>
       </c>
       <c r="F98" s="5">
@@ -3537,7 +3774,7 @@
       <c r="D99" s="3">
         <v>42.57</v>
       </c>
-      <c r="E99" s="22" t="s">
+      <c r="E99" s="23" t="s">
         <v>179</v>
       </c>
       <c r="F99" s="5">
@@ -3557,7 +3794,7 @@
       <c r="D100" s="3">
         <v>21.68</v>
       </c>
-      <c r="E100" s="22" t="s">
+      <c r="E100" s="23" t="s">
         <v>180</v>
       </c>
       <c r="F100" s="5">
@@ -3577,7 +3814,7 @@
       <c r="D101" s="3">
         <v>24.78</v>
       </c>
-      <c r="E101" s="22" t="s">
+      <c r="E101" s="23" t="s">
         <v>181</v>
       </c>
       <c r="F101" s="5">
@@ -3597,7 +3834,7 @@
       <c r="D102" s="3">
         <v>16.63</v>
       </c>
-      <c r="E102" s="22" t="s">
+      <c r="E102" s="23" t="s">
         <v>182</v>
       </c>
       <c r="F102" s="5">
@@ -3617,7 +3854,7 @@
       <c r="D103" s="3">
         <v>19.14</v>
       </c>
-      <c r="E103" s="22" t="s">
+      <c r="E103" s="23" t="s">
         <v>183</v>
       </c>
       <c r="F103" s="5">
@@ -3637,7 +3874,7 @@
       <c r="D104" s="3">
         <v>33.01</v>
       </c>
-      <c r="E104" s="22" t="s">
+      <c r="E104" s="23" t="s">
         <v>184</v>
       </c>
       <c r="F104" s="5">
@@ -3657,7 +3894,7 @@
       <c r="D105" s="3">
         <v>28.75</v>
       </c>
-      <c r="E105" s="24" t="s">
+      <c r="E105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="F105" s="5">
@@ -3677,7 +3914,7 @@
       <c r="D106" s="3">
         <v>58.82</v>
       </c>
-      <c r="E106" s="24" t="s">
+      <c r="E106" s="9" t="s">
         <v>27</v>
       </c>
       <c r="F106" s="5">
@@ -3697,7 +3934,7 @@
       <c r="D107" s="3">
         <v>23.490000000000002</v>
       </c>
-      <c r="E107" s="24" t="s">
+      <c r="E107" s="9" t="s">
         <v>28</v>
       </c>
       <c r="F107" s="5">
@@ -3717,7 +3954,7 @@
       <c r="D108" s="3">
         <v>59.9</v>
       </c>
-      <c r="E108" s="24" t="s">
+      <c r="E108" s="9" t="s">
         <v>29</v>
       </c>
       <c r="F108" s="5">
@@ -3726,812 +3963,1124 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="5"/>
-      <c r="B109" s="11"/>
+      <c r="B109" s="2" t="s">
+        <v>338</v>
+      </c>
       <c r="C109" s="5"/>
-      <c r="D109" s="14"/>
-      <c r="E109" s="15"/>
-      <c r="F109" s="13"/>
+      <c r="D109" s="3">
+        <v>10.89</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="F109" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="26"/>
-      <c r="B110" s="11"/>
+      <c r="A110" s="21"/>
+      <c r="B110" s="2" t="s">
+        <v>339</v>
+      </c>
       <c r="C110" s="5"/>
-      <c r="D110" s="14"/>
-      <c r="E110" s="15"/>
-      <c r="F110" s="13"/>
+      <c r="D110" s="3">
+        <v>20.63</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="F110" s="5">
+        <v>4</v>
+      </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="5"/>
-      <c r="B111" s="11"/>
+      <c r="B111" s="2" t="s">
+        <v>340</v>
+      </c>
       <c r="C111" s="5"/>
-      <c r="E111" s="12"/>
-      <c r="F111" s="5"/>
+      <c r="D111" s="3">
+        <v>35.6</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="F111" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="5"/>
-      <c r="B112" s="11"/>
+      <c r="B112" s="2" t="s">
+        <v>341</v>
+      </c>
       <c r="C112" s="5"/>
-      <c r="E112" s="12"/>
-      <c r="F112" s="5"/>
+      <c r="D112" s="3">
+        <v>30.21</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F112" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="5"/>
-      <c r="B113" s="11"/>
+      <c r="B113" s="2" t="s">
+        <v>342</v>
+      </c>
       <c r="C113" s="5"/>
-      <c r="E113" s="12"/>
-      <c r="F113" s="5"/>
+      <c r="D113" s="3">
+        <v>33.06</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="F113" s="5">
+        <v>3</v>
+      </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="5"/>
-      <c r="B114" s="11"/>
+      <c r="B114" s="2" t="s">
+        <v>343</v>
+      </c>
       <c r="C114" s="5"/>
-      <c r="E114" s="12"/>
-      <c r="F114" s="5"/>
+      <c r="D114" s="3">
+        <v>17.82</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="F114" s="5">
+        <v>5</v>
+      </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="5"/>
-      <c r="B115" s="11"/>
+      <c r="B115" s="2" t="s">
+        <v>344</v>
+      </c>
       <c r="C115" s="5"/>
-      <c r="E115" s="12"/>
-      <c r="F115" s="5"/>
+      <c r="D115" s="3">
+        <v>14.33</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="F115" s="5">
+        <v>4</v>
+      </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="5"/>
-      <c r="B116" s="11"/>
+      <c r="B116" s="2" t="s">
+        <v>345</v>
+      </c>
       <c r="C116" s="5"/>
-      <c r="D116" s="14"/>
-      <c r="E116" s="15"/>
-      <c r="F116" s="13"/>
+      <c r="D116" s="3">
+        <v>14.33</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F116" s="5">
+        <v>5</v>
+      </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="5"/>
-      <c r="B117" s="11"/>
+      <c r="B117" s="2" t="s">
+        <v>346</v>
+      </c>
       <c r="C117" s="5"/>
-      <c r="D117" s="14"/>
-      <c r="E117" s="15"/>
-      <c r="F117" s="13"/>
+      <c r="D117" s="3">
+        <v>14.33</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="F117" s="5">
+        <v>-1</v>
+      </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="5"/>
-      <c r="B118" s="11"/>
+      <c r="B118" s="2" t="s">
+        <v>347</v>
+      </c>
       <c r="C118" s="5"/>
-      <c r="D118" s="14"/>
-      <c r="E118" s="15"/>
-      <c r="F118" s="13"/>
+      <c r="D118" s="3">
+        <v>46.160000000000004</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="F118" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="5"/>
-      <c r="B119" s="11"/>
+      <c r="B119" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="C119" s="5"/>
-      <c r="D119" s="14"/>
-      <c r="E119" s="15"/>
-      <c r="F119" s="13"/>
+      <c r="D119" s="3">
+        <v>61.71</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="F119" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="5"/>
-      <c r="B120" s="16"/>
+      <c r="B120" s="2" t="s">
+        <v>377</v>
+      </c>
       <c r="C120" s="5"/>
-      <c r="E120" s="12"/>
-      <c r="F120" s="5"/>
+      <c r="D120" s="3">
+        <v>15.6</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="F120" s="5">
+        <v>4</v>
+      </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="5"/>
-      <c r="B121" s="11"/>
+      <c r="B121" s="2" t="s">
+        <v>378</v>
+      </c>
       <c r="C121" s="5"/>
-      <c r="D121" s="14"/>
-      <c r="E121" s="15"/>
-      <c r="F121" s="13"/>
+      <c r="D121" s="3">
+        <v>13.73</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="F121" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="5"/>
-      <c r="B122" s="11"/>
+      <c r="B122" s="2" t="s">
+        <v>379</v>
+      </c>
       <c r="C122" s="5"/>
-      <c r="D122" s="14"/>
-      <c r="E122" s="15"/>
-      <c r="F122" s="13"/>
+      <c r="D122" s="3">
+        <v>13.74</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="F122" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="5"/>
-      <c r="B123" s="11"/>
+      <c r="B123" s="2" t="s">
+        <v>380</v>
+      </c>
       <c r="C123" s="5"/>
-      <c r="D123" s="14"/>
-      <c r="E123" s="15"/>
-      <c r="F123" s="13"/>
+      <c r="D123" s="3">
+        <v>16.670000000000002</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F123" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="5"/>
-      <c r="B124" s="11"/>
+      <c r="B124" s="2" t="s">
+        <v>381</v>
+      </c>
       <c r="C124" s="5"/>
-      <c r="D124" s="14"/>
-      <c r="E124" s="15"/>
-      <c r="F124" s="13"/>
+      <c r="D124" s="3">
+        <v>24.490000000000002</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="F124" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="5"/>
-      <c r="B125" s="11"/>
+      <c r="B125" s="2" t="s">
+        <v>382</v>
+      </c>
       <c r="C125" s="5"/>
-      <c r="D125" s="14"/>
-      <c r="E125" s="15"/>
-      <c r="F125" s="13"/>
+      <c r="D125" s="3">
+        <v>14.31</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="F125" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="5"/>
-      <c r="B126" s="11"/>
+      <c r="B126" s="2" t="s">
+        <v>383</v>
+      </c>
       <c r="C126" s="5"/>
-      <c r="D126" s="14"/>
-      <c r="E126" s="15"/>
-      <c r="F126" s="13"/>
+      <c r="D126" s="3">
+        <v>21.54</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="F126" s="5">
+        <v>3</v>
+      </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="5"/>
-      <c r="B127" s="11"/>
+      <c r="B127" s="2" t="s">
+        <v>384</v>
+      </c>
       <c r="C127" s="5"/>
-      <c r="D127" s="14"/>
-      <c r="E127" s="15"/>
-      <c r="F127" s="13"/>
+      <c r="D127" s="3">
+        <v>48.35</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F127" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="5"/>
-      <c r="B128" s="11"/>
+      <c r="B128" s="2" t="s">
+        <v>385</v>
+      </c>
       <c r="C128" s="5"/>
-      <c r="D128" s="14"/>
-      <c r="E128" s="15"/>
-      <c r="F128" s="13"/>
+      <c r="D128" s="3">
+        <v>38.24</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="F128" s="5">
+        <v>5</v>
+      </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="5"/>
-      <c r="B129" s="11"/>
+      <c r="B129" s="2" t="s">
+        <v>386</v>
+      </c>
       <c r="C129" s="5"/>
-      <c r="D129" s="14"/>
-      <c r="E129" s="15"/>
-      <c r="F129" s="13"/>
+      <c r="D129" s="3">
+        <v>2.5300000000000002</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F129" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="5"/>
-      <c r="B130" s="11"/>
+      <c r="B130" s="2" t="s">
+        <v>387</v>
+      </c>
       <c r="C130" s="5"/>
-      <c r="D130" s="14"/>
-      <c r="E130" s="15"/>
-      <c r="F130" s="13"/>
+      <c r="D130" s="3">
+        <v>16.7</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="F130" s="5">
+        <v>3</v>
+      </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="5"/>
-      <c r="B131" s="11"/>
+      <c r="B131" s="2" t="s">
+        <v>388</v>
+      </c>
       <c r="C131" s="5"/>
-      <c r="D131" s="14"/>
-      <c r="E131" s="15"/>
-      <c r="F131" s="13"/>
+      <c r="D131" s="3">
+        <v>19.490000000000002</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="F131" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="5"/>
-      <c r="B132" s="11"/>
+      <c r="B132" s="2" t="s">
+        <v>389</v>
+      </c>
       <c r="C132" s="5"/>
-      <c r="D132" s="14"/>
-      <c r="E132" s="15"/>
-      <c r="F132" s="13"/>
+      <c r="D132" s="3">
+        <v>14.96</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F132" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="5"/>
-      <c r="B133" s="11"/>
+      <c r="B133" s="2" t="s">
+        <v>390</v>
+      </c>
       <c r="C133" s="5"/>
-      <c r="D133" s="14"/>
-      <c r="E133" s="15"/>
-      <c r="F133" s="13"/>
+      <c r="D133" s="3">
+        <v>36.78</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="F133" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="5"/>
-      <c r="B134" s="11"/>
+      <c r="B134" s="2" t="s">
+        <v>391</v>
+      </c>
       <c r="C134" s="5"/>
-      <c r="D134" s="14"/>
-      <c r="E134" s="15"/>
-      <c r="F134" s="13"/>
+      <c r="D134" s="3">
+        <v>21.6</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F134" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="5"/>
-      <c r="B135" s="11"/>
+      <c r="B135" s="2" t="s">
+        <v>392</v>
+      </c>
       <c r="C135" s="5"/>
-      <c r="D135" s="14"/>
-      <c r="E135" s="15"/>
-      <c r="F135" s="13"/>
+      <c r="D135" s="3">
+        <v>8.24</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="F135" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="5"/>
-      <c r="B136" s="11"/>
+      <c r="B136" s="2" t="s">
+        <v>393</v>
+      </c>
       <c r="C136" s="5"/>
-      <c r="D136" s="14"/>
-      <c r="E136" s="15"/>
-      <c r="F136" s="13"/>
+      <c r="D136" s="3">
+        <v>3.7</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="F136" s="5">
+        <v>3</v>
+      </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="5"/>
-      <c r="B137" s="11"/>
+      <c r="B137" s="2" t="s">
+        <v>394</v>
+      </c>
       <c r="C137" s="5"/>
-      <c r="D137" s="14"/>
-      <c r="E137" s="15"/>
-      <c r="F137" s="13"/>
+      <c r="D137" s="3">
+        <v>3.42</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F137" s="5">
+        <v>3</v>
+      </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="5"/>
-      <c r="B138" s="11"/>
+      <c r="B138" s="2" t="s">
+        <v>395</v>
+      </c>
       <c r="C138" s="5"/>
-      <c r="D138" s="14"/>
-      <c r="E138" s="15"/>
-      <c r="F138" s="13"/>
+      <c r="D138" s="3">
+        <v>4.59</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="F138" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="5"/>
-      <c r="B139" s="11"/>
+      <c r="B139" s="2" t="s">
+        <v>396</v>
+      </c>
       <c r="C139" s="5"/>
-      <c r="D139" s="14"/>
-      <c r="E139" s="15"/>
-      <c r="F139" s="13"/>
+      <c r="D139" s="3">
+        <v>12.4</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="F139" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="5"/>
+      <c r="B140" s="2" t="s">
+        <v>397</v>
+      </c>
       <c r="C140" s="5"/>
-      <c r="E140" s="12"/>
-      <c r="F140" s="5"/>
+      <c r="D140" s="3">
+        <v>10.16</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="F140" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="5"/>
+      <c r="B141" s="2" t="s">
+        <v>398</v>
+      </c>
       <c r="C141" s="5"/>
-      <c r="E141" s="12"/>
-      <c r="F141" s="5"/>
+      <c r="D141" s="3">
+        <v>9.15</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="F141" s="5">
+        <v>4</v>
+      </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="5"/>
+      <c r="B142" s="2" t="s">
+        <v>399</v>
+      </c>
       <c r="C142" s="5"/>
-      <c r="E142" s="12"/>
-      <c r="F142" s="5"/>
+      <c r="D142" s="3">
+        <v>11.69</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F142" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="5"/>
+      <c r="B143" s="2" t="s">
+        <v>400</v>
+      </c>
       <c r="C143" s="5"/>
-      <c r="E143" s="12"/>
-      <c r="F143" s="5"/>
+      <c r="D143" s="3">
+        <v>6.32</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="F143" s="5">
+        <v>3</v>
+      </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="5"/>
+      <c r="B144" s="2" t="s">
+        <v>401</v>
+      </c>
       <c r="C144" s="5"/>
-      <c r="E144" s="12"/>
-      <c r="F144" s="5"/>
+      <c r="D144" s="3">
+        <v>4.96</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="F144" s="5">
+        <v>3</v>
+      </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="5"/>
+      <c r="B145" s="2" t="s">
+        <v>402</v>
+      </c>
       <c r="C145" s="5"/>
-      <c r="E145" s="12"/>
-      <c r="F145" s="5"/>
+      <c r="D145" s="3">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F145" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="5"/>
+      <c r="B146" s="2" t="s">
+        <v>403</v>
+      </c>
       <c r="C146" s="5"/>
-      <c r="E146" s="12"/>
-      <c r="F146" s="5"/>
+      <c r="D146" s="3">
+        <v>8.14</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="F146" s="5">
+        <v>9</v>
+      </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="5"/>
+      <c r="B147" s="2" t="s">
+        <v>404</v>
+      </c>
       <c r="C147" s="5"/>
-      <c r="E147" s="12"/>
-      <c r="F147" s="5"/>
+      <c r="D147" s="3">
+        <v>5</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="F147" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="5"/>
+      <c r="B148" s="2" t="s">
+        <v>407</v>
+      </c>
       <c r="C148" s="5"/>
-      <c r="E148" s="12"/>
-      <c r="F148" s="5"/>
+      <c r="D148" s="3">
+        <v>68.489999999999995</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="F148" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="5"/>
-      <c r="B149" s="11"/>
+      <c r="B149" s="2" t="s">
+        <v>408</v>
+      </c>
       <c r="C149" s="5"/>
-      <c r="D149" s="14"/>
-      <c r="E149" s="15"/>
-      <c r="F149" s="13"/>
+      <c r="D149" s="3">
+        <v>53.36</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="F149" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="5"/>
       <c r="B150" s="11"/>
       <c r="C150" s="5"/>
-      <c r="D150" s="14"/>
-      <c r="E150" s="15"/>
-      <c r="F150" s="13"/>
+      <c r="D150" s="13"/>
+      <c r="E150" s="11"/>
+      <c r="F150" s="12"/>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="5"/>
       <c r="B151" s="11"/>
       <c r="C151" s="5"/>
-      <c r="D151" s="14"/>
-      <c r="E151" s="15"/>
-      <c r="F151" s="13"/>
+      <c r="D151" s="13"/>
+      <c r="E151" s="11"/>
+      <c r="F151" s="12"/>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="5"/>
-      <c r="B152" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="C152" s="5"/>
-      <c r="D152" s="3">
-        <v>28.75</v>
-      </c>
-      <c r="E152" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="F152" s="5">
-        <v>7</v>
-      </c>
+      <c r="E152" s="2"/>
+      <c r="F152" s="5"/>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" s="5"/>
-      <c r="B153" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="C153" s="5"/>
-      <c r="D153" s="3">
-        <v>58.82</v>
-      </c>
-      <c r="E153" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="F153" s="5">
-        <v>17</v>
-      </c>
+      <c r="E153" s="2"/>
+      <c r="F153" s="5"/>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" s="5"/>
-      <c r="B154" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="C154" s="5"/>
-      <c r="D154" s="3">
-        <v>23.490000000000002</v>
-      </c>
-      <c r="E154" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F154" s="5">
-        <v>12</v>
-      </c>
+      <c r="E154" s="2"/>
+      <c r="F154" s="5"/>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="5"/>
-      <c r="B155" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="C155" s="5"/>
-      <c r="D155" s="3">
-        <v>59.9</v>
-      </c>
-      <c r="E155" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F155" s="5">
-        <v>8</v>
-      </c>
+      <c r="E155" s="2"/>
+      <c r="F155" s="5"/>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" s="5"/>
       <c r="B156" s="11"/>
       <c r="C156" s="5"/>
-      <c r="D156" s="14"/>
-      <c r="E156" s="15"/>
-      <c r="F156" s="13"/>
+      <c r="D156" s="13"/>
+      <c r="E156" s="11"/>
+      <c r="F156" s="12"/>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" s="5"/>
       <c r="B157" s="11"/>
       <c r="C157" s="5"/>
-      <c r="D157" s="14"/>
-      <c r="E157" s="15"/>
-      <c r="F157" s="13"/>
+      <c r="D157" s="13"/>
+      <c r="E157" s="11"/>
+      <c r="F157" s="12"/>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" s="5"/>
       <c r="B158" s="11"/>
       <c r="C158" s="5"/>
-      <c r="D158" s="14"/>
-      <c r="E158" s="15"/>
-      <c r="F158" s="13"/>
+      <c r="D158" s="13"/>
+      <c r="E158" s="11"/>
+      <c r="F158" s="12"/>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" s="5"/>
       <c r="C159" s="5"/>
-      <c r="E159" s="12"/>
+      <c r="E159" s="2"/>
       <c r="F159" s="5"/>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" s="5"/>
       <c r="C160" s="5"/>
-      <c r="E160" s="12"/>
+      <c r="E160" s="2"/>
       <c r="F160" s="5"/>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" s="5"/>
       <c r="C161" s="5"/>
-      <c r="E161" s="12"/>
+      <c r="E161" s="2"/>
       <c r="F161" s="5"/>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" s="5"/>
       <c r="C162" s="5"/>
-      <c r="E162" s="12"/>
+      <c r="E162" s="2"/>
       <c r="F162" s="5"/>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" s="5"/>
       <c r="B163" s="11"/>
       <c r="C163" s="5"/>
-      <c r="E163" s="12"/>
+      <c r="E163" s="2"/>
       <c r="F163" s="5"/>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" s="5"/>
       <c r="B164" s="11"/>
       <c r="C164" s="5"/>
-      <c r="D164" s="14"/>
-      <c r="E164" s="15"/>
-      <c r="F164" s="13"/>
+      <c r="D164" s="13"/>
+      <c r="E164" s="11"/>
+      <c r="F164" s="12"/>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" s="5"/>
       <c r="B165" s="11"/>
       <c r="C165" s="5"/>
-      <c r="D165" s="14"/>
-      <c r="E165" s="15"/>
-      <c r="F165" s="13"/>
+      <c r="D165" s="13"/>
+      <c r="E165" s="11"/>
+      <c r="F165" s="12"/>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" s="5"/>
       <c r="B166" s="11"/>
       <c r="C166" s="5"/>
-      <c r="D166" s="14"/>
-      <c r="E166" s="15"/>
-      <c r="F166" s="13"/>
+      <c r="D166" s="13"/>
+      <c r="E166" s="11"/>
+      <c r="F166" s="12"/>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" s="5"/>
       <c r="B167" s="11"/>
       <c r="C167" s="5"/>
-      <c r="D167" s="14"/>
-      <c r="E167" s="15"/>
-      <c r="F167" s="13"/>
+      <c r="D167" s="13"/>
+      <c r="E167" s="11"/>
+      <c r="F167" s="12"/>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" s="5"/>
       <c r="B168" s="11"/>
       <c r="C168" s="5"/>
-      <c r="D168" s="14"/>
-      <c r="E168" s="15"/>
-      <c r="F168" s="13"/>
+      <c r="D168" s="13"/>
+      <c r="E168" s="11"/>
+      <c r="F168" s="12"/>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" s="5"/>
       <c r="B169" s="11"/>
       <c r="C169" s="5"/>
-      <c r="D169" s="14"/>
-      <c r="E169" s="15"/>
-      <c r="F169" s="13"/>
+      <c r="D169" s="13"/>
+      <c r="E169" s="11"/>
+      <c r="F169" s="12"/>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" s="5"/>
       <c r="B170" s="11"/>
       <c r="C170" s="5"/>
-      <c r="D170" s="14"/>
-      <c r="E170" s="15"/>
-      <c r="F170" s="13"/>
+      <c r="D170" s="13"/>
+      <c r="E170" s="11"/>
+      <c r="F170" s="12"/>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" s="5"/>
       <c r="B171" s="11"/>
       <c r="C171" s="5"/>
-      <c r="D171" s="14"/>
-      <c r="E171" s="15"/>
-      <c r="F171" s="13"/>
+      <c r="D171" s="13"/>
+      <c r="E171" s="11"/>
+      <c r="F171" s="12"/>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" s="5"/>
       <c r="B172" s="11"/>
       <c r="C172" s="5"/>
-      <c r="D172" s="14"/>
-      <c r="E172" s="15"/>
-      <c r="F172" s="13"/>
+      <c r="D172" s="13"/>
+      <c r="E172" s="11"/>
+      <c r="F172" s="12"/>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" s="5"/>
       <c r="B173" s="11"/>
       <c r="C173" s="5"/>
-      <c r="D173" s="14"/>
-      <c r="E173" s="15"/>
-      <c r="F173" s="13"/>
+      <c r="D173" s="13"/>
+      <c r="E173" s="11"/>
+      <c r="F173" s="12"/>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" s="5"/>
       <c r="B174" s="11"/>
       <c r="C174" s="5"/>
-      <c r="D174" s="14"/>
-      <c r="E174" s="15"/>
-      <c r="F174" s="13"/>
+      <c r="D174" s="13"/>
+      <c r="E174" s="11"/>
+      <c r="F174" s="12"/>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" s="5"/>
       <c r="B175" s="11"/>
       <c r="C175" s="5"/>
-      <c r="D175" s="14"/>
-      <c r="E175" s="15"/>
-      <c r="F175" s="13"/>
+      <c r="D175" s="13"/>
+      <c r="E175" s="11"/>
+      <c r="F175" s="12"/>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" s="5"/>
       <c r="B176" s="11"/>
       <c r="C176" s="5"/>
-      <c r="D176" s="14"/>
-      <c r="E176" s="15"/>
-      <c r="F176" s="13"/>
+      <c r="D176" s="13"/>
+      <c r="E176" s="11"/>
+      <c r="F176" s="12"/>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" s="5"/>
       <c r="B177" s="11"/>
       <c r="C177" s="5"/>
-      <c r="D177" s="14"/>
-      <c r="E177" s="15"/>
-      <c r="F177" s="13"/>
+      <c r="D177" s="13"/>
+      <c r="E177" s="11"/>
+      <c r="F177" s="12"/>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" s="5"/>
       <c r="B178" s="11"/>
       <c r="C178" s="5"/>
-      <c r="D178" s="14"/>
-      <c r="E178" s="15"/>
-      <c r="F178" s="13"/>
+      <c r="D178" s="13"/>
+      <c r="E178" s="11"/>
+      <c r="F178" s="12"/>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" s="5"/>
       <c r="B179" s="11"/>
       <c r="C179" s="5"/>
-      <c r="D179" s="14"/>
-      <c r="E179" s="15"/>
-      <c r="F179" s="13"/>
+      <c r="D179" s="13"/>
+      <c r="E179" s="11"/>
+      <c r="F179" s="12"/>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" s="5"/>
       <c r="C180" s="5"/>
-      <c r="E180" s="12"/>
+      <c r="E180" s="2"/>
       <c r="F180" s="5"/>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" s="5"/>
       <c r="C181" s="5"/>
-      <c r="E181" s="12"/>
+      <c r="E181" s="2"/>
       <c r="F181" s="5"/>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" s="5"/>
       <c r="B182" s="11"/>
       <c r="C182" s="5"/>
-      <c r="E182" s="12"/>
+      <c r="E182" s="2"/>
       <c r="F182" s="5"/>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" s="5"/>
       <c r="C183" s="5"/>
-      <c r="E183" s="12"/>
+      <c r="E183" s="2"/>
       <c r="F183" s="5"/>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" s="5"/>
       <c r="C184" s="5"/>
-      <c r="E184" s="12"/>
+      <c r="E184" s="2"/>
       <c r="F184" s="5"/>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" s="5"/>
       <c r="C185" s="5"/>
-      <c r="E185" s="12"/>
+      <c r="E185" s="2"/>
       <c r="F185" s="5"/>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" s="5"/>
       <c r="C186" s="5"/>
-      <c r="E186" s="12"/>
+      <c r="E186" s="2"/>
       <c r="F186" s="5"/>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187" s="5"/>
       <c r="C187" s="5"/>
-      <c r="E187" s="12"/>
+      <c r="E187" s="2"/>
       <c r="F187" s="5"/>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" s="5"/>
       <c r="C188" s="5"/>
-      <c r="E188" s="12"/>
+      <c r="E188" s="2"/>
       <c r="F188" s="5"/>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" s="5"/>
       <c r="C189" s="5"/>
-      <c r="E189" s="12"/>
+      <c r="E189" s="2"/>
       <c r="F189" s="5"/>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" s="5"/>
       <c r="C190" s="5"/>
-      <c r="E190" s="12"/>
+      <c r="E190" s="2"/>
       <c r="F190" s="5"/>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" s="5"/>
       <c r="C191" s="5"/>
-      <c r="E191" s="12"/>
+      <c r="E191" s="2"/>
       <c r="F191" s="5"/>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" s="5"/>
       <c r="C192" s="5"/>
-      <c r="E192" s="12"/>
+      <c r="E192" s="2"/>
       <c r="F192" s="5"/>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" s="5"/>
       <c r="C193" s="5"/>
-      <c r="E193" s="12"/>
+      <c r="E193" s="2"/>
       <c r="F193" s="5"/>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194" s="5"/>
       <c r="C194" s="5"/>
-      <c r="E194" s="12"/>
+      <c r="E194" s="2"/>
       <c r="F194" s="5"/>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195" s="5"/>
       <c r="C195" s="5"/>
-      <c r="E195" s="12"/>
+      <c r="E195" s="2"/>
       <c r="F195" s="5"/>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196" s="5"/>
       <c r="C196" s="5"/>
-      <c r="E196" s="12"/>
+      <c r="E196" s="2"/>
       <c r="F196" s="5"/>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197" s="5"/>
       <c r="C197" s="5"/>
-      <c r="E197" s="12"/>
+      <c r="E197" s="2"/>
       <c r="F197" s="5"/>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198" s="5"/>
       <c r="C198" s="5"/>
-      <c r="E198" s="12"/>
+      <c r="E198" s="2"/>
       <c r="F198" s="5"/>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199" s="5"/>
       <c r="C199" s="5"/>
-      <c r="E199" s="12"/>
+      <c r="E199" s="2"/>
       <c r="F199" s="5"/>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A200" s="5"/>
       <c r="C200" s="5"/>
-      <c r="E200" s="12"/>
+      <c r="E200" s="2"/>
       <c r="F200" s="5"/>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201" s="5"/>
       <c r="C201" s="5"/>
-      <c r="E201" s="12"/>
+      <c r="E201" s="2"/>
       <c r="F201" s="5"/>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202" s="5"/>
       <c r="C202" s="5"/>
-      <c r="E202" s="12"/>
+      <c r="E202" s="2"/>
       <c r="F202" s="5"/>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203" s="5"/>
       <c r="C203" s="5"/>
-      <c r="E203" s="12"/>
+      <c r="E203" s="2"/>
       <c r="F203" s="5"/>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204" s="5"/>
       <c r="C204" s="5"/>
-      <c r="E204" s="12"/>
+      <c r="E204" s="2"/>
       <c r="F204" s="5"/>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205" s="5"/>
       <c r="C205" s="5"/>
-      <c r="E205" s="12"/>
+      <c r="E205" s="2"/>
       <c r="F205" s="5"/>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206" s="5"/>
       <c r="C206" s="5"/>
-      <c r="E206" s="12"/>
+      <c r="E206" s="2"/>
       <c r="F206" s="5"/>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A207" s="5"/>
       <c r="C207" s="5"/>
-      <c r="E207" s="12"/>
+      <c r="E207" s="2"/>
       <c r="F207" s="5"/>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A208" s="5"/>
       <c r="C208" s="5"/>
-      <c r="E208" s="12"/>
+      <c r="E208" s="2"/>
       <c r="F208" s="5"/>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209" s="5"/>
       <c r="C209" s="5"/>
-      <c r="E209" s="12"/>
+      <c r="E209" s="2"/>
       <c r="F209" s="5"/>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210" s="5"/>
       <c r="C210" s="5"/>
-      <c r="E210" s="12"/>
+      <c r="E210" s="2"/>
       <c r="F210" s="5"/>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" s="5"/>
       <c r="C211" s="5"/>
-      <c r="E211" s="12"/>
+      <c r="E211" s="2"/>
       <c r="F211" s="5"/>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212" s="5"/>
       <c r="C212" s="5"/>
-      <c r="E212" s="12"/>
+      <c r="E212" s="2"/>
       <c r="F212" s="5"/>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" s="5"/>
       <c r="C213" s="5"/>
-      <c r="E213" s="12"/>
+      <c r="E213" s="2"/>
       <c r="F213" s="5"/>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" s="5"/>
       <c r="C214" s="5"/>
-      <c r="E214" s="12"/>
+      <c r="E214" s="2"/>
       <c r="F214" s="5"/>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" s="5"/>
       <c r="C215" s="5"/>
-      <c r="E215" s="12"/>
+      <c r="E215" s="2"/>
       <c r="F215" s="5"/>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216" s="5"/>
       <c r="B216" s="11"/>
       <c r="C216" s="5"/>
-      <c r="E216" s="12"/>
+      <c r="E216" s="2"/>
       <c r="F216" s="5"/>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217" s="5"/>
       <c r="C217" s="5"/>
-      <c r="E217" s="12"/>
+      <c r="E217" s="2"/>
       <c r="F217" s="5"/>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218" s="5"/>
       <c r="B218" s="11"/>
       <c r="C218" s="5"/>
-      <c r="E218" s="12"/>
+      <c r="E218" s="2"/>
       <c r="F218" s="5"/>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219" s="5"/>
       <c r="C219" s="5"/>
-      <c r="E219" s="12"/>
+      <c r="E219" s="2"/>
       <c r="F219" s="5"/>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/prix.xlsx
+++ b/prix/prix.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\site-internet\platres-et-enduits\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\platres-et-enduits\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36A36D4D-891B-49DF-9424-0B93C11DDE61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{335945C3-F9CD-411A-967A-7C2007BD8E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="431">
   <si>
     <t>path</t>
   </si>
@@ -1188,9 +1188,6 @@
     <t>61119210</t>
   </si>
   <si>
-    <t>platress+B2:B26e inox 280x130mm</t>
-  </si>
-  <si>
     <t>Platresse  hollande dentée inox 33433440</t>
   </si>
   <si>
@@ -1282,6 +1279,75 @@
   </si>
   <si>
     <t>Couteau à enduire 600mm x 0.3mm</t>
+  </si>
+  <si>
+    <t>galerie/palette-de-joint-droit-inox-230-PL090400.png</t>
+  </si>
+  <si>
+    <t>galerie/palette-de-joint-droite-PL252132.png</t>
+  </si>
+  <si>
+    <t>galerie/palette-de-platrier-alu-DS36950.png</t>
+  </si>
+  <si>
+    <t>galerie/platresse-a-chape-cp400262.png</t>
+  </si>
+  <si>
+    <t>galerie/platresse-acier-pointue-110x400-CP400040.png</t>
+  </si>
+  <si>
+    <t>galerie/platresse-coins-arrondis-406x100-CP5211150.png</t>
+  </si>
+  <si>
+    <t>galerie/platresse-inox-0.33-35x11-ds79015.png</t>
+  </si>
+  <si>
+    <t>galerie/platresse-inox-0.3mm-ds79000.png</t>
+  </si>
+  <si>
+    <t>galerie/platresse-inox-120x305-arrondie-0.65-DS704888.png</t>
+  </si>
+  <si>
+    <t>galerie/platresse-inox-260mm-cp217426.png</t>
+  </si>
+  <si>
+    <t>galerie/platresse-inox-280-dents-6x6mm-SO100606.png</t>
+  </si>
+  <si>
+    <t>galerie/platresse-inox-280.png</t>
+  </si>
+  <si>
+    <t>galerie/platresse-inox-280mm-dents-10x10-SO101010.png</t>
+  </si>
+  <si>
+    <t>galerie/platresse-inox-280mm-dents-8x8mm-SO100808.png</t>
+  </si>
+  <si>
+    <t>platress inox 280x130mm</t>
+  </si>
+  <si>
+    <t>galerie/platresse-inox-280x130mm-CP5204528.png</t>
+  </si>
+  <si>
+    <t>galerie/platresse-inox-dentee-12x12-SO101212.png</t>
+  </si>
+  <si>
+    <t>galerie/taloche-frottoir-blanc-120x250-PL266002.png</t>
+  </si>
+  <si>
+    <t>galerie/taloche-gratton-14x24cm-RM321200.png</t>
+  </si>
+  <si>
+    <t>galerie/taloche-plastique-14x8cm-PL237141.png</t>
+  </si>
+  <si>
+    <t>galerie/taloche-point-polyst-27x18-PL237271.png</t>
+  </si>
+  <si>
+    <t>galerie/taloche-point-polyst-noir-27x18-PL236270.png</t>
+  </si>
+  <si>
+    <t>galerie/platresse-acier-280-cp220028.png</t>
   </si>
 </sst>
 </file>
@@ -1336,10 +1402,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FFCE9178"/>
-      <name val="Consolas"/>
-      <family val="3"/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="11">
@@ -1417,7 +1483,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1475,13 +1541,31 @@
     <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1822,7 +1906,7 @@
   <dimension ref="A1:G448"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40.109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="51.6640625" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="52.21875" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.6640625" style="3" bestFit="1" customWidth="1"/>
@@ -3057,7 +3141,7 @@
       <c r="D63" s="3">
         <v>23.900000000000002</v>
       </c>
-      <c r="E63" s="22" t="s">
+      <c r="E63" s="21" t="s">
         <v>135</v>
       </c>
       <c r="F63" s="5">
@@ -3077,7 +3161,7 @@
       <c r="D64" s="3">
         <v>10.9</v>
       </c>
-      <c r="E64" s="22" t="s">
+      <c r="E64" s="21" t="s">
         <v>136</v>
       </c>
       <c r="F64" s="5">
@@ -3097,7 +3181,7 @@
       <c r="D65" s="3">
         <v>12.06</v>
       </c>
-      <c r="E65" s="22" t="s">
+      <c r="E65" s="21" t="s">
         <v>137</v>
       </c>
       <c r="F65" s="5">
@@ -3117,7 +3201,7 @@
       <c r="D66" s="3">
         <v>1.78</v>
       </c>
-      <c r="E66" s="22" t="s">
+      <c r="E66" s="21" t="s">
         <v>138</v>
       </c>
       <c r="F66" s="5">
@@ -3137,7 +3221,7 @@
       <c r="D67" s="3">
         <v>5.48</v>
       </c>
-      <c r="E67" s="22" t="s">
+      <c r="E67" s="21" t="s">
         <v>139</v>
       </c>
       <c r="F67" s="5">
@@ -3155,7 +3239,7 @@
       <c r="D68" s="3">
         <v>5</v>
       </c>
-      <c r="E68" s="22" t="s">
+      <c r="E68" s="21" t="s">
         <v>140</v>
       </c>
       <c r="F68" s="5">
@@ -3175,7 +3259,7 @@
       <c r="D69" s="3">
         <v>5.49</v>
       </c>
-      <c r="E69" s="22" t="s">
+      <c r="E69" s="21" t="s">
         <v>141</v>
       </c>
       <c r="F69" s="5">
@@ -3193,7 +3277,7 @@
       <c r="D70" s="3">
         <v>19.41</v>
       </c>
-      <c r="E70" s="22" t="s">
+      <c r="E70" s="21" t="s">
         <v>142</v>
       </c>
       <c r="F70" s="5">
@@ -3213,7 +3297,7 @@
       <c r="D71" s="3">
         <v>25.8</v>
       </c>
-      <c r="E71" s="23" t="s">
+      <c r="E71" s="22" t="s">
         <v>151</v>
       </c>
       <c r="F71" s="5">
@@ -3234,7 +3318,7 @@
       <c r="D72" s="3">
         <v>27.3</v>
       </c>
-      <c r="E72" s="23" t="s">
+      <c r="E72" s="22" t="s">
         <v>152</v>
       </c>
       <c r="F72" s="5">
@@ -3254,7 +3338,7 @@
       <c r="D73" s="3">
         <v>40.119999999999997</v>
       </c>
-      <c r="E73" s="23" t="s">
+      <c r="E73" s="22" t="s">
         <v>153</v>
       </c>
       <c r="F73" s="5">
@@ -3274,7 +3358,7 @@
       <c r="D74" s="3">
         <v>16.170000000000002</v>
       </c>
-      <c r="E74" s="23" t="s">
+      <c r="E74" s="22" t="s">
         <v>154</v>
       </c>
       <c r="F74" s="5">
@@ -3294,7 +3378,7 @@
       <c r="D75" s="3">
         <v>22.05</v>
       </c>
-      <c r="E75" s="23" t="s">
+      <c r="E75" s="22" t="s">
         <v>155</v>
       </c>
       <c r="F75" s="5">
@@ -3314,7 +3398,7 @@
       <c r="D76" s="3">
         <v>25.810000000000002</v>
       </c>
-      <c r="E76" s="23" t="s">
+      <c r="E76" s="22" t="s">
         <v>156</v>
       </c>
       <c r="F76" s="5">
@@ -3334,7 +3418,7 @@
       <c r="D77" s="3">
         <v>13.07</v>
       </c>
-      <c r="E77" s="23" t="s">
+      <c r="E77" s="22" t="s">
         <v>157</v>
       </c>
       <c r="F77" s="5">
@@ -3354,7 +3438,7 @@
       <c r="D78" s="3">
         <v>3.15</v>
       </c>
-      <c r="E78" s="23" t="s">
+      <c r="E78" s="22" t="s">
         <v>158</v>
       </c>
       <c r="F78" s="5">
@@ -3374,7 +3458,7 @@
       <c r="D79" s="3">
         <v>16.63</v>
       </c>
-      <c r="E79" s="23" t="s">
+      <c r="E79" s="22" t="s">
         <v>159</v>
       </c>
       <c r="F79" s="5">
@@ -3394,7 +3478,7 @@
       <c r="D80" s="3">
         <v>6.17</v>
       </c>
-      <c r="E80" s="23" t="s">
+      <c r="E80" s="22" t="s">
         <v>160</v>
       </c>
       <c r="F80" s="5">
@@ -3414,7 +3498,7 @@
       <c r="D81" s="3">
         <v>15.73</v>
       </c>
-      <c r="E81" s="23" t="s">
+      <c r="E81" s="22" t="s">
         <v>161</v>
       </c>
       <c r="F81" s="5">
@@ -3434,7 +3518,7 @@
       <c r="D82" s="3">
         <v>3.92</v>
       </c>
-      <c r="E82" s="23" t="s">
+      <c r="E82" s="22" t="s">
         <v>162</v>
       </c>
       <c r="F82" s="5">
@@ -3454,7 +3538,7 @@
       <c r="D83" s="3">
         <v>21.95</v>
       </c>
-      <c r="E83" s="23" t="s">
+      <c r="E83" s="22" t="s">
         <v>163</v>
       </c>
       <c r="F83" s="5">
@@ -3474,7 +3558,7 @@
       <c r="D84" s="3">
         <v>4.99</v>
       </c>
-      <c r="E84" s="23" t="s">
+      <c r="E84" s="22" t="s">
         <v>164</v>
       </c>
       <c r="F84" s="5">
@@ -3494,7 +3578,7 @@
       <c r="D85" s="3">
         <v>7.36</v>
       </c>
-      <c r="E85" s="23" t="s">
+      <c r="E85" s="22" t="s">
         <v>165</v>
       </c>
       <c r="F85" s="5">
@@ -3514,7 +3598,7 @@
       <c r="D86" s="3">
         <v>30.52</v>
       </c>
-      <c r="E86" s="23" t="s">
+      <c r="E86" s="22" t="s">
         <v>166</v>
       </c>
       <c r="F86" s="5">
@@ -3534,7 +3618,7 @@
       <c r="D87" s="3">
         <v>6.05</v>
       </c>
-      <c r="E87" s="23" t="s">
+      <c r="E87" s="22" t="s">
         <v>167</v>
       </c>
       <c r="F87" s="5">
@@ -3554,7 +3638,7 @@
       <c r="D88" s="3">
         <v>4.67</v>
       </c>
-      <c r="E88" s="23" t="s">
+      <c r="E88" s="22" t="s">
         <v>168</v>
       </c>
       <c r="F88" s="5">
@@ -3574,7 +3658,7 @@
       <c r="D89" s="3">
         <v>15.58</v>
       </c>
-      <c r="E89" s="23" t="s">
+      <c r="E89" s="22" t="s">
         <v>169</v>
       </c>
       <c r="F89" s="5">
@@ -3594,7 +3678,7 @@
       <c r="D90" s="3">
         <v>18.63</v>
       </c>
-      <c r="E90" s="23" t="s">
+      <c r="E90" s="22" t="s">
         <v>170</v>
       </c>
       <c r="F90" s="5">
@@ -3614,7 +3698,7 @@
       <c r="D91" s="3">
         <v>10.99</v>
       </c>
-      <c r="E91" s="23" t="s">
+      <c r="E91" s="22" t="s">
         <v>171</v>
       </c>
       <c r="F91" s="5">
@@ -3634,7 +3718,7 @@
       <c r="D92" s="3">
         <v>22.97</v>
       </c>
-      <c r="E92" s="23" t="s">
+      <c r="E92" s="22" t="s">
         <v>172</v>
       </c>
       <c r="F92" s="5">
@@ -3654,7 +3738,7 @@
       <c r="D93" s="3">
         <v>18.150000000000002</v>
       </c>
-      <c r="E93" s="23" t="s">
+      <c r="E93" s="22" t="s">
         <v>173</v>
       </c>
       <c r="F93" s="5">
@@ -3674,7 +3758,7 @@
       <c r="D94" s="3">
         <v>12.83</v>
       </c>
-      <c r="E94" s="23" t="s">
+      <c r="E94" s="22" t="s">
         <v>174</v>
       </c>
       <c r="F94" s="5">
@@ -3694,7 +3778,7 @@
       <c r="D95" s="3">
         <v>42.25</v>
       </c>
-      <c r="E95" s="23" t="s">
+      <c r="E95" s="22" t="s">
         <v>175</v>
       </c>
       <c r="F95" s="5">
@@ -3714,7 +3798,7 @@
       <c r="D96" s="3">
         <v>17.38</v>
       </c>
-      <c r="E96" s="23" t="s">
+      <c r="E96" s="22" t="s">
         <v>176</v>
       </c>
       <c r="F96" s="5">
@@ -3734,7 +3818,7 @@
       <c r="D97" s="3">
         <v>27.18</v>
       </c>
-      <c r="E97" s="23" t="s">
+      <c r="E97" s="22" t="s">
         <v>177</v>
       </c>
       <c r="F97" s="5">
@@ -3754,7 +3838,7 @@
       <c r="D98" s="3">
         <v>34.51</v>
       </c>
-      <c r="E98" s="23" t="s">
+      <c r="E98" s="22" t="s">
         <v>178</v>
       </c>
       <c r="F98" s="5">
@@ -3774,7 +3858,7 @@
       <c r="D99" s="3">
         <v>42.57</v>
       </c>
-      <c r="E99" s="23" t="s">
+      <c r="E99" s="22" t="s">
         <v>179</v>
       </c>
       <c r="F99" s="5">
@@ -3794,7 +3878,7 @@
       <c r="D100" s="3">
         <v>21.68</v>
       </c>
-      <c r="E100" s="23" t="s">
+      <c r="E100" s="22" t="s">
         <v>180</v>
       </c>
       <c r="F100" s="5">
@@ -3814,7 +3898,7 @@
       <c r="D101" s="3">
         <v>24.78</v>
       </c>
-      <c r="E101" s="23" t="s">
+      <c r="E101" s="22" t="s">
         <v>181</v>
       </c>
       <c r="F101" s="5">
@@ -3834,7 +3918,7 @@
       <c r="D102" s="3">
         <v>16.63</v>
       </c>
-      <c r="E102" s="23" t="s">
+      <c r="E102" s="22" t="s">
         <v>182</v>
       </c>
       <c r="F102" s="5">
@@ -3854,7 +3938,7 @@
       <c r="D103" s="3">
         <v>19.14</v>
       </c>
-      <c r="E103" s="23" t="s">
+      <c r="E103" s="22" t="s">
         <v>183</v>
       </c>
       <c r="F103" s="5">
@@ -3874,7 +3958,7 @@
       <c r="D104" s="3">
         <v>33.01</v>
       </c>
-      <c r="E104" s="23" t="s">
+      <c r="E104" s="22" t="s">
         <v>184</v>
       </c>
       <c r="F104" s="5">
@@ -3962,7 +4046,9 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="5"/>
+      <c r="A109" s="5" t="s">
+        <v>419</v>
+      </c>
       <c r="B109" s="2" t="s">
         <v>338</v>
       </c>
@@ -3978,7 +4064,9 @@
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="21"/>
+      <c r="A110" s="23" t="s">
+        <v>417</v>
+      </c>
       <c r="B110" s="2" t="s">
         <v>339</v>
       </c>
@@ -3994,7 +4082,9 @@
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="5"/>
+      <c r="A111" s="5" t="s">
+        <v>411</v>
+      </c>
       <c r="B111" s="2" t="s">
         <v>340</v>
       </c>
@@ -4010,7 +4100,9 @@
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="5"/>
+      <c r="A112" s="5" t="s">
+        <v>415</v>
+      </c>
       <c r="B112" s="2" t="s">
         <v>341</v>
       </c>
@@ -4026,7 +4118,9 @@
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="5"/>
+      <c r="A113" s="5" t="s">
+        <v>414</v>
+      </c>
       <c r="B113" s="2" t="s">
         <v>342</v>
       </c>
@@ -4042,7 +4136,9 @@
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="5"/>
+      <c r="A114" s="5" t="s">
+        <v>430</v>
+      </c>
       <c r="B114" s="2" t="s">
         <v>343</v>
       </c>
@@ -4058,7 +4154,9 @@
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="5"/>
+      <c r="A115" s="5" t="s">
+        <v>418</v>
+      </c>
       <c r="B115" s="2" t="s">
         <v>344</v>
       </c>
@@ -4074,7 +4172,9 @@
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="5"/>
+      <c r="A116" s="5" t="s">
+        <v>421</v>
+      </c>
       <c r="B116" s="2" t="s">
         <v>345</v>
       </c>
@@ -4090,7 +4190,9 @@
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="5"/>
+      <c r="A117" s="5" t="s">
+        <v>420</v>
+      </c>
       <c r="B117" s="2" t="s">
         <v>346</v>
       </c>
@@ -4106,23 +4208,25 @@
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="5"/>
-      <c r="B118" s="2" t="s">
+      <c r="A118" s="12"/>
+      <c r="B118" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="C118" s="5"/>
-      <c r="D118" s="3">
+      <c r="C118" s="12"/>
+      <c r="D118" s="13">
         <v>46.160000000000004</v>
       </c>
-      <c r="E118" s="2" t="s">
+      <c r="E118" s="11" t="s">
         <v>336</v>
       </c>
-      <c r="F118" s="5">
+      <c r="F118" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="5"/>
+      <c r="A119" s="5" t="s">
+        <v>416</v>
+      </c>
       <c r="B119" s="2" t="s">
         <v>348</v>
       </c>
@@ -4138,9 +4242,11 @@
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="5"/>
+      <c r="A120" s="5" t="s">
+        <v>423</v>
+      </c>
       <c r="B120" s="2" t="s">
-        <v>377</v>
+        <v>422</v>
       </c>
       <c r="C120" s="5"/>
       <c r="D120" s="3">
@@ -4154,57 +4260,59 @@
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="5"/>
-      <c r="B121" s="2" t="s">
+      <c r="A121" s="12"/>
+      <c r="B121" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="C121" s="12"/>
+      <c r="D121" s="13">
+        <v>13.73</v>
+      </c>
+      <c r="E121" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="F121" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" s="12"/>
+      <c r="B122" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="C121" s="5"/>
-      <c r="D121" s="3">
-        <v>13.73</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="F121" s="5">
+      <c r="C122" s="12"/>
+      <c r="D122" s="13">
+        <v>13.74</v>
+      </c>
+      <c r="E122" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="F122" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="5"/>
-      <c r="B122" s="2" t="s">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123" s="12"/>
+      <c r="B123" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="C122" s="5"/>
-      <c r="D122" s="3">
-        <v>13.74</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="F122" s="5">
+      <c r="C123" s="12"/>
+      <c r="D123" s="13">
+        <v>16.670000000000002</v>
+      </c>
+      <c r="E123" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="F123" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="5"/>
-      <c r="B123" s="2" t="s">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="B124" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="C123" s="5"/>
-      <c r="D123" s="3">
-        <v>16.670000000000002</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="F123" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="5"/>
-      <c r="B124" s="2" t="s">
-        <v>381</v>
       </c>
       <c r="C124" s="5"/>
       <c r="D124" s="3">
@@ -4218,9 +4326,11 @@
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="5"/>
+      <c r="A125" s="5" t="s">
+        <v>424</v>
+      </c>
       <c r="B125" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C125" s="5"/>
       <c r="D125" s="3">
@@ -4234,9 +4344,11 @@
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="5"/>
+      <c r="A126" s="5" t="s">
+        <v>412</v>
+      </c>
       <c r="B126" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C126" s="5"/>
       <c r="D126" s="3">
@@ -4250,25 +4362,27 @@
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="5"/>
-      <c r="B127" s="2" t="s">
+      <c r="A127" s="27"/>
+      <c r="B127" s="28" t="s">
+        <v>383</v>
+      </c>
+      <c r="C127" s="27"/>
+      <c r="D127" s="29">
+        <v>48.35</v>
+      </c>
+      <c r="E127" s="28" t="s">
+        <v>356</v>
+      </c>
+      <c r="F127" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="B128" s="2" t="s">
         <v>384</v>
-      </c>
-      <c r="C127" s="5"/>
-      <c r="D127" s="3">
-        <v>48.35</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="F127" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="5"/>
-      <c r="B128" s="2" t="s">
-        <v>385</v>
       </c>
       <c r="C128" s="5"/>
       <c r="D128" s="3">
@@ -4282,9 +4396,11 @@
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="5"/>
+      <c r="A129" s="5" t="s">
+        <v>427</v>
+      </c>
       <c r="B129" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C129" s="5"/>
       <c r="D129" s="3">
@@ -4298,9 +4414,11 @@
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="5"/>
+      <c r="A130" s="5" t="s">
+        <v>426</v>
+      </c>
       <c r="B130" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C130" s="5"/>
       <c r="D130" s="3">
@@ -4314,41 +4432,45 @@
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="5"/>
-      <c r="B131" s="2" t="s">
+      <c r="A131" s="24" t="s">
+        <v>425</v>
+      </c>
+      <c r="B131" s="25" t="s">
+        <v>387</v>
+      </c>
+      <c r="C131" s="24"/>
+      <c r="D131" s="26">
+        <v>19.490000000000002</v>
+      </c>
+      <c r="E131" s="25" t="s">
+        <v>360</v>
+      </c>
+      <c r="F131" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132" s="12"/>
+      <c r="B132" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="C131" s="5"/>
-      <c r="D131" s="3">
-        <v>19.490000000000002</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="F131" s="5">
+      <c r="C132" s="12"/>
+      <c r="D132" s="13">
+        <v>14.96</v>
+      </c>
+      <c r="E132" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="F132" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="5"/>
-      <c r="B132" s="2" t="s">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="B133" s="2" t="s">
         <v>389</v>
-      </c>
-      <c r="C132" s="5"/>
-      <c r="D132" s="3">
-        <v>14.96</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="F132" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="5"/>
-      <c r="B133" s="2" t="s">
-        <v>390</v>
       </c>
       <c r="C133" s="5"/>
       <c r="D133" s="3">
@@ -4362,25 +4484,27 @@
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="5"/>
-      <c r="B134" s="2" t="s">
+      <c r="A134" s="12"/>
+      <c r="B134" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="C134" s="12"/>
+      <c r="D134" s="13">
+        <v>21.6</v>
+      </c>
+      <c r="E134" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="F134" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="B135" s="2" t="s">
         <v>391</v>
-      </c>
-      <c r="C134" s="5"/>
-      <c r="D134" s="3">
-        <v>21.6</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="F134" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="5"/>
-      <c r="B135" s="2" t="s">
-        <v>392</v>
       </c>
       <c r="C135" s="5"/>
       <c r="D135" s="3">
@@ -4394,9 +4518,11 @@
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="5"/>
+      <c r="A136" s="5" t="s">
+        <v>428</v>
+      </c>
       <c r="B136" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C136" s="5"/>
       <c r="D136" s="3">
@@ -4410,9 +4536,11 @@
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="5"/>
+      <c r="A137" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="B137" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C137" s="5"/>
       <c r="D137" s="3">
@@ -4426,41 +4554,41 @@
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="5"/>
-      <c r="B138" s="2" t="s">
+      <c r="A138" s="12"/>
+      <c r="B138" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="C138" s="12"/>
+      <c r="D138" s="13">
+        <v>4.59</v>
+      </c>
+      <c r="E138" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="F138" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139" s="12"/>
+      <c r="B139" s="11" t="s">
         <v>395</v>
       </c>
-      <c r="C138" s="5"/>
-      <c r="D138" s="3">
-        <v>4.59</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="F138" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="5"/>
-      <c r="B139" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="C139" s="5"/>
-      <c r="D139" s="3">
+      <c r="C139" s="12"/>
+      <c r="D139" s="13">
         <v>12.4</v>
       </c>
-      <c r="E139" s="2" t="s">
+      <c r="E139" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="F139" s="5">
+      <c r="F139" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="5"/>
       <c r="B140" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C140" s="5"/>
       <c r="D140" s="3">
@@ -4476,7 +4604,7 @@
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="5"/>
       <c r="B141" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C141" s="5"/>
       <c r="D141" s="3">
@@ -4490,25 +4618,25 @@
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="5"/>
-      <c r="B142" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="C142" s="5"/>
-      <c r="D142" s="3">
+      <c r="A142" s="12"/>
+      <c r="B142" s="11" t="s">
+        <v>398</v>
+      </c>
+      <c r="C142" s="12"/>
+      <c r="D142" s="13">
         <v>11.69</v>
       </c>
-      <c r="E142" s="2" t="s">
+      <c r="E142" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="F142" s="5">
+      <c r="F142" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="5"/>
       <c r="B143" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C143" s="5"/>
       <c r="D143" s="3">
@@ -4524,7 +4652,7 @@
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="5"/>
       <c r="B144" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C144" s="5"/>
       <c r="D144" s="3">
@@ -4538,25 +4666,25 @@
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145" s="5"/>
-      <c r="B145" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="C145" s="5"/>
-      <c r="D145" s="3">
+      <c r="A145" s="12"/>
+      <c r="B145" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="C145" s="12"/>
+      <c r="D145" s="13">
         <v>9.8000000000000007</v>
       </c>
-      <c r="E145" s="2" t="s">
+      <c r="E145" s="11" t="s">
         <v>374</v>
       </c>
-      <c r="F145" s="5">
+      <c r="F145" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="5"/>
       <c r="B146" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C146" s="5"/>
       <c r="D146" s="3">
@@ -4570,32 +4698,32 @@
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147" s="5"/>
-      <c r="B147" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="C147" s="5"/>
-      <c r="D147" s="3">
+      <c r="A147" s="12"/>
+      <c r="B147" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="C147" s="12"/>
+      <c r="D147" s="13">
         <v>5</v>
       </c>
-      <c r="E147" s="2" t="s">
+      <c r="E147" s="11" t="s">
         <v>376</v>
       </c>
-      <c r="F147" s="5">
+      <c r="F147" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="5"/>
       <c r="B148" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C148" s="5"/>
       <c r="D148" s="3">
         <v>68.489999999999995</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F148" s="5">
         <v>2</v>
@@ -4604,14 +4732,14 @@
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="5"/>
       <c r="B149" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C149" s="5"/>
       <c r="D149" s="3">
         <v>53.36</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F149" s="5">
         <v>2</v>

--- a/prix/prix.xlsx
+++ b/prix/prix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\platres-et-enduits\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{335945C3-F9CD-411A-967A-7C2007BD8E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8DDE5F5-01CD-4920-9051-256355D6AAB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="438">
   <si>
     <t>path</t>
   </si>
@@ -1348,6 +1348,27 @@
   </si>
   <si>
     <t>galerie/platresse-acier-280-cp220028.png</t>
+  </si>
+  <si>
+    <t>galerie/couteau-a-enduire-600mmx0.3mm-mb541060.png</t>
+  </si>
+  <si>
+    <t>galerie/couteau-a-enduire-800mmx0.3mm-mb541080.png</t>
+  </si>
+  <si>
+    <t>galerie/frottoir-en-polyurethane-pl905280.png</t>
+  </si>
+  <si>
+    <t>galerie/platoir-plast-semelle-hydro-eponge-pl279028.png</t>
+  </si>
+  <si>
+    <t>galerie/taloche-angulaire-eponge-orange-pl265000.png</t>
+  </si>
+  <si>
+    <t>galerie/taloche-eponge-noire-pl277128.png</t>
+  </si>
+  <si>
+    <t>galerie/taloche-eponge-orange-pl277328.png</t>
   </si>
 </sst>
 </file>
@@ -4586,7 +4607,9 @@
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="5"/>
+      <c r="A140" s="5" t="s">
+        <v>435</v>
+      </c>
       <c r="B140" s="2" t="s">
         <v>396</v>
       </c>
@@ -4602,7 +4625,9 @@
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="5"/>
+      <c r="A141" s="5" t="s">
+        <v>437</v>
+      </c>
       <c r="B141" s="2" t="s">
         <v>397</v>
       </c>
@@ -4634,7 +4659,9 @@
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="5"/>
+      <c r="A143" s="5" t="s">
+        <v>436</v>
+      </c>
       <c r="B143" s="2" t="s">
         <v>399</v>
       </c>
@@ -4650,7 +4677,9 @@
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="5"/>
+      <c r="A144" s="5" t="s">
+        <v>433</v>
+      </c>
       <c r="B144" s="2" t="s">
         <v>400</v>
       </c>
@@ -4682,7 +4711,9 @@
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146" s="5"/>
+      <c r="A146" s="5" t="s">
+        <v>434</v>
+      </c>
       <c r="B146" s="2" t="s">
         <v>402</v>
       </c>
@@ -4714,7 +4745,9 @@
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" s="5"/>
+      <c r="A148" s="5" t="s">
+        <v>432</v>
+      </c>
       <c r="B148" s="2" t="s">
         <v>406</v>
       </c>
@@ -4730,7 +4763,9 @@
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149" s="5"/>
+      <c r="A149" s="5" t="s">
+        <v>431</v>
+      </c>
       <c r="B149" s="2" t="s">
         <v>407</v>
       </c>

--- a/prix/prix.xlsx
+++ b/prix/prix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\platres-et-enduits\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8DDE5F5-01CD-4920-9051-256355D6AAB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F12FC0-6119-493D-B95A-7B9B153E4A18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
+    <workbookView xWindow="1284" yWindow="312" windowWidth="19116" windowHeight="10884" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="471">
   <si>
     <t>path</t>
   </si>
@@ -1369,6 +1369,105 @@
   </si>
   <si>
     <t>galerie/taloche-eponge-orange-pl277328.png</t>
+  </si>
+  <si>
+    <t>71020100</t>
+  </si>
+  <si>
+    <t>71020111</t>
+  </si>
+  <si>
+    <t>71020112</t>
+  </si>
+  <si>
+    <t>71020113</t>
+  </si>
+  <si>
+    <t>71020114</t>
+  </si>
+  <si>
+    <t>71020140</t>
+  </si>
+  <si>
+    <t>71020150</t>
+  </si>
+  <si>
+    <t>71020153</t>
+  </si>
+  <si>
+    <t>71020154</t>
+  </si>
+  <si>
+    <t>71020155</t>
+  </si>
+  <si>
+    <t>71020156</t>
+  </si>
+  <si>
+    <t>71020157</t>
+  </si>
+  <si>
+    <t>71020158</t>
+  </si>
+  <si>
+    <t>71020159</t>
+  </si>
+  <si>
+    <t>71020160</t>
+  </si>
+  <si>
+    <t>Corniere fil tramé  3.05</t>
+  </si>
+  <si>
+    <t>Angle carré alu 2046 1.20m</t>
+  </si>
+  <si>
+    <t>Angle carré alu 2046 1.50m</t>
+  </si>
+  <si>
+    <t>Angle carré alu 2046 1.80m</t>
+  </si>
+  <si>
+    <t>Angle carré alu 2.00 m</t>
+  </si>
+  <si>
+    <t>Arrêt inox 2.50m -6mm</t>
+  </si>
+  <si>
+    <t>Cornière galva 25*25 pour plaque en 3m</t>
+  </si>
+  <si>
+    <t>Cornière galva de 150</t>
+  </si>
+  <si>
+    <t>Cornière galva de 180</t>
+  </si>
+  <si>
+    <t>Cornière galva de 200</t>
+  </si>
+  <si>
+    <t>Cornière galva de 220</t>
+  </si>
+  <si>
+    <t>Cornière galva de 250 27x27</t>
+  </si>
+  <si>
+    <t>Cornière galva de 260</t>
+  </si>
+  <si>
+    <t>Cornière galva de 280</t>
+  </si>
+  <si>
+    <t>Cornière galva de 300</t>
+  </si>
+  <si>
+    <t>pc</t>
+  </si>
+  <si>
+    <t>galerie/corniere-fil-trame.png</t>
+  </si>
+  <si>
+    <t>galerie/corniere-galva.png</t>
   </si>
 </sst>
 </file>
@@ -1429,7 +1528,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1490,6 +1589,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1504,7 +1609,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1588,6 +1693,24 @@
     </xf>
     <xf numFmtId="4" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4073,7 +4196,9 @@
       <c r="B109" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="C109" s="5"/>
+      <c r="C109" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D109" s="3">
         <v>10.89</v>
       </c>
@@ -4091,7 +4216,9 @@
       <c r="B110" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="C110" s="5"/>
+      <c r="C110" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D110" s="3">
         <v>20.63</v>
       </c>
@@ -4109,7 +4236,9 @@
       <c r="B111" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="C111" s="5"/>
+      <c r="C111" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D111" s="3">
         <v>35.6</v>
       </c>
@@ -4127,7 +4256,9 @@
       <c r="B112" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C112" s="5"/>
+      <c r="C112" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D112" s="3">
         <v>30.21</v>
       </c>
@@ -4145,7 +4276,9 @@
       <c r="B113" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="C113" s="5"/>
+      <c r="C113" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D113" s="3">
         <v>33.06</v>
       </c>
@@ -4163,7 +4296,9 @@
       <c r="B114" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="C114" s="5"/>
+      <c r="C114" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D114" s="3">
         <v>17.82</v>
       </c>
@@ -4181,7 +4316,9 @@
       <c r="B115" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="C115" s="5"/>
+      <c r="C115" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D115" s="3">
         <v>14.33</v>
       </c>
@@ -4199,7 +4336,9 @@
       <c r="B116" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="C116" s="5"/>
+      <c r="C116" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D116" s="3">
         <v>14.33</v>
       </c>
@@ -4217,7 +4356,9 @@
       <c r="B117" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C117" s="5"/>
+      <c r="C117" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D117" s="3">
         <v>14.33</v>
       </c>
@@ -4233,7 +4374,9 @@
       <c r="B118" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="C118" s="12"/>
+      <c r="C118" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D118" s="13">
         <v>46.160000000000004</v>
       </c>
@@ -4251,7 +4394,9 @@
       <c r="B119" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="C119" s="5"/>
+      <c r="C119" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D119" s="3">
         <v>61.71</v>
       </c>
@@ -4269,7 +4414,9 @@
       <c r="B120" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="C120" s="5"/>
+      <c r="C120" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D120" s="3">
         <v>15.6</v>
       </c>
@@ -4285,7 +4432,9 @@
       <c r="B121" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="C121" s="12"/>
+      <c r="C121" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D121" s="13">
         <v>13.73</v>
       </c>
@@ -4301,7 +4450,9 @@
       <c r="B122" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="C122" s="12"/>
+      <c r="C122" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D122" s="13">
         <v>13.74</v>
       </c>
@@ -4317,7 +4468,9 @@
       <c r="B123" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="C123" s="12"/>
+      <c r="C123" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D123" s="13">
         <v>16.670000000000002</v>
       </c>
@@ -4335,7 +4488,9 @@
       <c r="B124" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="C124" s="5"/>
+      <c r="C124" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D124" s="3">
         <v>24.490000000000002</v>
       </c>
@@ -4353,7 +4508,9 @@
       <c r="B125" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="C125" s="5"/>
+      <c r="C125" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D125" s="3">
         <v>14.31</v>
       </c>
@@ -4371,7 +4528,9 @@
       <c r="B126" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="C126" s="5"/>
+      <c r="C126" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D126" s="3">
         <v>21.54</v>
       </c>
@@ -4387,7 +4546,9 @@
       <c r="B127" s="28" t="s">
         <v>383</v>
       </c>
-      <c r="C127" s="27"/>
+      <c r="C127" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D127" s="29">
         <v>48.35</v>
       </c>
@@ -4405,7 +4566,9 @@
       <c r="B128" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="C128" s="5"/>
+      <c r="C128" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D128" s="3">
         <v>38.24</v>
       </c>
@@ -4423,7 +4586,9 @@
       <c r="B129" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="C129" s="5"/>
+      <c r="C129" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D129" s="3">
         <v>2.5300000000000002</v>
       </c>
@@ -4441,7 +4606,9 @@
       <c r="B130" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="C130" s="5"/>
+      <c r="C130" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D130" s="3">
         <v>16.7</v>
       </c>
@@ -4459,7 +4626,9 @@
       <c r="B131" s="25" t="s">
         <v>387</v>
       </c>
-      <c r="C131" s="24"/>
+      <c r="C131" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D131" s="26">
         <v>19.490000000000002</v>
       </c>
@@ -4475,7 +4644,9 @@
       <c r="B132" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="C132" s="12"/>
+      <c r="C132" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D132" s="13">
         <v>14.96</v>
       </c>
@@ -4493,7 +4664,9 @@
       <c r="B133" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="C133" s="5"/>
+      <c r="C133" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D133" s="3">
         <v>36.78</v>
       </c>
@@ -4509,7 +4682,9 @@
       <c r="B134" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="C134" s="12"/>
+      <c r="C134" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D134" s="13">
         <v>21.6</v>
       </c>
@@ -4527,7 +4702,9 @@
       <c r="B135" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="C135" s="5"/>
+      <c r="C135" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D135" s="3">
         <v>8.24</v>
       </c>
@@ -4545,7 +4722,9 @@
       <c r="B136" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="C136" s="5"/>
+      <c r="C136" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D136" s="3">
         <v>3.7</v>
       </c>
@@ -4563,7 +4742,9 @@
       <c r="B137" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="C137" s="5"/>
+      <c r="C137" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D137" s="3">
         <v>3.42</v>
       </c>
@@ -4579,7 +4760,9 @@
       <c r="B138" s="11" t="s">
         <v>394</v>
       </c>
-      <c r="C138" s="12"/>
+      <c r="C138" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D138" s="13">
         <v>4.59</v>
       </c>
@@ -4595,7 +4778,9 @@
       <c r="B139" s="11" t="s">
         <v>395</v>
       </c>
-      <c r="C139" s="12"/>
+      <c r="C139" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D139" s="13">
         <v>12.4</v>
       </c>
@@ -4613,7 +4798,9 @@
       <c r="B140" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="C140" s="5"/>
+      <c r="C140" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D140" s="3">
         <v>10.16</v>
       </c>
@@ -4631,7 +4818,9 @@
       <c r="B141" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="C141" s="5"/>
+      <c r="C141" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D141" s="3">
         <v>9.15</v>
       </c>
@@ -4647,7 +4836,9 @@
       <c r="B142" s="11" t="s">
         <v>398</v>
       </c>
-      <c r="C142" s="12"/>
+      <c r="C142" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D142" s="13">
         <v>11.69</v>
       </c>
@@ -4665,7 +4856,9 @@
       <c r="B143" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="C143" s="5"/>
+      <c r="C143" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D143" s="3">
         <v>6.32</v>
       </c>
@@ -4683,7 +4876,9 @@
       <c r="B144" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="C144" s="5"/>
+      <c r="C144" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D144" s="3">
         <v>4.96</v>
       </c>
@@ -4699,7 +4894,9 @@
       <c r="B145" s="11" t="s">
         <v>401</v>
       </c>
-      <c r="C145" s="12"/>
+      <c r="C145" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D145" s="13">
         <v>9.8000000000000007</v>
       </c>
@@ -4717,7 +4914,9 @@
       <c r="B146" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="C146" s="5"/>
+      <c r="C146" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D146" s="3">
         <v>8.14</v>
       </c>
@@ -4733,7 +4932,9 @@
       <c r="B147" s="11" t="s">
         <v>403</v>
       </c>
-      <c r="C147" s="12"/>
+      <c r="C147" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D147" s="13">
         <v>5</v>
       </c>
@@ -4751,7 +4952,9 @@
       <c r="B148" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="C148" s="5"/>
+      <c r="C148" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D148" s="3">
         <v>68.489999999999995</v>
       </c>
@@ -4769,7 +4972,9 @@
       <c r="B149" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="C149" s="5"/>
+      <c r="C149" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="D149" s="3">
         <v>53.36</v>
       </c>
@@ -4781,107 +4986,292 @@
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A150" s="5"/>
-      <c r="B150" s="11"/>
-      <c r="C150" s="5"/>
-      <c r="D150" s="13"/>
-      <c r="E150" s="11"/>
-      <c r="F150" s="12"/>
+      <c r="A150" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="D150" s="33">
+        <v>6.3</v>
+      </c>
+      <c r="E150" s="30" t="s">
+        <v>438</v>
+      </c>
+      <c r="F150" s="31">
+        <v>158</v>
+      </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A151" s="5"/>
-      <c r="B151" s="11"/>
-      <c r="C151" s="5"/>
-      <c r="D151" s="13"/>
-      <c r="E151" s="11"/>
-      <c r="F151" s="12"/>
+      <c r="A151" s="12"/>
+      <c r="B151" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C151" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="D151" s="32">
+        <v>0.61</v>
+      </c>
+      <c r="E151" s="34" t="s">
+        <v>439</v>
+      </c>
+      <c r="F151" s="35">
+        <v>0</v>
+      </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A152" s="5"/>
-      <c r="C152" s="5"/>
-      <c r="E152" s="2"/>
-      <c r="F152" s="5"/>
+      <c r="A152" s="12"/>
+      <c r="B152" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="C152" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="D152" s="32">
+        <v>0.61</v>
+      </c>
+      <c r="E152" s="34" t="s">
+        <v>440</v>
+      </c>
+      <c r="F152" s="35">
+        <v>0</v>
+      </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A153" s="5"/>
-      <c r="C153" s="5"/>
-      <c r="E153" s="2"/>
-      <c r="F153" s="5"/>
+      <c r="A153" s="12"/>
+      <c r="B153" s="11" t="s">
+        <v>456</v>
+      </c>
+      <c r="C153" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="D153" s="32">
+        <v>0.61</v>
+      </c>
+      <c r="E153" s="34" t="s">
+        <v>441</v>
+      </c>
+      <c r="F153" s="35">
+        <v>0</v>
+      </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A154" s="5"/>
-      <c r="C154" s="5"/>
-      <c r="E154" s="2"/>
-      <c r="F154" s="5"/>
+      <c r="A154" s="12"/>
+      <c r="B154" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="C154" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="D154" s="32">
+        <v>0.61</v>
+      </c>
+      <c r="E154" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="F154" s="35">
+        <v>0</v>
+      </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A155" s="5"/>
-      <c r="C155" s="5"/>
-      <c r="E155" s="2"/>
-      <c r="F155" s="5"/>
+      <c r="A155" s="12"/>
+      <c r="B155" s="11" t="s">
+        <v>458</v>
+      </c>
+      <c r="C155" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="D155" s="32">
+        <v>7.9300000000000006</v>
+      </c>
+      <c r="E155" s="34" t="s">
+        <v>443</v>
+      </c>
+      <c r="F155" s="35">
+        <v>0</v>
+      </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A156" s="5"/>
-      <c r="B156" s="11"/>
-      <c r="C156" s="5"/>
-      <c r="D156" s="13"/>
-      <c r="E156" s="11"/>
-      <c r="F156" s="12"/>
+      <c r="A156" s="12"/>
+      <c r="B156" s="11" t="s">
+        <v>459</v>
+      </c>
+      <c r="C156" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="D156" s="32">
+        <v>3.35</v>
+      </c>
+      <c r="E156" s="34" t="s">
+        <v>444</v>
+      </c>
+      <c r="F156" s="35">
+        <v>0</v>
+      </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A157" s="5"/>
-      <c r="B157" s="11"/>
-      <c r="C157" s="5"/>
-      <c r="D157" s="13"/>
-      <c r="E157" s="11"/>
-      <c r="F157" s="12"/>
+      <c r="A157" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="D157" s="33">
+        <v>2</v>
+      </c>
+      <c r="E157" s="30" t="s">
+        <v>445</v>
+      </c>
+      <c r="F157" s="31">
+        <v>119</v>
+      </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A158" s="5"/>
-      <c r="B158" s="11"/>
-      <c r="C158" s="5"/>
-      <c r="D158" s="13"/>
-      <c r="E158" s="11"/>
-      <c r="F158" s="12"/>
+      <c r="A158" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="D158" s="33">
+        <v>1.96</v>
+      </c>
+      <c r="E158" s="30" t="s">
+        <v>446</v>
+      </c>
+      <c r="F158" s="31">
+        <v>139</v>
+      </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A159" s="5"/>
-      <c r="C159" s="5"/>
-      <c r="E159" s="2"/>
-      <c r="F159" s="5"/>
+      <c r="A159" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C159" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="D159" s="33">
+        <v>3.63</v>
+      </c>
+      <c r="E159" s="30" t="s">
+        <v>447</v>
+      </c>
+      <c r="F159" s="31">
+        <v>134</v>
+      </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A160" s="5"/>
-      <c r="C160" s="5"/>
-      <c r="E160" s="2"/>
-      <c r="F160" s="5"/>
+      <c r="A160" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="D160" s="33">
+        <v>2.0300000000000002</v>
+      </c>
+      <c r="E160" s="30" t="s">
+        <v>448</v>
+      </c>
+      <c r="F160" s="31">
+        <v>176</v>
+      </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A161" s="5"/>
-      <c r="C161" s="5"/>
-      <c r="E161" s="2"/>
-      <c r="F161" s="5"/>
+      <c r="A161" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="C161" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="D161" s="33">
+        <v>2.31</v>
+      </c>
+      <c r="E161" s="30" t="s">
+        <v>449</v>
+      </c>
+      <c r="F161" s="31">
+        <v>161</v>
+      </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A162" s="5"/>
-      <c r="C162" s="5"/>
-      <c r="E162" s="2"/>
-      <c r="F162" s="5"/>
+      <c r="A162" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="D162" s="33">
+        <v>2.4</v>
+      </c>
+      <c r="E162" s="30" t="s">
+        <v>450</v>
+      </c>
+      <c r="F162" s="31">
+        <v>10</v>
+      </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A163" s="5"/>
-      <c r="B163" s="11"/>
-      <c r="C163" s="5"/>
-      <c r="E163" s="2"/>
-      <c r="F163" s="5"/>
+      <c r="A163" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="D163" s="33">
+        <v>2.58</v>
+      </c>
+      <c r="E163" s="30" t="s">
+        <v>451</v>
+      </c>
+      <c r="F163" s="31">
+        <v>10</v>
+      </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A164" s="5"/>
-      <c r="B164" s="11"/>
-      <c r="C164" s="5"/>
-      <c r="D164" s="13"/>
-      <c r="E164" s="11"/>
-      <c r="F164" s="12"/>
+      <c r="A164" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="D164" s="33">
+        <v>3.44</v>
+      </c>
+      <c r="E164" s="30" t="s">
+        <v>452</v>
+      </c>
+      <c r="F164" s="31">
+        <v>-11</v>
+      </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" s="5"/>

--- a/prix/prix.xlsx
+++ b/prix/prix.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\platres-et-enduits\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\platres-et-enduits\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F12FC0-6119-493D-B95A-7B9B153E4A18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B582483-2E1C-41BE-A194-B74198A79663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1284" yWindow="312" windowWidth="19116" windowHeight="10884" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="472">
   <si>
     <t>path</t>
   </si>
@@ -1468,6 +1468,9 @@
   </si>
   <si>
     <t>galerie/corniere-galva.png</t>
+  </si>
+  <si>
+    <t>250-27x27</t>
   </si>
 </sst>
 </file>
@@ -5120,8 +5123,8 @@
       <c r="B157" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="C157" s="5" t="s">
-        <v>468</v>
+      <c r="C157" s="2">
+        <v>150</v>
       </c>
       <c r="D157" s="33">
         <v>2</v>
@@ -5140,8 +5143,8 @@
       <c r="B158" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="C158" s="5" t="s">
-        <v>468</v>
+      <c r="C158" s="2">
+        <v>180</v>
       </c>
       <c r="D158" s="33">
         <v>1.96</v>
@@ -5160,8 +5163,8 @@
       <c r="B159" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="C159" s="5" t="s">
-        <v>468</v>
+      <c r="C159" s="2">
+        <v>200</v>
       </c>
       <c r="D159" s="33">
         <v>3.63</v>
@@ -5180,8 +5183,8 @@
       <c r="B160" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="C160" s="5" t="s">
-        <v>468</v>
+      <c r="C160" s="2">
+        <v>220</v>
       </c>
       <c r="D160" s="33">
         <v>2.0300000000000002</v>
@@ -5200,8 +5203,8 @@
       <c r="B161" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="C161" s="5" t="s">
-        <v>468</v>
+      <c r="C161" s="2" t="s">
+        <v>471</v>
       </c>
       <c r="D161" s="33">
         <v>2.31</v>
@@ -5220,8 +5223,8 @@
       <c r="B162" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="C162" s="5" t="s">
-        <v>468</v>
+      <c r="C162" s="2">
+        <v>260</v>
       </c>
       <c r="D162" s="33">
         <v>2.4</v>
@@ -5240,8 +5243,8 @@
       <c r="B163" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="C163" s="5" t="s">
-        <v>468</v>
+      <c r="C163" s="2">
+        <v>280</v>
       </c>
       <c r="D163" s="33">
         <v>2.58</v>
@@ -5260,8 +5263,8 @@
       <c r="B164" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="C164" s="5" t="s">
-        <v>468</v>
+      <c r="C164" s="2">
+        <v>300</v>
       </c>
       <c r="D164" s="33">
         <v>3.44</v>

--- a/prix/prix.xlsx
+++ b/prix/prix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\platres-et-enduits\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B582483-2E1C-41BE-A194-B74198A79663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7138F8D3-48C6-41AD-AE1F-981ED5378EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="472">
   <si>
     <t>path</t>
   </si>
@@ -4995,8 +4995,8 @@
       <c r="B150" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="C150" s="5" t="s">
-        <v>468</v>
+      <c r="C150" s="5">
+        <v>3.05</v>
       </c>
       <c r="D150" s="33">
         <v>6.3</v>

--- a/prix/prix.xlsx
+++ b/prix/prix.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\platres-et-enduits\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\platres-et-enduits\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7138F8D3-48C6-41AD-AE1F-981ED5378EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4859E5A-353F-43AB-AD35-143AC9C03C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -1531,7 +1531,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1598,6 +1598,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1612,7 +1618,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1685,34 +1691,85 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -2093,13 +2150,13 @@
       <c r="C2" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="31">
         <v>24.26</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="32">
         <v>6</v>
       </c>
     </row>
@@ -2113,13 +2170,13 @@
       <c r="C3" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="31">
         <v>23.1</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="32">
         <v>5</v>
       </c>
     </row>
@@ -2131,14 +2188,14 @@
       <c r="C4" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="31">
         <v>7.8</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="5">
-        <v>6</v>
+      <c r="F4" s="32">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -2149,14 +2206,14 @@
       <c r="C5" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="31">
         <v>7.51</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="5">
-        <v>0</v>
+      <c r="F5" s="32">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -2169,14 +2226,14 @@
       <c r="C6" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="31">
         <v>17.16</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="5">
-        <v>10</v>
+      <c r="F6" s="32">
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -2189,14 +2246,14 @@
       <c r="C7" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="31">
         <v>16.5</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="5">
-        <v>2</v>
+      <c r="F7" s="32">
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -2209,14 +2266,14 @@
       <c r="C8" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="31">
         <v>8.4499999999999993</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="5">
-        <v>19</v>
+      <c r="F8" s="32">
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -2229,14 +2286,14 @@
       <c r="C9" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="D9" s="3">
-        <v>30.060000000000002</v>
+      <c r="D9" s="31">
+        <v>30.66</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="5">
-        <v>0</v>
+      <c r="F9" s="32">
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -2249,13 +2306,13 @@
       <c r="C10" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="31">
         <v>32.44</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="32">
         <v>7</v>
       </c>
     </row>
@@ -2267,14 +2324,14 @@
       <c r="C11" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="31">
         <v>8.86</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="5">
-        <v>0</v>
+      <c r="F11" s="32">
+        <v>-1</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -2287,14 +2344,14 @@
       <c r="C12" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="31">
         <v>19.02</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="5">
-        <v>0</v>
+      <c r="F12" s="32">
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -2307,13 +2364,13 @@
       <c r="C13" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="31">
         <v>51.44</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="32">
         <v>1</v>
       </c>
     </row>
@@ -2325,14 +2382,14 @@
       <c r="C14" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="31">
         <v>11.58</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="5">
-        <v>0</v>
+      <c r="F14" s="32">
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -2345,13 +2402,13 @@
       <c r="C15" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="31">
         <v>35.56</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="32">
         <v>5</v>
       </c>
     </row>
@@ -2365,13 +2422,13 @@
       <c r="C16" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="31">
         <v>89.14</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="32">
         <v>4</v>
       </c>
     </row>
@@ -2385,13 +2442,13 @@
       <c r="C17" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="31">
         <v>24.32</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="32">
         <v>5</v>
       </c>
     </row>
@@ -2405,13 +2462,13 @@
       <c r="C18" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="31">
         <v>31.240000000000002</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="32">
         <v>4</v>
       </c>
     </row>
@@ -2425,13 +2482,13 @@
       <c r="C19" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="31">
         <v>28.82</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="32">
         <v>4</v>
       </c>
     </row>
@@ -2445,13 +2502,13 @@
       <c r="C20" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="31">
         <v>72.710000000000008</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="32">
         <v>3</v>
       </c>
     </row>
@@ -2465,14 +2522,14 @@
       <c r="C21" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="31">
         <v>9.64</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="F21" s="5">
-        <v>4</v>
+      <c r="F21" s="32">
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -2483,13 +2540,13 @@
       <c r="C22" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="31">
         <v>23.8</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22" s="32">
         <v>3</v>
       </c>
     </row>
@@ -2501,13 +2558,13 @@
       <c r="C23" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="31">
         <v>35.68</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="32">
         <v>0</v>
       </c>
     </row>
@@ -2519,14 +2576,14 @@
       <c r="C24" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="31">
         <v>18.22</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F24" s="5">
-        <v>25</v>
+      <c r="F24" s="32">
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -2537,13 +2594,13 @@
       <c r="C25" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D25" s="31">
         <v>18.150000000000002</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="32">
         <v>3</v>
       </c>
     </row>
@@ -2557,14 +2614,14 @@
       <c r="C26" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="31">
         <v>15.32</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F26" s="5">
-        <v>19</v>
+      <c r="F26" s="32">
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -2577,13 +2634,13 @@
       <c r="C27" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="31">
         <v>29.5</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="32">
         <v>3</v>
       </c>
     </row>
@@ -2597,14 +2654,14 @@
       <c r="C28" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="31">
         <v>44</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="F28" s="5">
-        <v>17</v>
+      <c r="F28" s="32">
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -2617,13 +2674,13 @@
       <c r="C29" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29" s="31">
         <v>64</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29" s="32">
         <v>2</v>
       </c>
     </row>
@@ -2635,13 +2692,13 @@
       <c r="C30" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D30" s="31">
         <v>18.37</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30" s="32">
         <v>0</v>
       </c>
     </row>
@@ -2653,13 +2710,13 @@
       <c r="C31" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="D31" s="3">
+      <c r="D31" s="31">
         <v>39.57</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F31" s="32">
         <v>-1</v>
       </c>
     </row>
@@ -2673,13 +2730,13 @@
       <c r="C32" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="31">
         <v>44.78</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F32" s="32">
         <v>1</v>
       </c>
     </row>
@@ -2691,13 +2748,13 @@
       <c r="C33" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="31">
         <v>43.74</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33" s="32">
         <v>0</v>
       </c>
     </row>
@@ -2709,13 +2766,13 @@
       <c r="C34" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D34" s="31">
         <v>25.22</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F34" s="32">
         <v>1</v>
       </c>
     </row>
@@ -2727,13 +2784,13 @@
       <c r="C35" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="31">
         <v>52.01</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="32">
         <v>2</v>
       </c>
     </row>
@@ -2745,13 +2802,13 @@
       <c r="C36" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="31">
         <v>24.32</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="F36" s="5">
+      <c r="F36" s="32">
         <v>8</v>
       </c>
     </row>
@@ -2765,14 +2822,14 @@
       <c r="C37" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="D37" s="3">
-        <v>14.19</v>
+      <c r="D37" s="33">
+        <v>14.59</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="F37" s="5">
-        <v>68</v>
+      <c r="F37" s="34">
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -2785,14 +2842,14 @@
       <c r="C38" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D38" s="33">
         <v>9.57</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F38" s="5">
-        <v>36</v>
+      <c r="F38" s="34">
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -2805,14 +2862,14 @@
       <c r="C39" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="D39" s="3">
+      <c r="D39" s="33">
         <v>13.65</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F39" s="5">
-        <v>104</v>
+      <c r="F39" s="34">
+        <v>74</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -2825,14 +2882,14 @@
       <c r="C40" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="D40" s="3">
+      <c r="D40" s="33">
         <v>12.27</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F40" s="5">
-        <v>636</v>
+      <c r="F40" s="34">
+        <v>360</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -2845,13 +2902,13 @@
       <c r="C41" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="33">
         <v>18.21</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F41" s="5">
+      <c r="F41" s="34">
         <v>22</v>
       </c>
     </row>
@@ -2865,14 +2922,14 @@
       <c r="C42" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="D42" s="3">
-        <v>15.540000000000001</v>
+      <c r="D42" s="33">
+        <v>15.92</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F42" s="5">
-        <v>59</v>
+      <c r="F42" s="34">
+        <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -2892,7 +2949,7 @@
         <v>12</v>
       </c>
       <c r="F43" s="5">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -2906,13 +2963,13 @@
         <v>228</v>
       </c>
       <c r="D44" s="3">
-        <v>31.470000000000002</v>
+        <v>32.04</v>
       </c>
       <c r="E44" s="15" t="s">
         <v>13</v>
       </c>
       <c r="F44" s="5">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -2932,7 +2989,7 @@
         <v>14</v>
       </c>
       <c r="F45" s="5">
-        <v>59</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -2952,7 +3009,7 @@
         <v>15</v>
       </c>
       <c r="F46" s="5">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -2965,14 +3022,14 @@
       <c r="C47" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="D47" s="3">
-        <v>5.47</v>
+      <c r="D47" s="35">
+        <v>5.5200000000000005</v>
       </c>
       <c r="E47" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="F47" s="5">
-        <v>114.4</v>
+      <c r="F47" s="36">
+        <v>268.00000000000006</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -2985,14 +3042,14 @@
       <c r="C48" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="35">
         <v>4.33</v>
       </c>
       <c r="E48" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="F48" s="5">
-        <v>290.16000000000008</v>
+      <c r="F48" s="36">
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -3005,14 +3062,14 @@
       <c r="C49" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D49" s="3">
-        <v>4.84</v>
+      <c r="D49" s="35">
+        <v>4.9000000000000004</v>
       </c>
       <c r="E49" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="F49" s="5">
-        <v>224.64000000000047</v>
+      <c r="F49" s="36">
+        <v>144.08000000000038</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -3025,14 +3082,14 @@
       <c r="C50" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D50" s="3">
+      <c r="D50" s="35">
         <v>5.09</v>
       </c>
       <c r="E50" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="F50" s="5">
-        <v>287.99999999999972</v>
+      <c r="F50" s="36">
+        <v>261.97999999999973</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -3045,13 +3102,13 @@
       <c r="C51" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="D51" s="3">
+      <c r="D51" s="35">
         <v>5.26</v>
       </c>
       <c r="E51" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="F51" s="5">
+      <c r="F51" s="36">
         <v>0</v>
       </c>
     </row>
@@ -3065,14 +3122,14 @@
       <c r="C52" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D52" s="3">
-        <v>5.09</v>
+      <c r="D52" s="35">
+        <v>4.96</v>
       </c>
       <c r="E52" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="F52" s="5">
-        <v>705.11999999999944</v>
+      <c r="F52" s="36">
+        <v>436.79999999999916</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -3085,13 +3142,13 @@
       <c r="C53" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="D53" s="3">
+      <c r="D53" s="35">
         <v>5.26</v>
       </c>
       <c r="E53" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="F53" s="5">
+      <c r="F53" s="36">
         <v>6.7199999999999758</v>
       </c>
     </row>
@@ -3105,13 +3162,13 @@
       <c r="C54" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="35">
         <v>5.13</v>
       </c>
       <c r="E54" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="F54" s="5">
+      <c r="F54" s="36">
         <v>0</v>
       </c>
     </row>
@@ -3125,14 +3182,14 @@
       <c r="C55" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D55" s="3">
+      <c r="D55" s="35">
         <v>5.09</v>
       </c>
       <c r="E55" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="F55" s="5">
-        <v>335.40199999999822</v>
+      <c r="F55" s="36">
+        <v>131.0419999999981</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -3145,14 +3202,14 @@
       <c r="C56" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D56" s="3">
-        <v>9.0400000000000009</v>
+      <c r="D56" s="35">
+        <v>8.4600000000000009</v>
       </c>
       <c r="E56" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="F56" s="5">
-        <v>84.2399999999991</v>
+      <c r="F56" s="36">
+        <v>207.47999999999905</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
@@ -3165,14 +3222,14 @@
       <c r="C57" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="35">
         <v>9.0400000000000009</v>
       </c>
       <c r="E57" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="F57" s="5">
-        <v>156.00000000000091</v>
+      <c r="F57" s="36">
+        <v>131.0400000000009</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -3185,13 +3242,13 @@
       <c r="C58" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="35">
         <v>7.25</v>
       </c>
       <c r="E58" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="F58" s="5">
+      <c r="F58" s="36">
         <v>0</v>
       </c>
     </row>
@@ -3205,14 +3262,14 @@
       <c r="C59" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="D59" s="3">
-        <v>8.16</v>
+      <c r="D59" s="35">
+        <v>8.2200000000000006</v>
       </c>
       <c r="E59" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="F59" s="5">
-        <v>-2.1316282072803006E-14</v>
+      <c r="F59" s="36">
+        <v>118.55999999999999</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
@@ -3225,13 +3282,13 @@
       <c r="C60" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="35">
         <v>7.71</v>
       </c>
       <c r="E60" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="F60" s="5">
+      <c r="F60" s="36">
         <v>0</v>
       </c>
     </row>
@@ -3245,14 +3302,14 @@
       <c r="C61" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D61" s="3">
+      <c r="D61" s="35">
         <v>8.4499999999999993</v>
       </c>
       <c r="E61" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="F61" s="5">
-        <v>156.00000000000011</v>
+      <c r="F61" s="36">
+        <v>87.360000000000113</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -3265,13 +3322,13 @@
       <c r="C62" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="35">
         <v>9.33</v>
       </c>
       <c r="E62" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="F62" s="5">
+      <c r="F62" s="36">
         <v>0</v>
       </c>
     </row>
@@ -3285,14 +3342,14 @@
       <c r="C63" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="D63" s="3">
+      <c r="D63" s="37">
         <v>23.900000000000002</v>
       </c>
       <c r="E63" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="F63" s="5">
-        <v>15</v>
+      <c r="F63" s="38">
+        <v>14</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
@@ -3305,14 +3362,14 @@
       <c r="C64" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="D64" s="3">
+      <c r="D64" s="37">
         <v>10.9</v>
       </c>
       <c r="E64" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="F64" s="5">
-        <v>3</v>
+      <c r="F64" s="38">
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
@@ -3325,14 +3382,14 @@
       <c r="C65" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="D65" s="3">
+      <c r="D65" s="37">
         <v>12.06</v>
       </c>
       <c r="E65" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="F65" s="5">
-        <v>2</v>
+      <c r="F65" s="38">
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
@@ -3345,14 +3402,14 @@
       <c r="C66" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="37">
         <v>1.78</v>
       </c>
       <c r="E66" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="F66" s="5">
-        <v>16</v>
+      <c r="F66" s="38">
+        <v>11</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
@@ -3365,14 +3422,14 @@
       <c r="C67" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="D67" s="3">
+      <c r="D67" s="37">
         <v>5.48</v>
       </c>
       <c r="E67" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="F67" s="5">
-        <v>25</v>
+      <c r="F67" s="38">
+        <v>17</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
@@ -3383,13 +3440,13 @@
       <c r="C68" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="D68" s="3">
+      <c r="D68" s="37">
         <v>5</v>
       </c>
       <c r="E68" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="F68" s="5">
+      <c r="F68" s="38">
         <v>0</v>
       </c>
     </row>
@@ -3403,14 +3460,14 @@
       <c r="C69" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="D69" s="3">
+      <c r="D69" s="37">
         <v>5.49</v>
       </c>
       <c r="E69" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="F69" s="5">
-        <v>3</v>
+      <c r="F69" s="38">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
@@ -3421,13 +3478,13 @@
       <c r="C70" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D70" s="3">
+      <c r="D70" s="37">
         <v>19.41</v>
       </c>
       <c r="E70" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="F70" s="5">
+      <c r="F70" s="38">
         <v>0</v>
       </c>
     </row>
@@ -3441,13 +3498,13 @@
       <c r="C71" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="D71" s="3">
+      <c r="D71" s="39">
         <v>25.8</v>
       </c>
       <c r="E71" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="F71" s="5">
+      <c r="F71" s="40">
         <v>4</v>
       </c>
       <c r="G71" s="19"/>
@@ -3462,14 +3519,14 @@
       <c r="C72" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="39">
         <v>27.3</v>
       </c>
       <c r="E72" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="F72" s="5">
-        <v>2</v>
+      <c r="F72" s="40">
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
@@ -3482,13 +3539,13 @@
       <c r="C73" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="D73" s="3">
+      <c r="D73" s="39">
         <v>40.119999999999997</v>
       </c>
       <c r="E73" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="F73" s="5">
+      <c r="F73" s="40">
         <v>5</v>
       </c>
     </row>
@@ -3502,14 +3559,14 @@
       <c r="C74" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="D74" s="3">
+      <c r="D74" s="39">
         <v>16.170000000000002</v>
       </c>
       <c r="E74" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="F74" s="5">
-        <v>10</v>
+      <c r="F74" s="40">
+        <v>9</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
@@ -3522,14 +3579,14 @@
       <c r="C75" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="D75" s="3">
+      <c r="D75" s="39">
         <v>22.05</v>
       </c>
       <c r="E75" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="F75" s="5">
-        <v>5</v>
+      <c r="F75" s="40">
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
@@ -3542,13 +3599,13 @@
       <c r="C76" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="39">
         <v>25.810000000000002</v>
       </c>
       <c r="E76" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="F76" s="5">
+      <c r="F76" s="40">
         <v>6</v>
       </c>
     </row>
@@ -3562,14 +3619,14 @@
       <c r="C77" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="D77" s="3">
+      <c r="D77" s="39">
         <v>13.07</v>
       </c>
       <c r="E77" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="F77" s="5">
-        <v>13</v>
+      <c r="F77" s="40">
+        <v>9</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
@@ -3582,14 +3639,14 @@
       <c r="C78" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="D78" s="3">
+      <c r="D78" s="39">
         <v>3.15</v>
       </c>
       <c r="E78" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="F78" s="5">
-        <v>14</v>
+      <c r="F78" s="40">
+        <v>9</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
@@ -3602,13 +3659,13 @@
       <c r="C79" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="D79" s="3">
+      <c r="D79" s="39">
         <v>16.63</v>
       </c>
       <c r="E79" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="F79" s="5">
+      <c r="F79" s="40">
         <v>36</v>
       </c>
     </row>
@@ -3622,14 +3679,14 @@
       <c r="C80" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="D80" s="3">
-        <v>6.17</v>
+      <c r="D80" s="39">
+        <v>6.36</v>
       </c>
       <c r="E80" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="F80" s="5">
-        <v>2</v>
+      <c r="F80" s="40">
+        <v>4</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
@@ -3642,14 +3699,14 @@
       <c r="C81" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="39">
         <v>15.73</v>
       </c>
       <c r="E81" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="F81" s="5">
-        <v>10</v>
+      <c r="F81" s="40">
+        <v>-14</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
@@ -3662,14 +3719,14 @@
       <c r="C82" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="D82" s="3">
+      <c r="D82" s="39">
         <v>3.92</v>
       </c>
       <c r="E82" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="F82" s="5">
-        <v>10</v>
+      <c r="F82" s="40">
+        <v>18</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
@@ -3682,14 +3739,14 @@
       <c r="C83" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="39">
         <v>21.95</v>
       </c>
       <c r="E83" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="F83" s="5">
-        <v>7</v>
+      <c r="F83" s="40">
+        <v>6</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
@@ -3702,14 +3759,14 @@
       <c r="C84" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D84" s="3">
+      <c r="D84" s="39">
         <v>4.99</v>
       </c>
       <c r="E84" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="F84" s="5">
-        <v>13</v>
+      <c r="F84" s="40">
+        <v>17</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
@@ -3722,13 +3779,13 @@
       <c r="C85" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D85" s="3">
+      <c r="D85" s="39">
         <v>7.36</v>
       </c>
       <c r="E85" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="F85" s="5">
+      <c r="F85" s="40">
         <v>11</v>
       </c>
     </row>
@@ -3742,13 +3799,13 @@
       <c r="C86" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="D86" s="3">
+      <c r="D86" s="39">
         <v>30.52</v>
       </c>
       <c r="E86" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="F86" s="5">
+      <c r="F86" s="40">
         <v>6</v>
       </c>
     </row>
@@ -3762,14 +3819,14 @@
       <c r="C87" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="D87" s="3">
+      <c r="D87" s="39">
         <v>6.05</v>
       </c>
       <c r="E87" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="F87" s="5">
-        <v>7</v>
+      <c r="F87" s="40">
+        <v>13</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
@@ -3782,13 +3839,13 @@
       <c r="C88" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="D88" s="3">
+      <c r="D88" s="39">
         <v>4.67</v>
       </c>
       <c r="E88" s="22" t="s">
         <v>168</v>
       </c>
-      <c r="F88" s="5">
+      <c r="F88" s="40">
         <v>5</v>
       </c>
     </row>
@@ -3802,13 +3859,13 @@
       <c r="C89" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="39">
         <v>15.58</v>
       </c>
       <c r="E89" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="F89" s="5">
+      <c r="F89" s="40">
         <v>0</v>
       </c>
     </row>
@@ -3822,14 +3879,14 @@
       <c r="C90" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="D90" s="3">
+      <c r="D90" s="39">
         <v>18.63</v>
       </c>
       <c r="E90" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="F90" s="5">
-        <v>8</v>
+      <c r="F90" s="40">
+        <v>6</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
@@ -3842,14 +3899,14 @@
       <c r="C91" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="D91" s="3">
-        <v>10.99</v>
+      <c r="D91" s="39">
+        <v>11.33</v>
       </c>
       <c r="E91" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="F91" s="5">
-        <v>0</v>
+      <c r="F91" s="40">
+        <v>6</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
@@ -3862,14 +3919,14 @@
       <c r="C92" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="D92" s="3">
+      <c r="D92" s="39">
         <v>22.97</v>
       </c>
       <c r="E92" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="F92" s="5">
-        <v>10</v>
+      <c r="F92" s="40">
+        <v>9</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
@@ -3882,13 +3939,13 @@
       <c r="C93" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="D93" s="3">
+      <c r="D93" s="39">
         <v>18.150000000000002</v>
       </c>
       <c r="E93" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="F93" s="5">
+      <c r="F93" s="40">
         <v>5</v>
       </c>
     </row>
@@ -3902,13 +3959,13 @@
       <c r="C94" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="39">
         <v>12.83</v>
       </c>
       <c r="E94" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="F94" s="5">
+      <c r="F94" s="40">
         <v>8</v>
       </c>
     </row>
@@ -3922,13 +3979,13 @@
       <c r="C95" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="D95" s="3">
+      <c r="D95" s="39">
         <v>42.25</v>
       </c>
       <c r="E95" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="F95" s="5">
+      <c r="F95" s="40">
         <v>11</v>
       </c>
     </row>
@@ -3942,13 +3999,13 @@
       <c r="C96" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="39">
         <v>17.38</v>
       </c>
       <c r="E96" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="F96" s="5">
+      <c r="F96" s="40">
         <v>3</v>
       </c>
     </row>
@@ -3962,14 +4019,14 @@
       <c r="C97" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="D97" s="3">
+      <c r="D97" s="39">
         <v>27.18</v>
       </c>
       <c r="E97" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="F97" s="5">
-        <v>4</v>
+      <c r="F97" s="40">
+        <v>3</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
@@ -3982,13 +4039,13 @@
       <c r="C98" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="D98" s="3">
+      <c r="D98" s="39">
         <v>34.51</v>
       </c>
       <c r="E98" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="F98" s="5">
+      <c r="F98" s="40">
         <v>7</v>
       </c>
     </row>
@@ -4002,13 +4059,13 @@
       <c r="C99" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="D99" s="3">
+      <c r="D99" s="39">
         <v>42.57</v>
       </c>
       <c r="E99" s="22" t="s">
         <v>179</v>
       </c>
-      <c r="F99" s="5">
+      <c r="F99" s="40">
         <v>7</v>
       </c>
     </row>
@@ -4022,13 +4079,13 @@
       <c r="C100" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="39">
         <v>21.68</v>
       </c>
       <c r="E100" s="22" t="s">
         <v>180</v>
       </c>
-      <c r="F100" s="5">
+      <c r="F100" s="40">
         <v>6</v>
       </c>
     </row>
@@ -4042,14 +4099,14 @@
       <c r="C101" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="39">
         <v>24.78</v>
       </c>
       <c r="E101" s="22" t="s">
         <v>181</v>
       </c>
-      <c r="F101" s="5">
-        <v>4</v>
+      <c r="F101" s="40">
+        <v>9</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
@@ -4062,13 +4119,13 @@
       <c r="C102" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="D102" s="3">
+      <c r="D102" s="39">
         <v>16.63</v>
       </c>
       <c r="E102" s="22" t="s">
         <v>182</v>
       </c>
-      <c r="F102" s="5">
+      <c r="F102" s="40">
         <v>0</v>
       </c>
     </row>
@@ -4082,14 +4139,14 @@
       <c r="C103" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="D103" s="3">
-        <v>19.14</v>
+      <c r="D103" s="39">
+        <v>19.72</v>
       </c>
       <c r="E103" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="F103" s="5">
-        <v>7</v>
+      <c r="F103" s="40">
+        <v>11</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
@@ -4102,13 +4159,13 @@
       <c r="C104" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="D104" s="3">
+      <c r="D104" s="39">
         <v>33.01</v>
       </c>
       <c r="E104" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="F104" s="5">
+      <c r="F104" s="40">
         <v>15</v>
       </c>
     </row>
@@ -4122,14 +4179,14 @@
       <c r="C105" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="D105" s="3">
+      <c r="D105" s="41">
         <v>28.75</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F105" s="5">
-        <v>7</v>
+      <c r="F105" s="42">
+        <v>17</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
@@ -4142,14 +4199,14 @@
       <c r="C106" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="D106" s="3">
+      <c r="D106" s="41">
         <v>58.82</v>
       </c>
       <c r="E106" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F106" s="5">
-        <v>17</v>
+      <c r="F106" s="42">
+        <v>13</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
@@ -4162,14 +4219,14 @@
       <c r="C107" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="D107" s="3">
+      <c r="D107" s="41">
         <v>23.490000000000002</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F107" s="5">
-        <v>12</v>
+      <c r="F107" s="42">
+        <v>8</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
@@ -4182,13 +4239,13 @@
       <c r="C108" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="D108" s="3">
+      <c r="D108" s="41">
         <v>59.9</v>
       </c>
       <c r="E108" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F108" s="5">
+      <c r="F108" s="42">
         <v>8</v>
       </c>
     </row>
@@ -4202,14 +4259,14 @@
       <c r="C109" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D109" s="3">
+      <c r="D109" s="45">
         <v>10.89</v>
       </c>
-      <c r="E109" s="2" t="s">
+      <c r="E109" s="30" t="s">
         <v>327</v>
       </c>
-      <c r="F109" s="5">
-        <v>2</v>
+      <c r="F109" s="46">
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
@@ -4222,13 +4279,13 @@
       <c r="C110" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D110" s="3">
+      <c r="D110" s="45">
         <v>20.63</v>
       </c>
-      <c r="E110" s="2" t="s">
+      <c r="E110" s="30" t="s">
         <v>328</v>
       </c>
-      <c r="F110" s="5">
+      <c r="F110" s="46">
         <v>4</v>
       </c>
     </row>
@@ -4242,13 +4299,13 @@
       <c r="C111" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D111" s="3">
+      <c r="D111" s="45">
         <v>35.6</v>
       </c>
-      <c r="E111" s="2" t="s">
+      <c r="E111" s="30" t="s">
         <v>329</v>
       </c>
-      <c r="F111" s="5">
+      <c r="F111" s="46">
         <v>0</v>
       </c>
     </row>
@@ -4262,14 +4319,14 @@
       <c r="C112" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D112" s="3">
+      <c r="D112" s="45">
         <v>30.21</v>
       </c>
-      <c r="E112" s="2" t="s">
+      <c r="E112" s="30" t="s">
         <v>330</v>
       </c>
-      <c r="F112" s="5">
-        <v>1</v>
+      <c r="F112" s="46">
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
@@ -4282,13 +4339,13 @@
       <c r="C113" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D113" s="3">
+      <c r="D113" s="45">
         <v>33.06</v>
       </c>
-      <c r="E113" s="2" t="s">
+      <c r="E113" s="30" t="s">
         <v>331</v>
       </c>
-      <c r="F113" s="5">
+      <c r="F113" s="46">
         <v>3</v>
       </c>
     </row>
@@ -4302,13 +4359,13 @@
       <c r="C114" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D114" s="3">
+      <c r="D114" s="45">
         <v>17.82</v>
       </c>
-      <c r="E114" s="2" t="s">
+      <c r="E114" s="30" t="s">
         <v>332</v>
       </c>
-      <c r="F114" s="5">
+      <c r="F114" s="46">
         <v>5</v>
       </c>
     </row>
@@ -4322,14 +4379,14 @@
       <c r="C115" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D115" s="3">
+      <c r="D115" s="45">
         <v>14.33</v>
       </c>
-      <c r="E115" s="2" t="s">
+      <c r="E115" s="30" t="s">
         <v>333</v>
       </c>
-      <c r="F115" s="5">
-        <v>4</v>
+      <c r="F115" s="46">
+        <v>2</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
@@ -4342,14 +4399,14 @@
       <c r="C116" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D116" s="3">
+      <c r="D116" s="45">
         <v>14.33</v>
       </c>
-      <c r="E116" s="2" t="s">
+      <c r="E116" s="30" t="s">
         <v>334</v>
       </c>
-      <c r="F116" s="5">
-        <v>5</v>
+      <c r="F116" s="46">
+        <v>4</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
@@ -4362,14 +4419,14 @@
       <c r="C117" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D117" s="3">
+      <c r="D117" s="45">
         <v>14.33</v>
       </c>
-      <c r="E117" s="2" t="s">
+      <c r="E117" s="30" t="s">
         <v>335</v>
       </c>
-      <c r="F117" s="5">
-        <v>-1</v>
+      <c r="F117" s="46">
+        <v>-4</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
@@ -4380,13 +4437,13 @@
       <c r="C118" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D118" s="13">
+      <c r="D118" s="45">
         <v>46.160000000000004</v>
       </c>
-      <c r="E118" s="11" t="s">
+      <c r="E118" s="43" t="s">
         <v>336</v>
       </c>
-      <c r="F118" s="12">
+      <c r="F118" s="46">
         <v>0</v>
       </c>
     </row>
@@ -4400,14 +4457,14 @@
       <c r="C119" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D119" s="3">
+      <c r="D119" s="45">
         <v>61.71</v>
       </c>
-      <c r="E119" s="2" t="s">
+      <c r="E119" s="30" t="s">
         <v>337</v>
       </c>
-      <c r="F119" s="5">
-        <v>2</v>
+      <c r="F119" s="46">
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
@@ -4420,14 +4477,14 @@
       <c r="C120" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D120" s="3">
+      <c r="D120" s="49">
         <v>15.6</v>
       </c>
-      <c r="E120" s="2" t="s">
+      <c r="E120" s="44" t="s">
         <v>349</v>
       </c>
-      <c r="F120" s="5">
-        <v>4</v>
+      <c r="F120" s="50">
+        <v>3</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
@@ -4438,13 +4495,13 @@
       <c r="C121" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D121" s="13">
+      <c r="D121" s="49">
         <v>13.73</v>
       </c>
-      <c r="E121" s="11" t="s">
+      <c r="E121" s="47" t="s">
         <v>350</v>
       </c>
-      <c r="F121" s="12">
+      <c r="F121" s="50">
         <v>0</v>
       </c>
     </row>
@@ -4456,13 +4513,13 @@
       <c r="C122" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D122" s="13">
+      <c r="D122" s="49">
         <v>13.74</v>
       </c>
-      <c r="E122" s="11" t="s">
+      <c r="E122" s="47" t="s">
         <v>351</v>
       </c>
-      <c r="F122" s="12">
+      <c r="F122" s="50">
         <v>0</v>
       </c>
     </row>
@@ -4474,13 +4531,13 @@
       <c r="C123" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D123" s="13">
+      <c r="D123" s="49">
         <v>16.670000000000002</v>
       </c>
-      <c r="E123" s="11" t="s">
+      <c r="E123" s="47" t="s">
         <v>352</v>
       </c>
-      <c r="F123" s="12">
+      <c r="F123" s="50">
         <v>0</v>
       </c>
     </row>
@@ -4494,13 +4551,13 @@
       <c r="C124" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D124" s="3">
+      <c r="D124" s="49">
         <v>24.490000000000002</v>
       </c>
-      <c r="E124" s="2" t="s">
+      <c r="E124" s="44" t="s">
         <v>353</v>
       </c>
-      <c r="F124" s="5">
+      <c r="F124" s="50">
         <v>2</v>
       </c>
     </row>
@@ -4514,14 +4571,14 @@
       <c r="C125" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D125" s="3">
+      <c r="D125" s="49">
         <v>14.31</v>
       </c>
-      <c r="E125" s="2" t="s">
+      <c r="E125" s="44" t="s">
         <v>354</v>
       </c>
-      <c r="F125" s="5">
-        <v>1</v>
+      <c r="F125" s="50">
+        <v>-3</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
@@ -4534,31 +4591,31 @@
       <c r="C126" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D126" s="3">
+      <c r="D126" s="49">
         <v>21.54</v>
       </c>
-      <c r="E126" s="2" t="s">
+      <c r="E126" s="44" t="s">
         <v>355</v>
       </c>
-      <c r="F126" s="5">
+      <c r="F126" s="50">
         <v>3</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="27"/>
-      <c r="B127" s="28" t="s">
+      <c r="A127" s="26"/>
+      <c r="B127" s="27" t="s">
         <v>383</v>
       </c>
       <c r="C127" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D127" s="29">
+      <c r="D127" s="49">
         <v>48.35</v>
       </c>
-      <c r="E127" s="28" t="s">
+      <c r="E127" s="47" t="s">
         <v>356</v>
       </c>
-      <c r="F127" s="27">
+      <c r="F127" s="50">
         <v>0</v>
       </c>
     </row>
@@ -4572,14 +4629,14 @@
       <c r="C128" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D128" s="3">
+      <c r="D128" s="49">
         <v>38.24</v>
       </c>
-      <c r="E128" s="2" t="s">
+      <c r="E128" s="44" t="s">
         <v>357</v>
       </c>
-      <c r="F128" s="5">
-        <v>5</v>
+      <c r="F128" s="50">
+        <v>4</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
@@ -4592,13 +4649,13 @@
       <c r="C129" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D129" s="3">
+      <c r="D129" s="49">
         <v>2.5300000000000002</v>
       </c>
-      <c r="E129" s="2" t="s">
+      <c r="E129" s="44" t="s">
         <v>358</v>
       </c>
-      <c r="F129" s="5">
+      <c r="F129" s="50">
         <v>1</v>
       </c>
     </row>
@@ -4612,13 +4669,13 @@
       <c r="C130" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D130" s="3">
+      <c r="D130" s="49">
         <v>16.7</v>
       </c>
-      <c r="E130" s="2" t="s">
+      <c r="E130" s="44" t="s">
         <v>359</v>
       </c>
-      <c r="F130" s="5">
+      <c r="F130" s="50">
         <v>3</v>
       </c>
     </row>
@@ -4632,13 +4689,13 @@
       <c r="C131" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D131" s="26">
+      <c r="D131" s="49">
         <v>19.490000000000002</v>
       </c>
-      <c r="E131" s="25" t="s">
+      <c r="E131" s="48" t="s">
         <v>360</v>
       </c>
-      <c r="F131" s="24">
+      <c r="F131" s="50">
         <v>0</v>
       </c>
     </row>
@@ -4650,13 +4707,13 @@
       <c r="C132" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D132" s="13">
+      <c r="D132" s="49">
         <v>14.96</v>
       </c>
-      <c r="E132" s="11" t="s">
+      <c r="E132" s="47" t="s">
         <v>361</v>
       </c>
-      <c r="F132" s="12">
+      <c r="F132" s="50">
         <v>0</v>
       </c>
     </row>
@@ -4670,13 +4727,13 @@
       <c r="C133" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D133" s="3">
+      <c r="D133" s="49">
         <v>36.78</v>
       </c>
-      <c r="E133" s="2" t="s">
+      <c r="E133" s="44" t="s">
         <v>362</v>
       </c>
-      <c r="F133" s="5">
+      <c r="F133" s="50">
         <v>1</v>
       </c>
     </row>
@@ -4688,13 +4745,13 @@
       <c r="C134" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D134" s="13">
+      <c r="D134" s="49">
         <v>21.6</v>
       </c>
-      <c r="E134" s="11" t="s">
+      <c r="E134" s="47" t="s">
         <v>363</v>
       </c>
-      <c r="F134" s="12">
+      <c r="F134" s="50">
         <v>0</v>
       </c>
     </row>
@@ -4708,14 +4765,14 @@
       <c r="C135" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D135" s="3">
+      <c r="D135" s="49">
         <v>8.24</v>
       </c>
-      <c r="E135" s="2" t="s">
+      <c r="E135" s="44" t="s">
         <v>364</v>
       </c>
-      <c r="F135" s="5">
-        <v>2</v>
+      <c r="F135" s="50">
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
@@ -4728,14 +4785,14 @@
       <c r="C136" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D136" s="3">
+      <c r="D136" s="49">
         <v>3.7</v>
       </c>
-      <c r="E136" s="2" t="s">
+      <c r="E136" s="44" t="s">
         <v>365</v>
       </c>
-      <c r="F136" s="5">
-        <v>3</v>
+      <c r="F136" s="50">
+        <v>2</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
@@ -4748,14 +4805,14 @@
       <c r="C137" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D137" s="3">
+      <c r="D137" s="49">
         <v>3.42</v>
       </c>
-      <c r="E137" s="2" t="s">
+      <c r="E137" s="44" t="s">
         <v>366</v>
       </c>
-      <c r="F137" s="5">
-        <v>3</v>
+      <c r="F137" s="50">
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
@@ -4766,13 +4823,13 @@
       <c r="C138" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D138" s="13">
+      <c r="D138" s="49">
         <v>4.59</v>
       </c>
-      <c r="E138" s="11" t="s">
+      <c r="E138" s="47" t="s">
         <v>367</v>
       </c>
-      <c r="F138" s="12">
+      <c r="F138" s="50">
         <v>0</v>
       </c>
     </row>
@@ -4784,13 +4841,13 @@
       <c r="C139" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D139" s="13">
+      <c r="D139" s="49">
         <v>12.4</v>
       </c>
-      <c r="E139" s="11" t="s">
+      <c r="E139" s="47" t="s">
         <v>368</v>
       </c>
-      <c r="F139" s="12">
+      <c r="F139" s="50">
         <v>0</v>
       </c>
     </row>
@@ -4804,13 +4861,13 @@
       <c r="C140" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D140" s="3">
+      <c r="D140" s="49">
         <v>10.16</v>
       </c>
-      <c r="E140" s="2" t="s">
+      <c r="E140" s="44" t="s">
         <v>369</v>
       </c>
-      <c r="F140" s="5">
+      <c r="F140" s="50">
         <v>2</v>
       </c>
     </row>
@@ -4824,14 +4881,14 @@
       <c r="C141" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D141" s="3">
+      <c r="D141" s="49">
         <v>9.15</v>
       </c>
-      <c r="E141" s="2" t="s">
+      <c r="E141" s="44" t="s">
         <v>370</v>
       </c>
-      <c r="F141" s="5">
-        <v>4</v>
+      <c r="F141" s="50">
+        <v>2</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
@@ -4842,14 +4899,14 @@
       <c r="C142" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D142" s="13">
+      <c r="D142" s="49">
         <v>11.69</v>
       </c>
-      <c r="E142" s="11" t="s">
+      <c r="E142" s="47" t="s">
         <v>371</v>
       </c>
-      <c r="F142" s="12">
-        <v>0</v>
+      <c r="F142" s="50">
+        <v>-1</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
@@ -4862,14 +4919,14 @@
       <c r="C143" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D143" s="3">
+      <c r="D143" s="49">
         <v>6.32</v>
       </c>
-      <c r="E143" s="2" t="s">
+      <c r="E143" s="44" t="s">
         <v>372</v>
       </c>
-      <c r="F143" s="5">
-        <v>3</v>
+      <c r="F143" s="50">
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
@@ -4882,13 +4939,13 @@
       <c r="C144" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D144" s="3">
+      <c r="D144" s="49">
         <v>4.96</v>
       </c>
-      <c r="E144" s="2" t="s">
+      <c r="E144" s="44" t="s">
         <v>373</v>
       </c>
-      <c r="F144" s="5">
+      <c r="F144" s="50">
         <v>3</v>
       </c>
     </row>
@@ -4900,13 +4957,13 @@
       <c r="C145" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D145" s="13">
+      <c r="D145" s="49">
         <v>9.8000000000000007</v>
       </c>
-      <c r="E145" s="11" t="s">
+      <c r="E145" s="47" t="s">
         <v>374</v>
       </c>
-      <c r="F145" s="12">
+      <c r="F145" s="50">
         <v>0</v>
       </c>
     </row>
@@ -4920,14 +4977,14 @@
       <c r="C146" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D146" s="3">
+      <c r="D146" s="49">
         <v>8.14</v>
       </c>
-      <c r="E146" s="2" t="s">
+      <c r="E146" s="44" t="s">
         <v>375</v>
       </c>
-      <c r="F146" s="5">
-        <v>9</v>
+      <c r="F146" s="50">
+        <v>7</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
@@ -4938,13 +4995,13 @@
       <c r="C147" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D147" s="13">
+      <c r="D147" s="49">
         <v>5</v>
       </c>
-      <c r="E147" s="11" t="s">
+      <c r="E147" s="47" t="s">
         <v>376</v>
       </c>
-      <c r="F147" s="12">
+      <c r="F147" s="50">
         <v>0</v>
       </c>
     </row>
@@ -4965,7 +5022,7 @@
         <v>404</v>
       </c>
       <c r="F148" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
@@ -4985,7 +5042,7 @@
         <v>405</v>
       </c>
       <c r="F149" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
@@ -4998,14 +5055,14 @@
       <c r="C150" s="5">
         <v>3.05</v>
       </c>
-      <c r="D150" s="33">
+      <c r="D150" s="51">
         <v>6.3</v>
       </c>
-      <c r="E150" s="30" t="s">
+      <c r="E150" s="28" t="s">
         <v>438</v>
       </c>
-      <c r="F150" s="31">
-        <v>158</v>
+      <c r="F150" s="52">
+        <v>244</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
@@ -5016,13 +5073,13 @@
       <c r="C151" s="12" t="s">
         <v>468</v>
       </c>
-      <c r="D151" s="32">
+      <c r="D151" s="51">
         <v>0.61</v>
       </c>
-      <c r="E151" s="34" t="s">
+      <c r="E151" s="29" t="s">
         <v>439</v>
       </c>
-      <c r="F151" s="35">
+      <c r="F151" s="52">
         <v>0</v>
       </c>
     </row>
@@ -5034,13 +5091,13 @@
       <c r="C152" s="12" t="s">
         <v>468</v>
       </c>
-      <c r="D152" s="32">
+      <c r="D152" s="51">
         <v>0.61</v>
       </c>
-      <c r="E152" s="34" t="s">
+      <c r="E152" s="29" t="s">
         <v>440</v>
       </c>
-      <c r="F152" s="35">
+      <c r="F152" s="52">
         <v>0</v>
       </c>
     </row>
@@ -5052,13 +5109,13 @@
       <c r="C153" s="12" t="s">
         <v>468</v>
       </c>
-      <c r="D153" s="32">
+      <c r="D153" s="51">
         <v>0.61</v>
       </c>
-      <c r="E153" s="34" t="s">
+      <c r="E153" s="29" t="s">
         <v>441</v>
       </c>
-      <c r="F153" s="35">
+      <c r="F153" s="52">
         <v>0</v>
       </c>
     </row>
@@ -5070,13 +5127,13 @@
       <c r="C154" s="12" t="s">
         <v>468</v>
       </c>
-      <c r="D154" s="32">
+      <c r="D154" s="51">
         <v>0.61</v>
       </c>
-      <c r="E154" s="34" t="s">
+      <c r="E154" s="29" t="s">
         <v>442</v>
       </c>
-      <c r="F154" s="35">
+      <c r="F154" s="52">
         <v>0</v>
       </c>
     </row>
@@ -5088,13 +5145,13 @@
       <c r="C155" s="12" t="s">
         <v>468</v>
       </c>
-      <c r="D155" s="32">
+      <c r="D155" s="51">
         <v>7.9300000000000006</v>
       </c>
-      <c r="E155" s="34" t="s">
+      <c r="E155" s="29" t="s">
         <v>443</v>
       </c>
-      <c r="F155" s="35">
+      <c r="F155" s="52">
         <v>0</v>
       </c>
     </row>
@@ -5106,13 +5163,13 @@
       <c r="C156" s="12" t="s">
         <v>468</v>
       </c>
-      <c r="D156" s="32">
+      <c r="D156" s="51">
         <v>3.35</v>
       </c>
-      <c r="E156" s="34" t="s">
+      <c r="E156" s="29" t="s">
         <v>444</v>
       </c>
-      <c r="F156" s="35">
+      <c r="F156" s="52">
         <v>0</v>
       </c>
     </row>
@@ -5126,14 +5183,14 @@
       <c r="C157" s="2">
         <v>150</v>
       </c>
-      <c r="D157" s="33">
+      <c r="D157" s="51">
         <v>2</v>
       </c>
-      <c r="E157" s="30" t="s">
+      <c r="E157" s="28" t="s">
         <v>445</v>
       </c>
-      <c r="F157" s="31">
-        <v>119</v>
+      <c r="F157" s="52">
+        <v>118</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
@@ -5146,14 +5203,14 @@
       <c r="C158" s="2">
         <v>180</v>
       </c>
-      <c r="D158" s="33">
+      <c r="D158" s="51">
         <v>1.96</v>
       </c>
-      <c r="E158" s="30" t="s">
+      <c r="E158" s="28" t="s">
         <v>446</v>
       </c>
-      <c r="F158" s="31">
-        <v>139</v>
+      <c r="F158" s="52">
+        <v>137</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
@@ -5166,13 +5223,13 @@
       <c r="C159" s="2">
         <v>200</v>
       </c>
-      <c r="D159" s="33">
+      <c r="D159" s="51">
         <v>3.63</v>
       </c>
-      <c r="E159" s="30" t="s">
+      <c r="E159" s="28" t="s">
         <v>447</v>
       </c>
-      <c r="F159" s="31">
+      <c r="F159" s="52">
         <v>134</v>
       </c>
     </row>
@@ -5186,13 +5243,13 @@
       <c r="C160" s="2">
         <v>220</v>
       </c>
-      <c r="D160" s="33">
+      <c r="D160" s="51">
         <v>2.0300000000000002</v>
       </c>
-      <c r="E160" s="30" t="s">
+      <c r="E160" s="28" t="s">
         <v>448</v>
       </c>
-      <c r="F160" s="31">
+      <c r="F160" s="52">
         <v>176</v>
       </c>
     </row>
@@ -5206,14 +5263,14 @@
       <c r="C161" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="D161" s="33">
-        <v>2.31</v>
-      </c>
-      <c r="E161" s="30" t="s">
+      <c r="D161" s="51">
+        <v>3.0500000000000003</v>
+      </c>
+      <c r="E161" s="28" t="s">
         <v>449</v>
       </c>
-      <c r="F161" s="31">
-        <v>161</v>
+      <c r="F161" s="52">
+        <v>257</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
@@ -5226,14 +5283,14 @@
       <c r="C162" s="2">
         <v>260</v>
       </c>
-      <c r="D162" s="33">
-        <v>2.4</v>
-      </c>
-      <c r="E162" s="30" t="s">
+      <c r="D162" s="51">
+        <v>3.16</v>
+      </c>
+      <c r="E162" s="28" t="s">
         <v>450</v>
       </c>
-      <c r="F162" s="31">
-        <v>10</v>
+      <c r="F162" s="52">
+        <v>251</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
@@ -5246,14 +5303,14 @@
       <c r="C163" s="2">
         <v>280</v>
       </c>
-      <c r="D163" s="33">
-        <v>2.58</v>
-      </c>
-      <c r="E163" s="30" t="s">
+      <c r="D163" s="51">
+        <v>3.4</v>
+      </c>
+      <c r="E163" s="28" t="s">
         <v>451</v>
       </c>
-      <c r="F163" s="31">
-        <v>10</v>
+      <c r="F163" s="52">
+        <v>135</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
@@ -5266,14 +5323,14 @@
       <c r="C164" s="2">
         <v>300</v>
       </c>
-      <c r="D164" s="33">
-        <v>3.44</v>
-      </c>
-      <c r="E164" s="30" t="s">
+      <c r="D164" s="51">
+        <v>3.65</v>
+      </c>
+      <c r="E164" s="28" t="s">
         <v>452</v>
       </c>
-      <c r="F164" s="31">
-        <v>-11</v>
+      <c r="F164" s="52">
+        <v>87</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/prix.xlsx
+++ b/prix/prix.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\platres-et-enduits\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4859E5A-353F-43AB-AD35-143AC9C03C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C81279A8-660B-4B3F-8F0D-8A24412B6A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -1706,6 +1706,18 @@
     <xf numFmtId="49" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1742,23 +1754,11 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2150,13 +2150,13 @@
       <c r="C2" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="D2" s="31">
+      <c r="D2" s="35">
         <v>24.26</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="32">
+      <c r="F2" s="36">
         <v>6</v>
       </c>
     </row>
@@ -2170,13 +2170,13 @@
       <c r="C3" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="D3" s="31">
+      <c r="D3" s="35">
         <v>23.1</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="32">
+      <c r="F3" s="36">
         <v>5</v>
       </c>
     </row>
@@ -2188,14 +2188,14 @@
       <c r="C4" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="D4" s="31">
+      <c r="D4" s="35">
         <v>7.8</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="32">
-        <v>4</v>
+      <c r="F4" s="36">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -2206,14 +2206,14 @@
       <c r="C5" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="D5" s="31">
-        <v>7.51</v>
+      <c r="D5" s="35">
+        <v>7.66</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="32">
-        <v>4</v>
+      <c r="F5" s="36">
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -2226,14 +2226,14 @@
       <c r="C6" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="35">
         <v>17.16</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="32">
-        <v>5</v>
+      <c r="F6" s="36">
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -2246,14 +2246,14 @@
       <c r="C7" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="D7" s="31">
-        <v>16.5</v>
+      <c r="D7" s="35">
+        <v>16.830000000000002</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="32">
-        <v>9</v>
+      <c r="F7" s="36">
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -2266,14 +2266,14 @@
       <c r="C8" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D8" s="31">
-        <v>8.4499999999999993</v>
+      <c r="D8" s="35">
+        <v>8.6</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="32">
-        <v>9</v>
+      <c r="F8" s="36">
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -2286,14 +2286,14 @@
       <c r="C9" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="D9" s="31">
-        <v>30.66</v>
+      <c r="D9" s="35">
+        <v>32.130000000000003</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="32">
-        <v>30</v>
+      <c r="F9" s="36">
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -2306,14 +2306,14 @@
       <c r="C10" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="D10" s="31">
-        <v>32.44</v>
+      <c r="D10" s="35">
+        <v>33.090000000000003</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="32">
-        <v>7</v>
+      <c r="F10" s="36">
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -2324,13 +2324,13 @@
       <c r="C11" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="35">
         <v>8.86</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="32">
+      <c r="F11" s="36">
         <v>-1</v>
       </c>
     </row>
@@ -2344,13 +2344,13 @@
       <c r="C12" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="D12" s="31">
-        <v>19.02</v>
+      <c r="D12" s="35">
+        <v>19.41</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="32">
+      <c r="F12" s="36">
         <v>4</v>
       </c>
     </row>
@@ -2364,14 +2364,14 @@
       <c r="C13" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="D13" s="31">
-        <v>51.44</v>
+      <c r="D13" s="35">
+        <v>65.33</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F13" s="32">
-        <v>1</v>
+      <c r="F13" s="36">
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -2382,14 +2382,14 @@
       <c r="C14" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D14" s="31">
-        <v>11.58</v>
+      <c r="D14" s="35">
+        <v>11.82</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="32">
-        <v>5</v>
+      <c r="F14" s="36">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -2402,13 +2402,13 @@
       <c r="C15" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D15" s="31">
+      <c r="D15" s="35">
         <v>35.56</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="32">
+      <c r="F15" s="36">
         <v>5</v>
       </c>
     </row>
@@ -2422,13 +2422,13 @@
       <c r="C16" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="35">
         <v>89.14</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="32">
+      <c r="F16" s="36">
         <v>4</v>
       </c>
     </row>
@@ -2442,14 +2442,14 @@
       <c r="C17" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="35">
         <v>24.32</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="32">
-        <v>5</v>
+      <c r="F17" s="36">
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -2462,13 +2462,13 @@
       <c r="C18" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="D18" s="31">
+      <c r="D18" s="35">
         <v>31.240000000000002</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F18" s="32">
+      <c r="F18" s="36">
         <v>4</v>
       </c>
     </row>
@@ -2482,13 +2482,13 @@
       <c r="C19" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D19" s="31">
+      <c r="D19" s="35">
         <v>28.82</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F19" s="32">
+      <c r="F19" s="36">
         <v>4</v>
       </c>
     </row>
@@ -2502,13 +2502,13 @@
       <c r="C20" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="D20" s="31">
+      <c r="D20" s="35">
         <v>72.710000000000008</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F20" s="32">
+      <c r="F20" s="36">
         <v>3</v>
       </c>
     </row>
@@ -2522,14 +2522,14 @@
       <c r="C21" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="D21" s="31">
-        <v>9.64</v>
+      <c r="D21" s="35">
+        <v>9.84</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="F21" s="32">
-        <v>0</v>
+      <c r="F21" s="36">
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -2540,14 +2540,14 @@
       <c r="C22" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="D22" s="31">
+      <c r="D22" s="35">
         <v>23.8</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="32">
-        <v>3</v>
+      <c r="F22" s="36">
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -2558,13 +2558,13 @@
       <c r="C23" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="D23" s="31">
+      <c r="D23" s="35">
         <v>35.68</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="F23" s="32">
+      <c r="F23" s="36">
         <v>0</v>
       </c>
     </row>
@@ -2576,14 +2576,14 @@
       <c r="C24" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="D24" s="31">
+      <c r="D24" s="35">
         <v>18.22</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F24" s="32">
-        <v>12</v>
+      <c r="F24" s="36">
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -2594,13 +2594,13 @@
       <c r="C25" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="D25" s="31">
+      <c r="D25" s="35">
         <v>18.150000000000002</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F25" s="32">
+      <c r="F25" s="36">
         <v>3</v>
       </c>
     </row>
@@ -2614,14 +2614,14 @@
       <c r="C26" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="D26" s="31">
-        <v>15.32</v>
+      <c r="D26" s="35">
+        <v>15.63</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F26" s="32">
-        <v>0</v>
+      <c r="F26" s="36">
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -2634,13 +2634,13 @@
       <c r="C27" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="D27" s="31">
+      <c r="D27" s="35">
         <v>29.5</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F27" s="32">
+      <c r="F27" s="36">
         <v>3</v>
       </c>
     </row>
@@ -2654,14 +2654,14 @@
       <c r="C28" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="D28" s="31">
-        <v>44</v>
+      <c r="D28" s="35">
+        <v>49.51</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="F28" s="32">
-        <v>5</v>
+      <c r="F28" s="36">
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -2674,14 +2674,14 @@
       <c r="C29" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="D29" s="31">
+      <c r="D29" s="35">
         <v>64</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="F29" s="32">
-        <v>2</v>
+      <c r="F29" s="36">
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -2692,13 +2692,13 @@
       <c r="C30" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D30" s="31">
+      <c r="D30" s="35">
         <v>18.37</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F30" s="32">
+      <c r="F30" s="36">
         <v>0</v>
       </c>
     </row>
@@ -2710,13 +2710,13 @@
       <c r="C31" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="D31" s="31">
+      <c r="D31" s="35">
         <v>39.57</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F31" s="32">
+      <c r="F31" s="36">
         <v>-1</v>
       </c>
     </row>
@@ -2730,13 +2730,13 @@
       <c r="C32" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="D32" s="31">
+      <c r="D32" s="35">
         <v>44.78</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="F32" s="32">
+      <c r="F32" s="36">
         <v>1</v>
       </c>
     </row>
@@ -2748,14 +2748,14 @@
       <c r="C33" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="D33" s="31">
-        <v>43.74</v>
+      <c r="D33" s="35">
+        <v>44.61</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="F33" s="32">
-        <v>0</v>
+      <c r="F33" s="36">
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -2766,13 +2766,13 @@
       <c r="C34" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="D34" s="31">
+      <c r="D34" s="35">
         <v>25.22</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="F34" s="32">
+      <c r="F34" s="36">
         <v>1</v>
       </c>
     </row>
@@ -2784,13 +2784,13 @@
       <c r="C35" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="D35" s="31">
+      <c r="D35" s="35">
         <v>52.01</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F35" s="32">
+      <c r="F35" s="36">
         <v>2</v>
       </c>
     </row>
@@ -2802,14 +2802,14 @@
       <c r="C36" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="D36" s="31">
+      <c r="D36" s="35">
         <v>24.32</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="F36" s="32">
-        <v>8</v>
+      <c r="F36" s="36">
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -2822,14 +2822,14 @@
       <c r="C37" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="D37" s="33">
+      <c r="D37" s="37">
         <v>14.59</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="F37" s="34">
-        <v>60</v>
+      <c r="F37" s="38">
+        <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -2842,14 +2842,14 @@
       <c r="C38" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="D38" s="33">
+      <c r="D38" s="37">
         <v>9.57</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F38" s="34">
-        <v>30</v>
+      <c r="F38" s="38">
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -2862,14 +2862,14 @@
       <c r="C39" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="D39" s="33">
+      <c r="D39" s="37">
         <v>13.65</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F39" s="34">
-        <v>74</v>
+      <c r="F39" s="38">
+        <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -2882,14 +2882,14 @@
       <c r="C40" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="D40" s="33">
-        <v>12.27</v>
+      <c r="D40" s="37">
+        <v>12.86</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F40" s="34">
-        <v>360</v>
+      <c r="F40" s="38">
+        <v>301</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -2902,14 +2902,14 @@
       <c r="C41" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="D41" s="33">
+      <c r="D41" s="37">
         <v>18.21</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F41" s="34">
-        <v>22</v>
+      <c r="F41" s="38">
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -2922,14 +2922,14 @@
       <c r="C42" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="D42" s="33">
+      <c r="D42" s="37">
         <v>15.92</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F42" s="34">
-        <v>39</v>
+      <c r="F42" s="38">
+        <v>74</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -2949,7 +2949,7 @@
         <v>12</v>
       </c>
       <c r="F43" s="5">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -2969,7 +2969,7 @@
         <v>13</v>
       </c>
       <c r="F44" s="5">
-        <v>14</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -2989,7 +2989,7 @@
         <v>14</v>
       </c>
       <c r="F45" s="5">
-        <v>43</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -3009,7 +3009,7 @@
         <v>15</v>
       </c>
       <c r="F46" s="5">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -3022,14 +3022,14 @@
       <c r="C47" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="D47" s="35">
+      <c r="D47" s="39">
         <v>5.5200000000000005</v>
       </c>
       <c r="E47" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="F47" s="36">
-        <v>268.00000000000006</v>
+      <c r="F47" s="40">
+        <v>231.2</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -3042,14 +3042,14 @@
       <c r="C48" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="D48" s="35">
-        <v>4.33</v>
+      <c r="D48" s="39">
+        <v>5.25</v>
       </c>
       <c r="E48" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="F48" s="36">
-        <v>0</v>
+      <c r="F48" s="40">
+        <v>418.08000000000004</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -3062,14 +3062,14 @@
       <c r="C49" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D49" s="35">
-        <v>4.9000000000000004</v>
+      <c r="D49" s="39">
+        <v>4.59</v>
       </c>
       <c r="E49" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="F49" s="36">
-        <v>144.08000000000038</v>
+      <c r="F49" s="40">
+        <v>207.60000000000034</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -3082,14 +3082,14 @@
       <c r="C50" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D50" s="35">
-        <v>5.09</v>
+      <c r="D50" s="39">
+        <v>5.07</v>
       </c>
       <c r="E50" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="F50" s="36">
-        <v>261.97999999999973</v>
+      <c r="F50" s="40">
+        <v>518.29999999999973</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -3102,13 +3102,13 @@
       <c r="C51" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="D51" s="35">
+      <c r="D51" s="39">
         <v>5.26</v>
       </c>
       <c r="E51" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="F51" s="36">
+      <c r="F51" s="40">
         <v>0</v>
       </c>
     </row>
@@ -3122,14 +3122,14 @@
       <c r="C52" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D52" s="35">
+      <c r="D52" s="39">
         <v>4.96</v>
       </c>
       <c r="E52" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="F52" s="36">
-        <v>436.79999999999916</v>
+      <c r="F52" s="40">
+        <v>201.23999999999907</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -3142,13 +3142,13 @@
       <c r="C53" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="D53" s="35">
+      <c r="D53" s="39">
         <v>5.26</v>
       </c>
       <c r="E53" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="F53" s="36">
+      <c r="F53" s="40">
         <v>6.7199999999999758</v>
       </c>
     </row>
@@ -3162,13 +3162,13 @@
       <c r="C54" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D54" s="35">
+      <c r="D54" s="39">
         <v>5.13</v>
       </c>
       <c r="E54" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="F54" s="36">
+      <c r="F54" s="40">
         <v>0</v>
       </c>
     </row>
@@ -3182,14 +3182,14 @@
       <c r="C55" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D55" s="35">
-        <v>5.09</v>
+      <c r="D55" s="39">
+        <v>4.66</v>
       </c>
       <c r="E55" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="F55" s="36">
-        <v>131.0419999999981</v>
+      <c r="F55" s="40">
+        <v>143.52199999999806</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -3202,14 +3202,14 @@
       <c r="C56" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D56" s="35">
-        <v>8.4600000000000009</v>
+      <c r="D56" s="39">
+        <v>8.68</v>
       </c>
       <c r="E56" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="F56" s="36">
-        <v>207.47999999999905</v>
+      <c r="F56" s="40">
+        <v>148.21999999999906</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
@@ -3222,14 +3222,14 @@
       <c r="C57" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D57" s="35">
-        <v>9.0400000000000009</v>
+      <c r="D57" s="39">
+        <v>8.1999999999999993</v>
       </c>
       <c r="E57" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="F57" s="36">
-        <v>131.0400000000009</v>
+      <c r="F57" s="40">
+        <v>161.24000000000086</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -3242,13 +3242,13 @@
       <c r="C58" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D58" s="35">
+      <c r="D58" s="39">
         <v>7.25</v>
       </c>
       <c r="E58" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="F58" s="36">
+      <c r="F58" s="40">
         <v>0</v>
       </c>
     </row>
@@ -3262,14 +3262,14 @@
       <c r="C59" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="D59" s="35">
-        <v>8.2200000000000006</v>
+      <c r="D59" s="39">
+        <v>8.1300000000000008</v>
       </c>
       <c r="E59" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="F59" s="36">
-        <v>118.55999999999999</v>
+      <c r="F59" s="40">
+        <v>115.43999999999997</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
@@ -3282,14 +3282,14 @@
       <c r="C60" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="D60" s="35">
-        <v>7.71</v>
+      <c r="D60" s="39">
+        <v>8.43</v>
       </c>
       <c r="E60" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="F60" s="36">
-        <v>0</v>
+      <c r="F60" s="40">
+        <v>98.279999999999973</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
@@ -3302,13 +3302,13 @@
       <c r="C61" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D61" s="35">
+      <c r="D61" s="39">
         <v>8.4499999999999993</v>
       </c>
       <c r="E61" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="F61" s="36">
+      <c r="F61" s="40">
         <v>87.360000000000113</v>
       </c>
     </row>
@@ -3322,13 +3322,13 @@
       <c r="C62" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D62" s="35">
+      <c r="D62" s="39">
         <v>9.33</v>
       </c>
       <c r="E62" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="F62" s="36">
+      <c r="F62" s="40">
         <v>0</v>
       </c>
     </row>
@@ -3342,14 +3342,14 @@
       <c r="C63" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="D63" s="37">
-        <v>23.900000000000002</v>
+      <c r="D63" s="41">
+        <v>23.9</v>
       </c>
       <c r="E63" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="F63" s="38">
-        <v>14</v>
+      <c r="F63" s="42">
+        <v>9</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
@@ -3362,14 +3362,14 @@
       <c r="C64" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="D64" s="37">
-        <v>10.9</v>
+      <c r="D64" s="41">
+        <v>11.120000000000001</v>
       </c>
       <c r="E64" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="F64" s="38">
-        <v>0</v>
+      <c r="F64" s="42">
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
@@ -3382,14 +3382,14 @@
       <c r="C65" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="D65" s="37">
-        <v>12.06</v>
+      <c r="D65" s="41">
+        <v>12.58</v>
       </c>
       <c r="E65" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="F65" s="38">
-        <v>1</v>
+      <c r="F65" s="42">
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
@@ -3402,14 +3402,14 @@
       <c r="C66" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="D66" s="37">
+      <c r="D66" s="41">
         <v>1.78</v>
       </c>
       <c r="E66" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="F66" s="38">
-        <v>11</v>
+      <c r="F66" s="42">
+        <v>52</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
@@ -3422,14 +3422,14 @@
       <c r="C67" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="D67" s="37">
+      <c r="D67" s="41">
         <v>5.48</v>
       </c>
       <c r="E67" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="F67" s="38">
-        <v>17</v>
+      <c r="F67" s="42">
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
@@ -3440,13 +3440,13 @@
       <c r="C68" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="D68" s="37">
+      <c r="D68" s="41">
         <v>5</v>
       </c>
       <c r="E68" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="F68" s="38">
+      <c r="F68" s="42">
         <v>0</v>
       </c>
     </row>
@@ -3460,14 +3460,14 @@
       <c r="C69" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="D69" s="37">
+      <c r="D69" s="41">
         <v>5.49</v>
       </c>
       <c r="E69" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="F69" s="38">
-        <v>2</v>
+      <c r="F69" s="42">
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
@@ -3478,13 +3478,13 @@
       <c r="C70" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D70" s="37">
+      <c r="D70" s="41">
         <v>19.41</v>
       </c>
       <c r="E70" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="F70" s="38">
+      <c r="F70" s="42">
         <v>0</v>
       </c>
     </row>
@@ -3498,14 +3498,14 @@
       <c r="C71" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="D71" s="39">
+      <c r="D71" s="43">
         <v>25.8</v>
       </c>
       <c r="E71" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="F71" s="40">
-        <v>4</v>
+      <c r="F71" s="44">
+        <v>3</v>
       </c>
       <c r="G71" s="19"/>
     </row>
@@ -3519,14 +3519,14 @@
       <c r="C72" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="D72" s="39">
+      <c r="D72" s="43">
         <v>27.3</v>
       </c>
       <c r="E72" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="F72" s="40">
-        <v>1</v>
+      <c r="F72" s="44">
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
@@ -3539,13 +3539,13 @@
       <c r="C73" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="D73" s="39">
+      <c r="D73" s="43">
         <v>40.119999999999997</v>
       </c>
       <c r="E73" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="F73" s="40">
+      <c r="F73" s="44">
         <v>5</v>
       </c>
     </row>
@@ -3559,13 +3559,13 @@
       <c r="C74" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="D74" s="39">
+      <c r="D74" s="43">
         <v>16.170000000000002</v>
       </c>
       <c r="E74" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="F74" s="40">
+      <c r="F74" s="44">
         <v>9</v>
       </c>
     </row>
@@ -3579,13 +3579,13 @@
       <c r="C75" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="D75" s="39">
+      <c r="D75" s="43">
         <v>22.05</v>
       </c>
       <c r="E75" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="F75" s="40">
+      <c r="F75" s="44">
         <v>4</v>
       </c>
     </row>
@@ -3599,13 +3599,13 @@
       <c r="C76" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="D76" s="39">
+      <c r="D76" s="43">
         <v>25.810000000000002</v>
       </c>
       <c r="E76" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="F76" s="40">
+      <c r="F76" s="44">
         <v>6</v>
       </c>
     </row>
@@ -3619,14 +3619,14 @@
       <c r="C77" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="D77" s="39">
+      <c r="D77" s="43">
         <v>13.07</v>
       </c>
       <c r="E77" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="F77" s="40">
-        <v>9</v>
+      <c r="F77" s="44">
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
@@ -3639,13 +3639,13 @@
       <c r="C78" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="D78" s="39">
-        <v>3.15</v>
+      <c r="D78" s="43">
+        <v>3.22</v>
       </c>
       <c r="E78" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="F78" s="40">
+      <c r="F78" s="44">
         <v>9</v>
       </c>
     </row>
@@ -3659,13 +3659,13 @@
       <c r="C79" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="D79" s="39">
+      <c r="D79" s="43">
         <v>16.63</v>
       </c>
       <c r="E79" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="F79" s="40">
+      <c r="F79" s="44">
         <v>36</v>
       </c>
     </row>
@@ -3679,13 +3679,13 @@
       <c r="C80" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="D80" s="39">
+      <c r="D80" s="43">
         <v>6.36</v>
       </c>
       <c r="E80" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="F80" s="40">
+      <c r="F80" s="44">
         <v>4</v>
       </c>
     </row>
@@ -3699,14 +3699,14 @@
       <c r="C81" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D81" s="39">
+      <c r="D81" s="43">
         <v>15.73</v>
       </c>
       <c r="E81" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="F81" s="40">
-        <v>-14</v>
+      <c r="F81" s="44">
+        <v>-20</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
@@ -3719,14 +3719,14 @@
       <c r="C82" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="D82" s="39">
+      <c r="D82" s="43">
         <v>3.92</v>
       </c>
       <c r="E82" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="F82" s="40">
-        <v>18</v>
+      <c r="F82" s="44">
+        <v>11</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
@@ -3739,14 +3739,14 @@
       <c r="C83" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D83" s="39">
+      <c r="D83" s="43">
         <v>21.95</v>
       </c>
       <c r="E83" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="F83" s="40">
-        <v>6</v>
+      <c r="F83" s="44">
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
@@ -3759,14 +3759,14 @@
       <c r="C84" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D84" s="39">
+      <c r="D84" s="43">
         <v>4.99</v>
       </c>
       <c r="E84" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="F84" s="40">
-        <v>17</v>
+      <c r="F84" s="44">
+        <v>12</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
@@ -3779,14 +3779,14 @@
       <c r="C85" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D85" s="39">
+      <c r="D85" s="43">
         <v>7.36</v>
       </c>
       <c r="E85" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="F85" s="40">
-        <v>11</v>
+      <c r="F85" s="44">
+        <v>10</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
@@ -3799,13 +3799,13 @@
       <c r="C86" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="D86" s="39">
+      <c r="D86" s="43">
         <v>30.52</v>
       </c>
       <c r="E86" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="F86" s="40">
+      <c r="F86" s="44">
         <v>6</v>
       </c>
     </row>
@@ -3819,14 +3819,14 @@
       <c r="C87" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="D87" s="39">
+      <c r="D87" s="43">
         <v>6.05</v>
       </c>
       <c r="E87" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="F87" s="40">
-        <v>13</v>
+      <c r="F87" s="44">
+        <v>12</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
@@ -3839,13 +3839,13 @@
       <c r="C88" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="D88" s="39">
+      <c r="D88" s="43">
         <v>4.67</v>
       </c>
       <c r="E88" s="22" t="s">
         <v>168</v>
       </c>
-      <c r="F88" s="40">
+      <c r="F88" s="44">
         <v>5</v>
       </c>
     </row>
@@ -3859,13 +3859,13 @@
       <c r="C89" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="D89" s="39">
+      <c r="D89" s="43">
         <v>15.58</v>
       </c>
       <c r="E89" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="F89" s="40">
+      <c r="F89" s="44">
         <v>0</v>
       </c>
     </row>
@@ -3879,13 +3879,13 @@
       <c r="C90" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="D90" s="39">
+      <c r="D90" s="43">
         <v>18.63</v>
       </c>
       <c r="E90" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="F90" s="40">
+      <c r="F90" s="44">
         <v>6</v>
       </c>
     </row>
@@ -3899,13 +3899,13 @@
       <c r="C91" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="D91" s="39">
+      <c r="D91" s="43">
         <v>11.33</v>
       </c>
       <c r="E91" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="F91" s="40">
+      <c r="F91" s="44">
         <v>6</v>
       </c>
     </row>
@@ -3919,14 +3919,14 @@
       <c r="C92" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="D92" s="39">
+      <c r="D92" s="43">
         <v>22.97</v>
       </c>
       <c r="E92" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="F92" s="40">
-        <v>9</v>
+      <c r="F92" s="44">
+        <v>6</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
@@ -3939,13 +3939,13 @@
       <c r="C93" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="D93" s="39">
+      <c r="D93" s="43">
         <v>18.150000000000002</v>
       </c>
       <c r="E93" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="F93" s="40">
+      <c r="F93" s="44">
         <v>5</v>
       </c>
     </row>
@@ -3959,14 +3959,14 @@
       <c r="C94" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="D94" s="39">
+      <c r="D94" s="43">
         <v>12.83</v>
       </c>
       <c r="E94" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="F94" s="40">
-        <v>8</v>
+      <c r="F94" s="44">
+        <v>7</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
@@ -3979,13 +3979,13 @@
       <c r="C95" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="D95" s="39">
+      <c r="D95" s="43">
         <v>42.25</v>
       </c>
       <c r="E95" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="F95" s="40">
+      <c r="F95" s="44">
         <v>11</v>
       </c>
     </row>
@@ -3999,13 +3999,13 @@
       <c r="C96" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="D96" s="39">
+      <c r="D96" s="43">
         <v>17.38</v>
       </c>
       <c r="E96" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="F96" s="40">
+      <c r="F96" s="44">
         <v>3</v>
       </c>
     </row>
@@ -4019,13 +4019,13 @@
       <c r="C97" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="D97" s="39">
+      <c r="D97" s="43">
         <v>27.18</v>
       </c>
       <c r="E97" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="F97" s="40">
+      <c r="F97" s="44">
         <v>3</v>
       </c>
     </row>
@@ -4039,13 +4039,13 @@
       <c r="C98" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="D98" s="39">
+      <c r="D98" s="43">
         <v>34.51</v>
       </c>
       <c r="E98" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="F98" s="40">
+      <c r="F98" s="44">
         <v>7</v>
       </c>
     </row>
@@ -4059,13 +4059,13 @@
       <c r="C99" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="D99" s="39">
+      <c r="D99" s="43">
         <v>42.57</v>
       </c>
       <c r="E99" s="22" t="s">
         <v>179</v>
       </c>
-      <c r="F99" s="40">
+      <c r="F99" s="44">
         <v>7</v>
       </c>
     </row>
@@ -4079,13 +4079,13 @@
       <c r="C100" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="D100" s="39">
+      <c r="D100" s="43">
         <v>21.68</v>
       </c>
       <c r="E100" s="22" t="s">
         <v>180</v>
       </c>
-      <c r="F100" s="40">
+      <c r="F100" s="44">
         <v>6</v>
       </c>
     </row>
@@ -4099,14 +4099,14 @@
       <c r="C101" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D101" s="39">
+      <c r="D101" s="43">
         <v>24.78</v>
       </c>
       <c r="E101" s="22" t="s">
         <v>181</v>
       </c>
-      <c r="F101" s="40">
-        <v>9</v>
+      <c r="F101" s="44">
+        <v>4</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
@@ -4119,13 +4119,13 @@
       <c r="C102" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="D102" s="39">
+      <c r="D102" s="43">
         <v>16.63</v>
       </c>
       <c r="E102" s="22" t="s">
         <v>182</v>
       </c>
-      <c r="F102" s="40">
+      <c r="F102" s="44">
         <v>0</v>
       </c>
     </row>
@@ -4139,14 +4139,14 @@
       <c r="C103" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="D103" s="39">
+      <c r="D103" s="43">
         <v>19.72</v>
       </c>
       <c r="E103" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="F103" s="40">
-        <v>11</v>
+      <c r="F103" s="44">
+        <v>3</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
@@ -4159,13 +4159,13 @@
       <c r="C104" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="D104" s="39">
+      <c r="D104" s="43">
         <v>33.01</v>
       </c>
       <c r="E104" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="F104" s="40">
+      <c r="F104" s="44">
         <v>15</v>
       </c>
     </row>
@@ -4179,14 +4179,14 @@
       <c r="C105" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="D105" s="41">
+      <c r="D105" s="45">
         <v>28.75</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F105" s="42">
-        <v>17</v>
+      <c r="F105" s="46">
+        <v>11</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
@@ -4199,14 +4199,14 @@
       <c r="C106" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="D106" s="41">
+      <c r="D106" s="45">
         <v>58.82</v>
       </c>
       <c r="E106" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F106" s="42">
-        <v>13</v>
+      <c r="F106" s="46">
+        <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
@@ -4219,14 +4219,14 @@
       <c r="C107" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="D107" s="41">
+      <c r="D107" s="45">
         <v>23.490000000000002</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F107" s="42">
-        <v>8</v>
+      <c r="F107" s="46">
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
@@ -4239,13 +4239,13 @@
       <c r="C108" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="D108" s="41">
+      <c r="D108" s="45">
         <v>59.9</v>
       </c>
       <c r="E108" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F108" s="42">
+      <c r="F108" s="46">
         <v>8</v>
       </c>
     </row>
@@ -4259,14 +4259,14 @@
       <c r="C109" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D109" s="45">
-        <v>10.89</v>
+      <c r="D109" s="47">
+        <v>11.33</v>
       </c>
       <c r="E109" s="30" t="s">
         <v>327</v>
       </c>
-      <c r="F109" s="46">
-        <v>1</v>
+      <c r="F109" s="48">
+        <v>-1</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
@@ -4279,13 +4279,13 @@
       <c r="C110" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D110" s="45">
+      <c r="D110" s="47">
         <v>20.63</v>
       </c>
       <c r="E110" s="30" t="s">
         <v>328</v>
       </c>
-      <c r="F110" s="46">
+      <c r="F110" s="48">
         <v>4</v>
       </c>
     </row>
@@ -4299,13 +4299,13 @@
       <c r="C111" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D111" s="45">
+      <c r="D111" s="47">
         <v>35.6</v>
       </c>
       <c r="E111" s="30" t="s">
         <v>329</v>
       </c>
-      <c r="F111" s="46">
+      <c r="F111" s="48">
         <v>0</v>
       </c>
     </row>
@@ -4319,13 +4319,13 @@
       <c r="C112" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D112" s="45">
+      <c r="D112" s="47">
         <v>30.21</v>
       </c>
       <c r="E112" s="30" t="s">
         <v>330</v>
       </c>
-      <c r="F112" s="46">
+      <c r="F112" s="48">
         <v>0</v>
       </c>
     </row>
@@ -4339,14 +4339,14 @@
       <c r="C113" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D113" s="45">
+      <c r="D113" s="47">
         <v>33.06</v>
       </c>
       <c r="E113" s="30" t="s">
         <v>331</v>
       </c>
-      <c r="F113" s="46">
-        <v>3</v>
+      <c r="F113" s="48">
+        <v>2</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
@@ -4359,14 +4359,14 @@
       <c r="C114" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D114" s="45">
+      <c r="D114" s="47">
         <v>17.82</v>
       </c>
       <c r="E114" s="30" t="s">
         <v>332</v>
       </c>
-      <c r="F114" s="46">
-        <v>5</v>
+      <c r="F114" s="48">
+        <v>4</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
@@ -4379,14 +4379,14 @@
       <c r="C115" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D115" s="45">
+      <c r="D115" s="47">
         <v>14.33</v>
       </c>
       <c r="E115" s="30" t="s">
         <v>333</v>
       </c>
-      <c r="F115" s="46">
-        <v>2</v>
+      <c r="F115" s="48">
+        <v>4</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
@@ -4399,14 +4399,14 @@
       <c r="C116" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D116" s="45">
+      <c r="D116" s="47">
         <v>14.33</v>
       </c>
       <c r="E116" s="30" t="s">
         <v>334</v>
       </c>
-      <c r="F116" s="46">
-        <v>4</v>
+      <c r="F116" s="48">
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
@@ -4419,14 +4419,14 @@
       <c r="C117" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D117" s="45">
+      <c r="D117" s="47">
         <v>14.33</v>
       </c>
       <c r="E117" s="30" t="s">
         <v>335</v>
       </c>
-      <c r="F117" s="46">
-        <v>-4</v>
+      <c r="F117" s="48">
+        <v>-1</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
@@ -4437,13 +4437,13 @@
       <c r="C118" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D118" s="45">
+      <c r="D118" s="47">
         <v>46.160000000000004</v>
       </c>
-      <c r="E118" s="43" t="s">
+      <c r="E118" s="31" t="s">
         <v>336</v>
       </c>
-      <c r="F118" s="46">
+      <c r="F118" s="48">
         <v>0</v>
       </c>
     </row>
@@ -4457,14 +4457,14 @@
       <c r="C119" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D119" s="45">
+      <c r="D119" s="47">
         <v>61.71</v>
       </c>
       <c r="E119" s="30" t="s">
         <v>337</v>
       </c>
-      <c r="F119" s="46">
-        <v>1</v>
+      <c r="F119" s="48">
+        <v>3</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
@@ -4480,11 +4480,11 @@
       <c r="D120" s="49">
         <v>15.6</v>
       </c>
-      <c r="E120" s="44" t="s">
+      <c r="E120" s="32" t="s">
         <v>349</v>
       </c>
       <c r="F120" s="50">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
@@ -4498,7 +4498,7 @@
       <c r="D121" s="49">
         <v>13.73</v>
       </c>
-      <c r="E121" s="47" t="s">
+      <c r="E121" s="33" t="s">
         <v>350</v>
       </c>
       <c r="F121" s="50">
@@ -4516,7 +4516,7 @@
       <c r="D122" s="49">
         <v>13.74</v>
       </c>
-      <c r="E122" s="47" t="s">
+      <c r="E122" s="33" t="s">
         <v>351</v>
       </c>
       <c r="F122" s="50">
@@ -4534,7 +4534,7 @@
       <c r="D123" s="49">
         <v>16.670000000000002</v>
       </c>
-      <c r="E123" s="47" t="s">
+      <c r="E123" s="33" t="s">
         <v>352</v>
       </c>
       <c r="F123" s="50">
@@ -4554,7 +4554,7 @@
       <c r="D124" s="49">
         <v>24.490000000000002</v>
       </c>
-      <c r="E124" s="44" t="s">
+      <c r="E124" s="32" t="s">
         <v>353</v>
       </c>
       <c r="F124" s="50">
@@ -4574,11 +4574,11 @@
       <c r="D125" s="49">
         <v>14.31</v>
       </c>
-      <c r="E125" s="44" t="s">
+      <c r="E125" s="32" t="s">
         <v>354</v>
       </c>
       <c r="F125" s="50">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
@@ -4594,7 +4594,7 @@
       <c r="D126" s="49">
         <v>21.54</v>
       </c>
-      <c r="E126" s="44" t="s">
+      <c r="E126" s="32" t="s">
         <v>355</v>
       </c>
       <c r="F126" s="50">
@@ -4612,7 +4612,7 @@
       <c r="D127" s="49">
         <v>48.35</v>
       </c>
-      <c r="E127" s="47" t="s">
+      <c r="E127" s="33" t="s">
         <v>356</v>
       </c>
       <c r="F127" s="50">
@@ -4632,11 +4632,11 @@
       <c r="D128" s="49">
         <v>38.24</v>
       </c>
-      <c r="E128" s="44" t="s">
+      <c r="E128" s="32" t="s">
         <v>357</v>
       </c>
       <c r="F128" s="50">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
@@ -4652,7 +4652,7 @@
       <c r="D129" s="49">
         <v>2.5300000000000002</v>
       </c>
-      <c r="E129" s="44" t="s">
+      <c r="E129" s="32" t="s">
         <v>358</v>
       </c>
       <c r="F129" s="50">
@@ -4672,7 +4672,7 @@
       <c r="D130" s="49">
         <v>16.7</v>
       </c>
-      <c r="E130" s="44" t="s">
+      <c r="E130" s="32" t="s">
         <v>359</v>
       </c>
       <c r="F130" s="50">
@@ -4692,7 +4692,7 @@
       <c r="D131" s="49">
         <v>19.490000000000002</v>
       </c>
-      <c r="E131" s="48" t="s">
+      <c r="E131" s="34" t="s">
         <v>360</v>
       </c>
       <c r="F131" s="50">
@@ -4710,7 +4710,7 @@
       <c r="D132" s="49">
         <v>14.96</v>
       </c>
-      <c r="E132" s="47" t="s">
+      <c r="E132" s="33" t="s">
         <v>361</v>
       </c>
       <c r="F132" s="50">
@@ -4730,7 +4730,7 @@
       <c r="D133" s="49">
         <v>36.78</v>
       </c>
-      <c r="E133" s="44" t="s">
+      <c r="E133" s="32" t="s">
         <v>362</v>
       </c>
       <c r="F133" s="50">
@@ -4748,7 +4748,7 @@
       <c r="D134" s="49">
         <v>21.6</v>
       </c>
-      <c r="E134" s="47" t="s">
+      <c r="E134" s="33" t="s">
         <v>363</v>
       </c>
       <c r="F134" s="50">
@@ -4768,11 +4768,11 @@
       <c r="D135" s="49">
         <v>8.24</v>
       </c>
-      <c r="E135" s="44" t="s">
+      <c r="E135" s="32" t="s">
         <v>364</v>
       </c>
       <c r="F135" s="50">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
@@ -4788,11 +4788,11 @@
       <c r="D136" s="49">
         <v>3.7</v>
       </c>
-      <c r="E136" s="44" t="s">
+      <c r="E136" s="32" t="s">
         <v>365</v>
       </c>
       <c r="F136" s="50">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
@@ -4808,11 +4808,11 @@
       <c r="D137" s="49">
         <v>3.42</v>
       </c>
-      <c r="E137" s="44" t="s">
+      <c r="E137" s="32" t="s">
         <v>366</v>
       </c>
       <c r="F137" s="50">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
@@ -4826,7 +4826,7 @@
       <c r="D138" s="49">
         <v>4.59</v>
       </c>
-      <c r="E138" s="47" t="s">
+      <c r="E138" s="33" t="s">
         <v>367</v>
       </c>
       <c r="F138" s="50">
@@ -4844,7 +4844,7 @@
       <c r="D139" s="49">
         <v>12.4</v>
       </c>
-      <c r="E139" s="47" t="s">
+      <c r="E139" s="33" t="s">
         <v>368</v>
       </c>
       <c r="F139" s="50">
@@ -4864,7 +4864,7 @@
       <c r="D140" s="49">
         <v>10.16</v>
       </c>
-      <c r="E140" s="44" t="s">
+      <c r="E140" s="32" t="s">
         <v>369</v>
       </c>
       <c r="F140" s="50">
@@ -4884,11 +4884,11 @@
       <c r="D141" s="49">
         <v>9.15</v>
       </c>
-      <c r="E141" s="44" t="s">
+      <c r="E141" s="32" t="s">
         <v>370</v>
       </c>
       <c r="F141" s="50">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
@@ -4900,13 +4900,13 @@
         <v>468</v>
       </c>
       <c r="D142" s="49">
-        <v>11.69</v>
-      </c>
-      <c r="E142" s="47" t="s">
+        <v>12.02</v>
+      </c>
+      <c r="E142" s="33" t="s">
         <v>371</v>
       </c>
       <c r="F142" s="50">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
@@ -4922,11 +4922,11 @@
       <c r="D143" s="49">
         <v>6.32</v>
       </c>
-      <c r="E143" s="44" t="s">
+      <c r="E143" s="32" t="s">
         <v>372</v>
       </c>
       <c r="F143" s="50">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
@@ -4940,13 +4940,13 @@
         <v>468</v>
       </c>
       <c r="D144" s="49">
-        <v>4.96</v>
-      </c>
-      <c r="E144" s="44" t="s">
+        <v>6.23</v>
+      </c>
+      <c r="E144" s="32" t="s">
         <v>373</v>
       </c>
       <c r="F144" s="50">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
@@ -4960,7 +4960,7 @@
       <c r="D145" s="49">
         <v>9.8000000000000007</v>
       </c>
-      <c r="E145" s="47" t="s">
+      <c r="E145" s="33" t="s">
         <v>374</v>
       </c>
       <c r="F145" s="50">
@@ -4980,11 +4980,11 @@
       <c r="D146" s="49">
         <v>8.14</v>
       </c>
-      <c r="E146" s="44" t="s">
+      <c r="E146" s="32" t="s">
         <v>375</v>
       </c>
       <c r="F146" s="50">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
@@ -4998,7 +4998,7 @@
       <c r="D147" s="49">
         <v>5</v>
       </c>
-      <c r="E147" s="47" t="s">
+      <c r="E147" s="33" t="s">
         <v>376</v>
       </c>
       <c r="F147" s="50">
@@ -5022,7 +5022,7 @@
         <v>404</v>
       </c>
       <c r="F148" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
@@ -5042,7 +5042,7 @@
         <v>405</v>
       </c>
       <c r="F149" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
@@ -5062,7 +5062,7 @@
         <v>438</v>
       </c>
       <c r="F150" s="52">
-        <v>244</v>
+        <v>250</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
@@ -5164,13 +5164,13 @@
         <v>468</v>
       </c>
       <c r="D156" s="51">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="E156" s="29" t="s">
         <v>444</v>
       </c>
       <c r="F156" s="52">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
@@ -5190,7 +5190,7 @@
         <v>445</v>
       </c>
       <c r="F157" s="52">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
@@ -5230,7 +5230,7 @@
         <v>447</v>
       </c>
       <c r="F159" s="52">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
@@ -5250,7 +5250,7 @@
         <v>448</v>
       </c>
       <c r="F160" s="52">
-        <v>176</v>
+        <v>151</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
@@ -5270,7 +5270,7 @@
         <v>449</v>
       </c>
       <c r="F161" s="52">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
@@ -5290,7 +5290,7 @@
         <v>450</v>
       </c>
       <c r="F162" s="52">
-        <v>251</v>
+        <v>180</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
@@ -5310,7 +5310,7 @@
         <v>451</v>
       </c>
       <c r="F163" s="52">
-        <v>135</v>
+        <v>85</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
@@ -5330,7 +5330,7 @@
         <v>452</v>
       </c>
       <c r="F164" s="52">
-        <v>87</v>
+        <v>35</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/prix.xlsx
+++ b/prix/prix.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\platres-et-enduits\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C81279A8-660B-4B3F-8F0D-8A24412B6A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3972BC67-59DF-49DB-B649-ACBEA46CA44B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
+    <workbookView xWindow="23016" yWindow="84" windowWidth="19116" windowHeight="10884" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -2150,13 +2150,13 @@
       <c r="C2" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="D2" s="35">
+      <c r="D2" s="37">
         <v>24.26</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="36">
+      <c r="F2" s="38">
         <v>6</v>
       </c>
     </row>
@@ -2170,13 +2170,13 @@
       <c r="C3" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="D3" s="35">
+      <c r="D3" s="37">
         <v>23.1</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="36">
+      <c r="F3" s="38">
         <v>5</v>
       </c>
     </row>
@@ -2188,14 +2188,14 @@
       <c r="C4" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="D4" s="35">
+      <c r="D4" s="37">
         <v>7.8</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="36">
-        <v>2</v>
+      <c r="F4" s="38">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -2206,14 +2206,14 @@
       <c r="C5" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="37">
         <v>7.66</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="36">
-        <v>16</v>
+      <c r="F5" s="38">
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -2226,13 +2226,13 @@
       <c r="C6" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="D6" s="35">
+      <c r="D6" s="37">
         <v>17.16</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="36">
+      <c r="F6" s="38">
         <v>4</v>
       </c>
     </row>
@@ -2246,14 +2246,14 @@
       <c r="C7" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="D7" s="35">
+      <c r="D7" s="37">
         <v>16.830000000000002</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="36">
-        <v>11</v>
+      <c r="F7" s="38">
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -2266,14 +2266,14 @@
       <c r="C8" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D8" s="35">
+      <c r="D8" s="37">
         <v>8.6</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="36">
-        <v>22</v>
+      <c r="F8" s="38">
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -2286,14 +2286,14 @@
       <c r="C9" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="D9" s="35">
+      <c r="D9" s="37">
         <v>32.130000000000003</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="36">
-        <v>35</v>
+      <c r="F9" s="38">
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -2306,14 +2306,14 @@
       <c r="C10" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="D10" s="35">
+      <c r="D10" s="37">
         <v>33.090000000000003</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="36">
-        <v>11</v>
+      <c r="F10" s="38">
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -2324,13 +2324,13 @@
       <c r="C11" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="37">
         <v>8.86</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="36">
+      <c r="F11" s="38">
         <v>-1</v>
       </c>
     </row>
@@ -2344,14 +2344,14 @@
       <c r="C12" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="D12" s="35">
+      <c r="D12" s="37">
         <v>19.41</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="36">
-        <v>4</v>
+      <c r="F12" s="38">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -2364,13 +2364,13 @@
       <c r="C13" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="D13" s="35">
+      <c r="D13" s="37">
         <v>65.33</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F13" s="36">
+      <c r="F13" s="38">
         <v>3</v>
       </c>
     </row>
@@ -2382,14 +2382,14 @@
       <c r="C14" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D14" s="35">
+      <c r="D14" s="37">
         <v>11.82</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="36">
-        <v>10</v>
+      <c r="F14" s="38">
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -2402,14 +2402,14 @@
       <c r="C15" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D15" s="35">
+      <c r="D15" s="37">
         <v>35.56</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="36">
-        <v>5</v>
+      <c r="F15" s="38">
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -2422,13 +2422,13 @@
       <c r="C16" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="D16" s="35">
+      <c r="D16" s="37">
         <v>89.14</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="36">
+      <c r="F16" s="38">
         <v>4</v>
       </c>
     </row>
@@ -2442,13 +2442,13 @@
       <c r="C17" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="D17" s="35">
+      <c r="D17" s="37">
         <v>24.32</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="36">
+      <c r="F17" s="38">
         <v>4</v>
       </c>
     </row>
@@ -2462,13 +2462,13 @@
       <c r="C18" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="D18" s="35">
+      <c r="D18" s="37">
         <v>31.240000000000002</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F18" s="36">
+      <c r="F18" s="38">
         <v>4</v>
       </c>
     </row>
@@ -2482,13 +2482,13 @@
       <c r="C19" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D19" s="35">
+      <c r="D19" s="37">
         <v>28.82</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F19" s="36">
+      <c r="F19" s="38">
         <v>4</v>
       </c>
     </row>
@@ -2502,13 +2502,13 @@
       <c r="C20" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="D20" s="35">
+      <c r="D20" s="37">
         <v>72.710000000000008</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F20" s="36">
+      <c r="F20" s="38">
         <v>3</v>
       </c>
     </row>
@@ -2522,13 +2522,13 @@
       <c r="C21" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="D21" s="35">
+      <c r="D21" s="37">
         <v>9.84</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="F21" s="36">
+      <c r="F21" s="38">
         <v>12</v>
       </c>
     </row>
@@ -2540,13 +2540,13 @@
       <c r="C22" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="D22" s="35">
+      <c r="D22" s="37">
         <v>23.8</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="36">
+      <c r="F22" s="38">
         <v>2</v>
       </c>
     </row>
@@ -2558,13 +2558,13 @@
       <c r="C23" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="D23" s="35">
+      <c r="D23" s="37">
         <v>35.68</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="F23" s="36">
+      <c r="F23" s="38">
         <v>0</v>
       </c>
     </row>
@@ -2576,14 +2576,14 @@
       <c r="C24" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="D24" s="35">
+      <c r="D24" s="37">
         <v>18.22</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F24" s="36">
-        <v>8</v>
+      <c r="F24" s="38">
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -2594,14 +2594,14 @@
       <c r="C25" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="D25" s="35">
+      <c r="D25" s="37">
         <v>18.150000000000002</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F25" s="36">
-        <v>3</v>
+      <c r="F25" s="38">
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -2614,14 +2614,14 @@
       <c r="C26" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="D26" s="35">
+      <c r="D26" s="37">
         <v>15.63</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F26" s="36">
-        <v>18</v>
+      <c r="F26" s="38">
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -2634,13 +2634,13 @@
       <c r="C27" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="D27" s="35">
+      <c r="D27" s="37">
         <v>29.5</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F27" s="36">
+      <c r="F27" s="38">
         <v>3</v>
       </c>
     </row>
@@ -2654,14 +2654,14 @@
       <c r="C28" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="D28" s="35">
+      <c r="D28" s="37">
         <v>49.51</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="F28" s="36">
-        <v>10</v>
+      <c r="F28" s="38">
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -2674,13 +2674,13 @@
       <c r="C29" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="D29" s="35">
+      <c r="D29" s="37">
         <v>64</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="F29" s="36">
+      <c r="F29" s="38">
         <v>1</v>
       </c>
     </row>
@@ -2692,13 +2692,13 @@
       <c r="C30" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="D30" s="35">
+      <c r="D30" s="37">
         <v>18.37</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F30" s="36">
+      <c r="F30" s="38">
         <v>0</v>
       </c>
     </row>
@@ -2710,13 +2710,13 @@
       <c r="C31" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="D31" s="35">
+      <c r="D31" s="37">
         <v>39.57</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F31" s="36">
+      <c r="F31" s="38">
         <v>-1</v>
       </c>
     </row>
@@ -2730,14 +2730,14 @@
       <c r="C32" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="D32" s="35">
+      <c r="D32" s="37">
         <v>44.78</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="F32" s="36">
-        <v>1</v>
+      <c r="F32" s="38">
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -2748,13 +2748,13 @@
       <c r="C33" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="D33" s="35">
+      <c r="D33" s="37">
         <v>44.61</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="F33" s="36">
+      <c r="F33" s="38">
         <v>3</v>
       </c>
     </row>
@@ -2766,13 +2766,13 @@
       <c r="C34" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="D34" s="35">
+      <c r="D34" s="37">
         <v>25.22</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="F34" s="36">
+      <c r="F34" s="38">
         <v>1</v>
       </c>
     </row>
@@ -2784,13 +2784,13 @@
       <c r="C35" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="D35" s="35">
+      <c r="D35" s="37">
         <v>52.01</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F35" s="36">
+      <c r="F35" s="38">
         <v>2</v>
       </c>
     </row>
@@ -2802,14 +2802,14 @@
       <c r="C36" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="D36" s="35">
+      <c r="D36" s="37">
         <v>24.32</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="F36" s="36">
-        <v>7</v>
+      <c r="F36" s="38">
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -2822,14 +2822,14 @@
       <c r="C37" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="D37" s="37">
-        <v>14.59</v>
+      <c r="D37" s="39">
+        <v>15.06</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="F37" s="38">
-        <v>64</v>
+      <c r="F37" s="40">
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -2842,14 +2842,14 @@
       <c r="C38" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="D38" s="37">
+      <c r="D38" s="39">
         <v>9.57</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F38" s="38">
-        <v>23</v>
+      <c r="F38" s="40">
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -2862,14 +2862,14 @@
       <c r="C39" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="D39" s="37">
+      <c r="D39" s="39">
         <v>13.65</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F39" s="38">
-        <v>62</v>
+      <c r="F39" s="40">
+        <v>57</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -2882,14 +2882,14 @@
       <c r="C40" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="D40" s="37">
+      <c r="D40" s="39">
         <v>12.86</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F40" s="38">
-        <v>301</v>
+      <c r="F40" s="40">
+        <v>448</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -2902,14 +2902,14 @@
       <c r="C41" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="D41" s="37">
+      <c r="D41" s="39">
         <v>18.21</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F41" s="38">
-        <v>35</v>
+      <c r="F41" s="40">
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -2922,14 +2922,14 @@
       <c r="C42" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="D42" s="37">
-        <v>15.92</v>
+      <c r="D42" s="39">
+        <v>16.48</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F42" s="38">
-        <v>74</v>
+      <c r="F42" s="40">
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -2949,7 +2949,7 @@
         <v>12</v>
       </c>
       <c r="F43" s="5">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -2963,13 +2963,13 @@
         <v>228</v>
       </c>
       <c r="D44" s="3">
-        <v>32.04</v>
+        <v>30.2</v>
       </c>
       <c r="E44" s="15" t="s">
         <v>13</v>
       </c>
       <c r="F44" s="5">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -2989,7 +2989,7 @@
         <v>14</v>
       </c>
       <c r="F45" s="5">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -3003,13 +3003,13 @@
         <v>239</v>
       </c>
       <c r="D46" s="3">
-        <v>6.6400000000000006</v>
+        <v>7.08</v>
       </c>
       <c r="E46" s="16" t="s">
         <v>15</v>
       </c>
       <c r="F46" s="5">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -3022,14 +3022,14 @@
       <c r="C47" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="D47" s="39">
+      <c r="D47" s="41">
         <v>5.5200000000000005</v>
       </c>
       <c r="E47" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="F47" s="40">
-        <v>231.2</v>
+      <c r="F47" s="42">
+        <v>230.40000000000003</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -3042,14 +3042,14 @@
       <c r="C48" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="D48" s="39">
+      <c r="D48" s="41">
         <v>5.25</v>
       </c>
       <c r="E48" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="F48" s="40">
-        <v>418.08000000000004</v>
+      <c r="F48" s="42">
+        <v>321.36</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -3062,14 +3062,14 @@
       <c r="C49" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D49" s="39">
-        <v>4.59</v>
+      <c r="D49" s="41">
+        <v>4.74</v>
       </c>
       <c r="E49" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="F49" s="40">
-        <v>207.60000000000034</v>
+      <c r="F49" s="42">
+        <v>265.32000000000028</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -3082,14 +3082,14 @@
       <c r="C50" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D50" s="39">
-        <v>5.07</v>
+      <c r="D50" s="41">
+        <v>4.66</v>
       </c>
       <c r="E50" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="F50" s="40">
-        <v>518.29999999999973</v>
+      <c r="F50" s="42">
+        <v>377.17999999999972</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -3102,13 +3102,13 @@
       <c r="C51" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="D51" s="39">
+      <c r="D51" s="41">
         <v>5.26</v>
       </c>
       <c r="E51" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="F51" s="40">
+      <c r="F51" s="42">
         <v>0</v>
       </c>
     </row>
@@ -3122,14 +3122,14 @@
       <c r="C52" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D52" s="39">
-        <v>4.96</v>
+      <c r="D52" s="41">
+        <v>2.65</v>
       </c>
       <c r="E52" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="F52" s="40">
-        <v>201.23999999999907</v>
+      <c r="F52" s="42">
+        <v>472.67999999999915</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -3142,13 +3142,13 @@
       <c r="C53" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="D53" s="39">
+      <c r="D53" s="41">
         <v>5.26</v>
       </c>
       <c r="E53" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="F53" s="40">
+      <c r="F53" s="42">
         <v>6.7199999999999758</v>
       </c>
     </row>
@@ -3162,13 +3162,13 @@
       <c r="C54" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D54" s="39">
+      <c r="D54" s="41">
         <v>5.13</v>
       </c>
       <c r="E54" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="F54" s="40">
+      <c r="F54" s="42">
         <v>0</v>
       </c>
     </row>
@@ -3182,14 +3182,14 @@
       <c r="C55" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D55" s="39">
-        <v>4.66</v>
+      <c r="D55" s="41">
+        <v>4.83</v>
       </c>
       <c r="E55" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="F55" s="40">
-        <v>143.52199999999806</v>
+      <c r="F55" s="42">
+        <v>298.14199999999801</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -3202,14 +3202,14 @@
       <c r="C56" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D56" s="39">
-        <v>8.68</v>
+      <c r="D56" s="41">
+        <v>8.18</v>
       </c>
       <c r="E56" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="F56" s="40">
-        <v>148.21999999999906</v>
+      <c r="F56" s="42">
+        <v>254.29999999999907</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
@@ -3222,14 +3222,14 @@
       <c r="C57" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D57" s="39">
-        <v>8.1999999999999993</v>
+      <c r="D57" s="41">
+        <v>8.48</v>
       </c>
       <c r="E57" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="F57" s="40">
-        <v>161.24000000000086</v>
+      <c r="F57" s="42">
+        <v>298.52000000000089</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -3242,13 +3242,13 @@
       <c r="C58" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D58" s="39">
+      <c r="D58" s="41">
         <v>7.25</v>
       </c>
       <c r="E58" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="F58" s="40">
+      <c r="F58" s="42">
         <v>0</v>
       </c>
     </row>
@@ -3262,13 +3262,13 @@
       <c r="C59" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="D59" s="39">
+      <c r="D59" s="41">
         <v>8.1300000000000008</v>
       </c>
       <c r="E59" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="F59" s="40">
+      <c r="F59" s="42">
         <v>115.43999999999997</v>
       </c>
     </row>
@@ -3282,14 +3282,14 @@
       <c r="C60" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="D60" s="39">
+      <c r="D60" s="41">
         <v>8.43</v>
       </c>
       <c r="E60" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="F60" s="40">
-        <v>98.279999999999973</v>
+      <c r="F60" s="42">
+        <v>85.799999999999969</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
@@ -3302,14 +3302,14 @@
       <c r="C61" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D61" s="39">
+      <c r="D61" s="41">
         <v>8.4499999999999993</v>
       </c>
       <c r="E61" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="F61" s="40">
-        <v>87.360000000000113</v>
+      <c r="F61" s="42">
+        <v>84.240000000000109</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -3322,13 +3322,13 @@
       <c r="C62" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D62" s="39">
+      <c r="D62" s="41">
         <v>9.33</v>
       </c>
       <c r="E62" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="F62" s="40">
+      <c r="F62" s="42">
         <v>0</v>
       </c>
     </row>
@@ -3342,14 +3342,14 @@
       <c r="C63" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="D63" s="41">
-        <v>23.9</v>
+      <c r="D63" s="43">
+        <v>23.900000000000002</v>
       </c>
       <c r="E63" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="F63" s="42">
-        <v>9</v>
+      <c r="F63" s="44">
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
@@ -3362,14 +3362,14 @@
       <c r="C64" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="D64" s="41">
+      <c r="D64" s="43">
         <v>11.120000000000001</v>
       </c>
       <c r="E64" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="F64" s="42">
-        <v>7</v>
+      <c r="F64" s="44">
+        <v>4</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
@@ -3382,13 +3382,13 @@
       <c r="C65" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="D65" s="41">
+      <c r="D65" s="43">
         <v>12.58</v>
       </c>
       <c r="E65" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="F65" s="42">
+      <c r="F65" s="44">
         <v>12</v>
       </c>
     </row>
@@ -3402,14 +3402,14 @@
       <c r="C66" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="D66" s="41">
-        <v>1.78</v>
+      <c r="D66" s="43">
+        <v>1.84</v>
       </c>
       <c r="E66" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="F66" s="42">
-        <v>52</v>
+      <c r="F66" s="44">
+        <v>22</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
@@ -3422,14 +3422,14 @@
       <c r="C67" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="D67" s="41">
-        <v>5.48</v>
+      <c r="D67" s="43">
+        <v>5.72</v>
       </c>
       <c r="E67" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="F67" s="42">
-        <v>2</v>
+      <c r="F67" s="44">
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
@@ -3440,13 +3440,13 @@
       <c r="C68" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="D68" s="41">
+      <c r="D68" s="43">
         <v>5</v>
       </c>
       <c r="E68" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="F68" s="42">
+      <c r="F68" s="44">
         <v>0</v>
       </c>
     </row>
@@ -3460,13 +3460,13 @@
       <c r="C69" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="D69" s="41">
+      <c r="D69" s="43">
         <v>5.49</v>
       </c>
       <c r="E69" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="F69" s="42">
+      <c r="F69" s="44">
         <v>0</v>
       </c>
     </row>
@@ -3478,13 +3478,13 @@
       <c r="C70" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D70" s="41">
+      <c r="D70" s="43">
         <v>19.41</v>
       </c>
       <c r="E70" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="F70" s="42">
+      <c r="F70" s="44">
         <v>0</v>
       </c>
     </row>
@@ -3498,14 +3498,14 @@
       <c r="C71" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="D71" s="43">
+      <c r="D71" s="45">
         <v>25.8</v>
       </c>
       <c r="E71" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="F71" s="44">
-        <v>3</v>
+      <c r="F71" s="46">
+        <v>1</v>
       </c>
       <c r="G71" s="19"/>
     </row>
@@ -3519,13 +3519,13 @@
       <c r="C72" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="D72" s="43">
+      <c r="D72" s="45">
         <v>27.3</v>
       </c>
       <c r="E72" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="F72" s="44">
+      <c r="F72" s="46">
         <v>0</v>
       </c>
     </row>
@@ -3539,13 +3539,13 @@
       <c r="C73" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="D73" s="43">
+      <c r="D73" s="45">
         <v>40.119999999999997</v>
       </c>
       <c r="E73" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="F73" s="44">
+      <c r="F73" s="46">
         <v>5</v>
       </c>
     </row>
@@ -3559,14 +3559,14 @@
       <c r="C74" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="D74" s="43">
+      <c r="D74" s="45">
         <v>16.170000000000002</v>
       </c>
       <c r="E74" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="F74" s="44">
-        <v>9</v>
+      <c r="F74" s="46">
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
@@ -3579,14 +3579,14 @@
       <c r="C75" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="D75" s="43">
+      <c r="D75" s="45">
         <v>22.05</v>
       </c>
       <c r="E75" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="F75" s="44">
-        <v>4</v>
+      <c r="F75" s="46">
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
@@ -3599,13 +3599,13 @@
       <c r="C76" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="D76" s="43">
+      <c r="D76" s="45">
         <v>25.810000000000002</v>
       </c>
       <c r="E76" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="F76" s="44">
+      <c r="F76" s="46">
         <v>6</v>
       </c>
     </row>
@@ -3619,14 +3619,14 @@
       <c r="C77" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="D77" s="43">
+      <c r="D77" s="45">
         <v>13.07</v>
       </c>
       <c r="E77" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="F77" s="44">
-        <v>0</v>
+      <c r="F77" s="46">
+        <v>18</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
@@ -3639,13 +3639,13 @@
       <c r="C78" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="D78" s="43">
+      <c r="D78" s="45">
         <v>3.22</v>
       </c>
       <c r="E78" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="F78" s="44">
+      <c r="F78" s="46">
         <v>9</v>
       </c>
     </row>
@@ -3659,13 +3659,13 @@
       <c r="C79" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="D79" s="43">
+      <c r="D79" s="45">
         <v>16.63</v>
       </c>
       <c r="E79" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="F79" s="44">
+      <c r="F79" s="46">
         <v>36</v>
       </c>
     </row>
@@ -3679,14 +3679,14 @@
       <c r="C80" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="D80" s="43">
+      <c r="D80" s="45">
         <v>6.36</v>
       </c>
       <c r="E80" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="F80" s="44">
-        <v>4</v>
+      <c r="F80" s="46">
+        <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
@@ -3699,14 +3699,14 @@
       <c r="C81" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D81" s="43">
+      <c r="D81" s="45">
         <v>15.73</v>
       </c>
       <c r="E81" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="F81" s="44">
-        <v>-20</v>
+      <c r="F81" s="46">
+        <v>-10</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
@@ -3719,14 +3719,14 @@
       <c r="C82" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="D82" s="43">
+      <c r="D82" s="45">
         <v>3.92</v>
       </c>
       <c r="E82" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="F82" s="44">
-        <v>11</v>
+      <c r="F82" s="46">
+        <v>10</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
@@ -3739,14 +3739,14 @@
       <c r="C83" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D83" s="43">
+      <c r="D83" s="45">
         <v>21.95</v>
       </c>
       <c r="E83" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="F83" s="44">
-        <v>5</v>
+      <c r="F83" s="46">
+        <v>2</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
@@ -3759,14 +3759,14 @@
       <c r="C84" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D84" s="43">
+      <c r="D84" s="45">
         <v>4.99</v>
       </c>
       <c r="E84" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="F84" s="44">
-        <v>12</v>
+      <c r="F84" s="46">
+        <v>8</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
@@ -3779,14 +3779,14 @@
       <c r="C85" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D85" s="43">
+      <c r="D85" s="45">
         <v>7.36</v>
       </c>
       <c r="E85" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="F85" s="44">
-        <v>10</v>
+      <c r="F85" s="46">
+        <v>19</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
@@ -3799,13 +3799,13 @@
       <c r="C86" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="D86" s="43">
+      <c r="D86" s="45">
         <v>30.52</v>
       </c>
       <c r="E86" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="F86" s="44">
+      <c r="F86" s="46">
         <v>6</v>
       </c>
     </row>
@@ -3819,14 +3819,14 @@
       <c r="C87" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="D87" s="43">
+      <c r="D87" s="45">
         <v>6.05</v>
       </c>
       <c r="E87" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="F87" s="44">
-        <v>12</v>
+      <c r="F87" s="46">
+        <v>11</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
@@ -3839,13 +3839,13 @@
       <c r="C88" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="D88" s="43">
+      <c r="D88" s="45">
         <v>4.67</v>
       </c>
       <c r="E88" s="22" t="s">
         <v>168</v>
       </c>
-      <c r="F88" s="44">
+      <c r="F88" s="46">
         <v>5</v>
       </c>
     </row>
@@ -3859,13 +3859,13 @@
       <c r="C89" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="D89" s="43">
+      <c r="D89" s="45">
         <v>15.58</v>
       </c>
       <c r="E89" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="F89" s="44">
+      <c r="F89" s="46">
         <v>0</v>
       </c>
     </row>
@@ -3879,14 +3879,14 @@
       <c r="C90" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="D90" s="43">
+      <c r="D90" s="45">
         <v>18.63</v>
       </c>
       <c r="E90" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="F90" s="44">
-        <v>6</v>
+      <c r="F90" s="46">
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
@@ -3899,13 +3899,13 @@
       <c r="C91" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="D91" s="43">
+      <c r="D91" s="45">
         <v>11.33</v>
       </c>
       <c r="E91" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="F91" s="44">
+      <c r="F91" s="46">
         <v>6</v>
       </c>
     </row>
@@ -3919,14 +3919,14 @@
       <c r="C92" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="D92" s="43">
+      <c r="D92" s="45">
         <v>22.97</v>
       </c>
       <c r="E92" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="F92" s="44">
-        <v>6</v>
+      <c r="F92" s="46">
+        <v>15</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
@@ -3939,13 +3939,13 @@
       <c r="C93" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="D93" s="43">
+      <c r="D93" s="45">
         <v>18.150000000000002</v>
       </c>
       <c r="E93" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="F93" s="44">
+      <c r="F93" s="46">
         <v>5</v>
       </c>
     </row>
@@ -3959,13 +3959,13 @@
       <c r="C94" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="D94" s="43">
+      <c r="D94" s="45">
         <v>12.83</v>
       </c>
       <c r="E94" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="F94" s="44">
+      <c r="F94" s="46">
         <v>7</v>
       </c>
     </row>
@@ -3979,13 +3979,13 @@
       <c r="C95" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="D95" s="43">
+      <c r="D95" s="45">
         <v>42.25</v>
       </c>
       <c r="E95" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="F95" s="44">
+      <c r="F95" s="46">
         <v>11</v>
       </c>
     </row>
@@ -3999,13 +3999,13 @@
       <c r="C96" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="D96" s="43">
+      <c r="D96" s="45">
         <v>17.38</v>
       </c>
       <c r="E96" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="F96" s="44">
+      <c r="F96" s="46">
         <v>3</v>
       </c>
     </row>
@@ -4019,13 +4019,13 @@
       <c r="C97" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="D97" s="43">
+      <c r="D97" s="45">
         <v>27.18</v>
       </c>
       <c r="E97" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="F97" s="44">
+      <c r="F97" s="46">
         <v>3</v>
       </c>
     </row>
@@ -4039,13 +4039,13 @@
       <c r="C98" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="D98" s="43">
+      <c r="D98" s="45">
         <v>34.51</v>
       </c>
       <c r="E98" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="F98" s="44">
+      <c r="F98" s="46">
         <v>7</v>
       </c>
     </row>
@@ -4059,13 +4059,13 @@
       <c r="C99" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="D99" s="43">
+      <c r="D99" s="45">
         <v>42.57</v>
       </c>
       <c r="E99" s="22" t="s">
         <v>179</v>
       </c>
-      <c r="F99" s="44">
+      <c r="F99" s="46">
         <v>7</v>
       </c>
     </row>
@@ -4079,13 +4079,13 @@
       <c r="C100" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="D100" s="43">
+      <c r="D100" s="45">
         <v>21.68</v>
       </c>
       <c r="E100" s="22" t="s">
         <v>180</v>
       </c>
-      <c r="F100" s="44">
+      <c r="F100" s="46">
         <v>6</v>
       </c>
     </row>
@@ -4099,14 +4099,14 @@
       <c r="C101" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D101" s="43">
+      <c r="D101" s="45">
         <v>24.78</v>
       </c>
       <c r="E101" s="22" t="s">
         <v>181</v>
       </c>
-      <c r="F101" s="44">
-        <v>4</v>
+      <c r="F101" s="46">
+        <v>9</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
@@ -4119,13 +4119,13 @@
       <c r="C102" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="D102" s="43">
+      <c r="D102" s="45">
         <v>16.63</v>
       </c>
       <c r="E102" s="22" t="s">
         <v>182</v>
       </c>
-      <c r="F102" s="44">
+      <c r="F102" s="46">
         <v>0</v>
       </c>
     </row>
@@ -4139,14 +4139,14 @@
       <c r="C103" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="D103" s="43">
+      <c r="D103" s="45">
         <v>19.72</v>
       </c>
       <c r="E103" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="F103" s="44">
-        <v>3</v>
+      <c r="F103" s="46">
+        <v>12</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
@@ -4159,13 +4159,13 @@
       <c r="C104" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="D104" s="43">
+      <c r="D104" s="45">
         <v>33.01</v>
       </c>
       <c r="E104" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="F104" s="44">
+      <c r="F104" s="46">
         <v>15</v>
       </c>
     </row>
@@ -4179,14 +4179,14 @@
       <c r="C105" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="D105" s="45">
+      <c r="D105" s="35">
         <v>28.75</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F105" s="46">
-        <v>11</v>
+      <c r="F105" s="36">
+        <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
@@ -4199,14 +4199,14 @@
       <c r="C106" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="D106" s="45">
+      <c r="D106" s="35">
         <v>58.82</v>
       </c>
       <c r="E106" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F106" s="46">
-        <v>8</v>
+      <c r="F106" s="36">
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
@@ -4219,14 +4219,14 @@
       <c r="C107" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="D107" s="45">
+      <c r="D107" s="35">
         <v>23.490000000000002</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F107" s="46">
-        <v>5</v>
+      <c r="F107" s="36">
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
@@ -4239,14 +4239,14 @@
       <c r="C108" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="D108" s="45">
+      <c r="D108" s="35">
         <v>59.9</v>
       </c>
       <c r="E108" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F108" s="46">
-        <v>8</v>
+      <c r="F108" s="36">
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
@@ -4266,7 +4266,7 @@
         <v>327</v>
       </c>
       <c r="F109" s="48">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
@@ -4320,13 +4320,13 @@
         <v>468</v>
       </c>
       <c r="D112" s="47">
-        <v>30.21</v>
+        <v>33.230000000000004</v>
       </c>
       <c r="E112" s="30" t="s">
         <v>330</v>
       </c>
       <c r="F112" s="48">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
@@ -4340,13 +4340,13 @@
         <v>468</v>
       </c>
       <c r="D113" s="47">
-        <v>33.06</v>
+        <v>36.36</v>
       </c>
       <c r="E113" s="30" t="s">
         <v>331</v>
       </c>
       <c r="F113" s="48">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
@@ -4366,7 +4366,7 @@
         <v>332</v>
       </c>
       <c r="F114" s="48">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
@@ -4386,7 +4386,7 @@
         <v>333</v>
       </c>
       <c r="F115" s="48">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
@@ -4400,7 +4400,7 @@
         <v>468</v>
       </c>
       <c r="D116" s="47">
-        <v>14.33</v>
+        <v>15.67</v>
       </c>
       <c r="E116" s="30" t="s">
         <v>334</v>
@@ -4420,13 +4420,13 @@
         <v>468</v>
       </c>
       <c r="D117" s="47">
-        <v>14.33</v>
+        <v>15.67</v>
       </c>
       <c r="E117" s="30" t="s">
         <v>335</v>
       </c>
       <c r="F117" s="48">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
@@ -4464,7 +4464,7 @@
         <v>337</v>
       </c>
       <c r="F119" s="48">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
@@ -4478,13 +4478,13 @@
         <v>468</v>
       </c>
       <c r="D120" s="49">
-        <v>15.6</v>
+        <v>17.059999999999999</v>
       </c>
       <c r="E120" s="32" t="s">
         <v>349</v>
       </c>
       <c r="F120" s="50">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
@@ -4572,13 +4572,13 @@
         <v>468</v>
       </c>
       <c r="D125" s="49">
-        <v>14.31</v>
+        <v>15.67</v>
       </c>
       <c r="E125" s="32" t="s">
         <v>354</v>
       </c>
       <c r="F125" s="50">
-        <v>-4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
@@ -4636,7 +4636,7 @@
         <v>357</v>
       </c>
       <c r="F128" s="50">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
@@ -4650,13 +4650,13 @@
         <v>468</v>
       </c>
       <c r="D129" s="49">
-        <v>2.5300000000000002</v>
+        <v>3.2800000000000002</v>
       </c>
       <c r="E129" s="32" t="s">
         <v>358</v>
       </c>
       <c r="F129" s="50">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
@@ -4676,7 +4676,7 @@
         <v>359</v>
       </c>
       <c r="F130" s="50">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
@@ -4786,13 +4786,13 @@
         <v>468</v>
       </c>
       <c r="D136" s="49">
-        <v>3.7</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="E136" s="32" t="s">
         <v>365</v>
       </c>
       <c r="F136" s="50">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
@@ -4812,7 +4812,7 @@
         <v>366</v>
       </c>
       <c r="F137" s="50">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
@@ -4882,7 +4882,7 @@
         <v>468</v>
       </c>
       <c r="D141" s="49">
-        <v>9.15</v>
+        <v>9.69</v>
       </c>
       <c r="E141" s="32" t="s">
         <v>370</v>
@@ -4920,13 +4920,13 @@
         <v>468</v>
       </c>
       <c r="D143" s="49">
-        <v>6.32</v>
+        <v>6.5600000000000005</v>
       </c>
       <c r="E143" s="32" t="s">
         <v>372</v>
       </c>
       <c r="F143" s="50">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
@@ -4958,7 +4958,7 @@
         <v>468</v>
       </c>
       <c r="D145" s="49">
-        <v>9.8000000000000007</v>
+        <v>10.53</v>
       </c>
       <c r="E145" s="33" t="s">
         <v>374</v>
@@ -4984,7 +4984,7 @@
         <v>375</v>
       </c>
       <c r="F146" s="50">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
@@ -5062,7 +5062,7 @@
         <v>438</v>
       </c>
       <c r="F150" s="52">
-        <v>250</v>
+        <v>280</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
@@ -5170,7 +5170,7 @@
         <v>444</v>
       </c>
       <c r="F156" s="52">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
@@ -5230,7 +5230,7 @@
         <v>447</v>
       </c>
       <c r="F159" s="52">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
@@ -5250,7 +5250,7 @@
         <v>448</v>
       </c>
       <c r="F160" s="52">
-        <v>151</v>
+        <v>143</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
@@ -5270,7 +5270,7 @@
         <v>449</v>
       </c>
       <c r="F161" s="52">
-        <v>254</v>
+        <v>248</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
@@ -5310,7 +5310,7 @@
         <v>451</v>
       </c>
       <c r="F163" s="52">
-        <v>85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
